--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A4F930-F9B2-5442-9A03-7BB034FC45F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A75BF7-25AB-5540-BB28-9B46579182B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20900" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maps!$A$1:$K$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maps!$A$1:$L$177</definedName>
     <definedName name="partID">[1]parts!$A:$A</definedName>
     <definedName name="partLabel">[1]parts!$B:$B</definedName>
   </definedNames>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="477">
   <si>
     <t>reporting_jurisdiction</t>
   </si>
@@ -1157,9 +1157,6 @@
     <t>Complete</t>
   </si>
   <si>
-    <t>{"expr":"(str({dashboard_ignore}) == 'yes') + (str({analysis_ignore}) == 'yes') == 0"}</t>
-  </si>
-  <si>
     <t>Temporary expr to merge this with sample_collect_date</t>
   </si>
   <si>
@@ -1464,6 +1461,28 @@
   </si>
   <si>
     <t>unused_customData</t>
+  </si>
+  <si>
+    <t>collPer</t>
+  </si>
+  <si>
+    <t>exprValue</t>
+  </si>
+  <si>
+    <t>def get_coll_per(val: str) -&gt; str:
+    val = val.split(" ", maxsplit=1)[0]
+    hours = val.split("-hr")
+    if len(hours) == 2:
+        hours = hours[0]
+        return hours
+    return ""
+target = get_coll_per(src.sample_type)</t>
+  </si>
+  <si>
+    <t>(str(dashboard_ignore) == 'yes') + (str(analysis_ignore) == 'yes') == 0</t>
+  </si>
+  <si>
+    <t>---</t>
   </si>
 </sst>
 </file>
@@ -1589,7 +1608,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1627,6 +1646,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12835,7 +12859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}">
-  <dimension ref="A1:K176"/>
+  <dimension ref="A1:L177"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10"/>
@@ -12844,52 +12868,55 @@
     <col min="4" max="4" width="24.6640625" style="10" customWidth="1"/>
     <col min="5" max="5" width="17.5" style="10" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" style="10" customWidth="1"/>
-    <col min="7" max="9" width="20" style="10" customWidth="1"/>
-    <col min="10" max="10" width="28.6640625" style="10" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="10"/>
+    <col min="7" max="10" width="20" style="10" customWidth="1"/>
+    <col min="11" max="11" width="28.6640625" style="10" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>369</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L1" s="6" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>0</v>
@@ -12902,20 +12929,21 @@
         <v>131</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="12"/>
+      <c r="K2" s="11" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>4</v>
@@ -12928,18 +12956,19 @@
         <v>145</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
-      <c r="J3" s="11"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J3" s="12"/>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>1</v>
@@ -12952,15 +12981,16 @@
         <v>89</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>2</v>
@@ -12972,15 +13002,15 @@
         <v>93</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>3</v>
@@ -12993,18 +13023,19 @@
         <v>91</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K6" s="11"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>4</v>
@@ -13017,15 +13048,16 @@
         <v>92</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="11"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B8" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>5</v>
@@ -13037,15 +13069,15 @@
         <v>179</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>6</v>
@@ -13065,8 +13097,9 @@
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="11"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="b">
         <v>1</v>
       </c>
@@ -13083,13 +13116,14 @@
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K10" s="11"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="b">
         <v>0</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>7</v>
@@ -13106,17 +13140,18 @@
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J11" s="14"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>8</v>
@@ -13129,18 +13164,19 @@
         <v>113</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="11"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="b">
         <v>0</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>8</v>
@@ -13160,8 +13196,9 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="11"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="b">
         <v>0</v>
       </c>
@@ -13175,11 +13212,12 @@
       <c r="G14" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="H14" s="11"/>
+      <c r="H14" s="21"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="11"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="b">
         <v>0</v>
       </c>
@@ -13196,8 +13234,9 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="b">
         <v>0</v>
       </c>
@@ -13214,8 +13253,9 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K16" s="11"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="b">
         <v>0</v>
       </c>
@@ -13229,11 +13269,12 @@
       <c r="G17" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="H17" s="11"/>
+      <c r="H17" s="21"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K17" s="11"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="b">
         <v>0</v>
       </c>
@@ -13250,8 +13291,9 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K18" s="11"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="b">
         <v>0</v>
       </c>
@@ -13268,8 +13310,9 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
       <c r="J19" s="11"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K19" s="11"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="b">
         <v>0</v>
       </c>
@@ -13286,8 +13329,9 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K20" s="11"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="b">
         <v>0</v>
       </c>
@@ -13304,8 +13348,9 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K21" s="11"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="b">
         <v>0</v>
       </c>
@@ -13322,8 +13367,9 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K22" s="11"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="b">
         <v>0</v>
       </c>
@@ -13340,8 +13386,9 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K23" s="11"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="b">
         <v>0</v>
       </c>
@@ -13355,11 +13402,12 @@
       <c r="G24" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="H24" s="11"/>
+      <c r="H24" s="21"/>
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K24" s="11"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="b">
         <v>0</v>
       </c>
@@ -13376,8 +13424,9 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K25" s="11"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="b">
         <v>0</v>
       </c>
@@ -13394,8 +13443,9 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K26" s="11"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="b">
         <v>0</v>
       </c>
@@ -13412,8 +13462,9 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K27" s="11"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="D28" s="5" t="s">
         <v>112</v>
       </c>
@@ -13422,10 +13473,11 @@
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J28" s="13"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B29" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>9</v>
@@ -13437,12 +13489,12 @@
         <v>133</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B30" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>10</v>
@@ -13454,15 +13506,15 @@
         <v>133</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>11</v>
@@ -13475,15 +13527,16 @@
         <v>132</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
       <c r="J31" s="11"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K31" s="11"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B32" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>12</v>
@@ -13495,12 +13548,12 @@
         <v>131</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B33" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>13</v>
@@ -13512,12 +13565,12 @@
         <v>179</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B34" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>14</v>
@@ -13529,12 +13582,12 @@
         <v>179</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B35" s="12" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>15</v>
@@ -13547,17 +13600,18 @@
         <v>179</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="12" t="s">
+      <c r="J35" s="12"/>
+      <c r="K35" s="12" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B36" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>16</v>
@@ -13569,15 +13623,15 @@
         <v>179</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>17</v>
@@ -13594,11 +13648,12 @@
       <c r="G37" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="H37" s="11"/>
+      <c r="H37" s="21"/>
       <c r="I37" s="11"/>
       <c r="J37" s="11"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K37" s="11"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="b">
         <v>1</v>
       </c>
@@ -13614,11 +13669,12 @@
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
-      <c r="J38" s="12" t="s">
+      <c r="J38" s="11"/>
+      <c r="K38" s="12" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="b">
         <v>1</v>
       </c>
@@ -13634,231 +13690,246 @@
       </c>
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
-      <c r="J39" s="12" t="s">
+      <c r="J39" s="11"/>
+      <c r="K39" s="12" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="D40" s="5" t="s">
         <v>137</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="J40" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="K40" s="12" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="D41" s="5" t="s">
         <v>138</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="J41" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="K41" s="12" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="B42" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="11" t="s">
+      <c r="B42" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>476</v>
+      </c>
+      <c r="D42" s="5"/>
+      <c r="E42" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="F42" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="G42" s="11" t="s">
-        <v>417</v>
-      </c>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F42" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="H42" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="K42" s="12"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>146</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D43" s="3"/>
       <c r="E43" s="11" t="s">
         <v>139</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="G43" s="15" t="s">
-        <v>161</v>
+        <v>144</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>416</v>
       </c>
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
       <c r="J43" s="11"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K43" s="11"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="H44" s="11"/>
+      <c r="B44" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" s="21"/>
       <c r="I44" s="11"/>
       <c r="J44" s="11"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K44" s="11"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="D45" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
       <c r="J45" s="11"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K45" s="11"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
       <c r="D46" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
       <c r="J46" s="11"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K46" s="11"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="D47" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
       <c r="J47" s="11"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K47" s="11"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
       <c r="D48" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
       <c r="J48" s="11"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K48" s="11"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
       <c r="D49" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
-      <c r="G49" s="15" t="s">
-        <v>152</v>
+      <c r="G49" s="11" t="s">
+        <v>158</v>
       </c>
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
       <c r="J49" s="11"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K49" s="11"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
       <c r="D50" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
-      <c r="G50" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="H50" s="11"/>
+      <c r="G50" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="H50" s="21"/>
       <c r="I50" s="11"/>
       <c r="J50" s="11"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B51" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C51" s="10" t="s">
+      <c r="K50" s="11"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B52" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C52" s="10" t="s">
         <v>20</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B52" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>21</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>129</v>
@@ -13867,34 +13938,32 @@
         <v>179</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B53" s="12" t="s">
-        <v>467</v>
-      </c>
-      <c r="C53" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B53" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B54" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="C54" s="12" t="s">
         <v>22</v>
-      </c>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="G53" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="H53" s="12"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="12"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B54" s="12" t="s">
-        <v>467</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>23</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="12"/>
@@ -13902,35 +13971,39 @@
         <v>179</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
       <c r="J54" s="12"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B55" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C55" s="10" t="s">
+      <c r="K54" s="12"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B55" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="12"/>
+      <c r="K55" s="12"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B56" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C56" s="10" t="s">
         <v>24</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B56" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>25</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>175</v>
@@ -13939,15 +14012,15 @@
         <v>179</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B57" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>175</v>
@@ -13956,15 +14029,15 @@
         <v>179</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B58" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>175</v>
@@ -13973,15 +14046,15 @@
         <v>179</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B59" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>175</v>
@@ -13990,15 +14063,15 @@
         <v>179</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B60" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>175</v>
@@ -14007,15 +14080,15 @@
         <v>179</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B61" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>175</v>
@@ -14024,15 +14097,15 @@
         <v>179</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B62" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>175</v>
@@ -14041,15 +14114,15 @@
         <v>179</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B63" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>175</v>
@@ -14058,15 +14131,15 @@
         <v>179</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B64" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>175</v>
@@ -14075,15 +14148,15 @@
         <v>179</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B65" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>175</v>
@@ -14092,15 +14165,15 @@
         <v>179</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B66" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>175</v>
@@ -14109,15 +14182,15 @@
         <v>179</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B67" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>175</v>
@@ -14126,307 +14199,313 @@
         <v>179</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B68" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C68" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B69" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C69" s="10" t="s">
         <v>37</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B69" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>38</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>129</v>
       </c>
       <c r="F69" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B70" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F70" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="G69" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A70" s="10" t="b">
+      <c r="G70" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A71" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="B70" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C70" s="11" t="s">
+      <c r="B71" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C71" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11" t="s">
+      <c r="D71" s="11"/>
+      <c r="E71" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F70" s="11" t="s">
+      <c r="F71" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G70" s="11" t="s">
+      <c r="G71" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B72" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A73" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="G73" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="H70" s="11"/>
-      <c r="I70" s="11"/>
-      <c r="J70" s="11"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B71" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E71" s="10" t="s">
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B74" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E74" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="F71" s="13" t="s">
+      <c r="F74" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="G71" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A72" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11" t="s">
+      <c r="G74" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A75" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="11" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B76" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E76" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F76" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A77" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F77" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G72" s="11" t="s">
-        <v>419</v>
-      </c>
-      <c r="H72" s="11"/>
-      <c r="I72" s="11"/>
-      <c r="J72" s="11"/>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B73" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E73" s="10" t="s">
+      <c r="G77" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="H77" s="11"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="11" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B78" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E78" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="F73" s="13" t="s">
+      <c r="F78" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="G73" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A74" s="10" t="b">
+      <c r="G78" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A79" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="B74" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11" t="s">
+      <c r="B79" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F74" s="11" t="s">
+      <c r="F79" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G74" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="H74" s="11"/>
-      <c r="I74" s="11"/>
-      <c r="J74" s="11"/>
-      <c r="K74" s="11" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B75" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E75" s="10" t="s">
+      <c r="G79" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="11"/>
+      <c r="K79" s="11"/>
+      <c r="L79" s="11" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B80" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E80" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="F75" s="13" t="s">
+      <c r="F80" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="G75" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A76" s="10" t="b">
+      <c r="G80" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A81" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="B76" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="F76" s="11" t="s">
+      <c r="B81" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F81" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G76" s="11" t="s">
-        <v>421</v>
-      </c>
-      <c r="H76" s="11"/>
-      <c r="I76" s="11"/>
-      <c r="J76" s="11"/>
-      <c r="K76" s="11" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B77" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F77" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="G77" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A78" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C78" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="F78" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G78" s="11" t="s">
+      <c r="G81" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="H78" s="11"/>
-      <c r="I78" s="11"/>
-      <c r="J78" s="11"/>
-      <c r="K78" s="11" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B79" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F79" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="G79" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A80" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="F80" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G80" s="11" t="s">
-        <v>423</v>
-      </c>
-      <c r="H80" s="11"/>
-      <c r="I80" s="11"/>
-      <c r="J80" s="11"/>
-      <c r="K80" s="11" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B81" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C81" s="10" t="s">
+      <c r="H81" s="11"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="11" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B82" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C82" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F81" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B82" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C82" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>175</v>
@@ -14435,46 +14514,35 @@
         <v>179</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A83" s="10" t="b">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B83" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F83" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A84" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="B83" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C83" s="11" t="s">
+      <c r="B84" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C84" s="11" t="s">
         <v>52</v>
-      </c>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="F83" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="G83" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="H83" s="11"/>
-      <c r="I83" s="11" t="s">
-        <v>462</v>
-      </c>
-      <c r="J83" s="12" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A84" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>53</v>
       </c>
       <c r="D84" s="11"/>
       <c r="E84" s="11" t="s">
@@ -14488,22 +14556,22 @@
       </c>
       <c r="H84" s="11"/>
       <c r="I84" s="11"/>
-      <c r="J84" s="12" t="s">
+      <c r="J84" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="K84" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="K84" s="11" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="10" t="b">
         <v>0</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D85" s="11"/>
       <c r="E85" s="11" t="s">
@@ -14517,36 +14585,50 @@
       </c>
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
-      <c r="J85" s="12" t="s">
+      <c r="J85" s="11"/>
+      <c r="K85" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="K85" s="11" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B86" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C86" s="10" t="s">
+      <c r="L85" s="11" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A86" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="H86" s="11"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="11"/>
+      <c r="K86" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="L86" s="11" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B87" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C87" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F86" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="G86" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B87" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>129</v>
@@ -14555,15 +14637,15 @@
         <v>179</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B88" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>129</v>
@@ -14572,15 +14654,15 @@
         <v>179</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B89" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>129</v>
@@ -14589,15 +14671,15 @@
         <v>179</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B90" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>129</v>
@@ -14606,15 +14688,15 @@
         <v>179</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B91" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>129</v>
@@ -14623,113 +14705,113 @@
         <v>179</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A92" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D92" s="11"/>
-      <c r="E92" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="F92" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="G92" s="11" t="s">
-        <v>424</v>
-      </c>
-      <c r="H92" s="11"/>
-      <c r="I92" s="11"/>
-      <c r="J92" s="11"/>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B92" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F92" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D93" s="11"/>
       <c r="E93" s="11" t="s">
         <v>139</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H93" s="11"/>
       <c r="I93" s="11"/>
       <c r="J93" s="11"/>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="11"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D94" s="11" t="s">
-        <v>165</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D94" s="11"/>
       <c r="E94" s="11" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G94" s="11" t="s">
-        <v>172</v>
+        <v>424</v>
       </c>
       <c r="H94" s="11"/>
       <c r="I94" s="11"/>
-      <c r="J94" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J94" s="11"/>
+      <c r="K94" s="11"/>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="B95" s="11"/>
-      <c r="C95" s="11"/>
+      <c r="B95" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>63</v>
+      </c>
       <c r="D95" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="E95" s="11"/>
-      <c r="F95" s="11"/>
+        <v>165</v>
+      </c>
+      <c r="E95" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="F95" s="11" t="s">
+        <v>171</v>
+      </c>
       <c r="G95" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H95" s="11"/>
       <c r="I95" s="11"/>
-      <c r="J95" s="12" t="s">
+      <c r="J95" s="11"/>
+      <c r="K95" s="12" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="D96" s="11" t="s">
-        <v>463</v>
+        <v>166</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="11"/>
@@ -14738,211 +14820,221 @@
       </c>
       <c r="H96" s="11"/>
       <c r="I96" s="11"/>
-      <c r="J96" s="12" t="s">
+      <c r="J96" s="11"/>
+      <c r="K96" s="12" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="B97" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C97" s="11" t="s">
+      <c r="B97" s="11"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="E97" s="11"/>
+      <c r="F97" s="11"/>
+      <c r="G97" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H97" s="11"/>
+      <c r="I97" s="11"/>
+      <c r="J97" s="11"/>
+      <c r="K97" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A98" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C98" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="D98" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E97" s="11" t="s">
+      <c r="E98" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="F97" s="11" t="s">
+      <c r="F98" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="G97" s="11" t="s">
-        <v>426</v>
-      </c>
-      <c r="H97" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="I97" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="J97" s="12" t="s">
+      <c r="G98" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="H98" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="I98" s="11"/>
+      <c r="J98" s="11"/>
+      <c r="K98" s="12" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A98" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="B98" s="11"/>
-      <c r="C98" s="11"/>
-      <c r="D98" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="E98" s="11"/>
-      <c r="F98" s="11"/>
-      <c r="G98" s="11" t="s">
-        <v>427</v>
-      </c>
-      <c r="H98" s="11"/>
-      <c r="I98" s="11"/>
-      <c r="J98" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="K98" s="10" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="10" t="b">
         <v>0</v>
       </c>
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="D99" s="11" t="s">
-        <v>463</v>
+        <v>166</v>
       </c>
       <c r="E99" s="11"/>
       <c r="F99" s="11"/>
       <c r="G99" s="11" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H99" s="11"/>
       <c r="I99" s="11"/>
-      <c r="J99" s="12" t="s">
+      <c r="J99" s="11"/>
+      <c r="K99" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="K99" s="10" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="10" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="B100" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>65</v>
-      </c>
+      <c r="B100" s="11"/>
+      <c r="C100" s="11"/>
       <c r="D100" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E100" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="F100" s="11" t="s">
-        <v>168</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="E100" s="11"/>
+      <c r="F100" s="11"/>
       <c r="G100" s="11" t="s">
         <v>426</v>
       </c>
       <c r="H100" s="11"/>
       <c r="I100" s="11"/>
-      <c r="J100" s="12" t="s">
+      <c r="J100" s="11"/>
+      <c r="K100" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="K100" s="10" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="10" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="B101" s="11"/>
-      <c r="C101" s="11"/>
+      <c r="B101" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="D101" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="E101" s="11"/>
-      <c r="F101" s="11"/>
+        <v>165</v>
+      </c>
+      <c r="E101" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="F101" s="11" t="s">
+        <v>168</v>
+      </c>
       <c r="G101" s="11" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H101" s="11"/>
       <c r="I101" s="11"/>
-      <c r="J101" s="12" t="s">
+      <c r="J101" s="11"/>
+      <c r="K101" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="K101" s="10" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="10" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="10" t="b">
         <v>0</v>
       </c>
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11" t="s">
-        <v>463</v>
+        <v>166</v>
       </c>
       <c r="E102" s="11"/>
       <c r="F102" s="11"/>
       <c r="G102" s="11" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H102" s="11"/>
       <c r="I102" s="11"/>
-      <c r="J102" s="12" t="s">
+      <c r="J102" s="11"/>
+      <c r="K102" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="K102" s="10" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L102" s="10" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B103" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C103" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D103" s="11"/>
-      <c r="E103" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="F103" s="11" t="s">
-        <v>188</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B103" s="11"/>
+      <c r="C103" s="11"/>
+      <c r="D103" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="E103" s="11"/>
+      <c r="F103" s="11"/>
       <c r="G103" s="11" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H103" s="11"/>
       <c r="I103" s="11"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B104" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C104" s="10" t="s">
+      <c r="J103" s="11"/>
+      <c r="K103" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="L103" s="10" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A104" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D104" s="11"/>
+      <c r="E104" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F104" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G104" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="H104" s="11"/>
+      <c r="I104" s="11"/>
+      <c r="J104" s="11"/>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B105" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C105" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="E104" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F104" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="G104" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B105" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C105" s="10" t="s">
-        <v>68</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>129</v>
@@ -14951,15 +15043,15 @@
         <v>179</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B106" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>129</v>
@@ -14968,15 +15060,15 @@
         <v>179</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B107" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>129</v>
@@ -14985,15 +15077,15 @@
         <v>179</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B108" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>129</v>
@@ -15002,15 +15094,15 @@
         <v>179</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B109" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>129</v>
@@ -15019,15 +15111,15 @@
         <v>179</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B110" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E110" s="10" t="s">
         <v>129</v>
@@ -15036,15 +15128,15 @@
         <v>179</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B111" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>129</v>
@@ -15053,15 +15145,15 @@
         <v>179</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B112" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>129</v>
@@ -15070,15 +15162,15 @@
         <v>179</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B113" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>129</v>
@@ -15087,15 +15179,15 @@
         <v>179</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B114" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>129</v>
@@ -15104,15 +15196,15 @@
         <v>179</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B115" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>129</v>
@@ -15121,15 +15213,15 @@
         <v>179</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B116" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>129</v>
@@ -15138,15 +15230,15 @@
         <v>179</v>
       </c>
       <c r="G116" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B117" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>129</v>
@@ -15155,15 +15247,15 @@
         <v>179</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B118" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>129</v>
@@ -15172,15 +15264,15 @@
         <v>179</v>
       </c>
       <c r="G118" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B119" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>129</v>
@@ -15189,15 +15281,15 @@
         <v>179</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B120" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>129</v>
@@ -15206,71 +15298,66 @@
         <v>179</v>
       </c>
       <c r="G120" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A121" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="B121" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C121" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D121" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E121" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="F121" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="G121" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="H121" s="11"/>
-      <c r="I121" s="11"/>
-      <c r="J121" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="K121" s="11" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B121" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F121" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="G121" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="B122" s="11"/>
-      <c r="C122" s="11"/>
+      <c r="B122" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>84</v>
+      </c>
       <c r="D122" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="E122" s="11"/>
-      <c r="F122" s="11"/>
+        <v>165</v>
+      </c>
+      <c r="E122" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="F122" s="11" t="s">
+        <v>171</v>
+      </c>
       <c r="G122" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H122" s="11"/>
       <c r="I122" s="11"/>
-      <c r="J122" s="12" t="s">
+      <c r="J122" s="11"/>
+      <c r="K122" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="K122" s="11" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L122" s="11" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" s="10" t="b">
         <v>0</v>
       </c>
       <c r="B123" s="11"/>
       <c r="C123" s="11"/>
       <c r="D123" s="11" t="s">
-        <v>463</v>
+        <v>166</v>
       </c>
       <c r="E123" s="11"/>
       <c r="F123" s="11"/>
@@ -15279,496 +15366,523 @@
       </c>
       <c r="H123" s="11"/>
       <c r="I123" s="11"/>
-      <c r="J123" s="12" t="s">
+      <c r="J123" s="11"/>
+      <c r="K123" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="K123" s="11" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L123" s="11" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B124" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D124" s="11"/>
-      <c r="E124" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="F124" s="11" t="s">
-        <v>351</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B124" s="11"/>
+      <c r="C124" s="11"/>
+      <c r="D124" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="E124" s="11"/>
+      <c r="F124" s="11"/>
       <c r="G124" s="11" t="s">
-        <v>429</v>
+        <v>173</v>
       </c>
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
       <c r="J124" s="11"/>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K124" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="L124" s="11" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D125" s="11"/>
       <c r="E125" s="11" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G125" s="11" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
       <c r="J125" s="11"/>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B126" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C126" s="10" t="s">
+      <c r="K125" s="11"/>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A126" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B126" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D126" s="11"/>
+      <c r="E126" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="F126" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="G126" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="H126" s="11"/>
+      <c r="I126" s="11"/>
+      <c r="J126" s="11"/>
+      <c r="K126" s="11"/>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B127" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C127" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D126" s="5" t="s">
+      <c r="D127" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="G126" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D127" s="5" t="s">
+      <c r="G127" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D128" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="G127" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D128" s="5" t="s">
-        <v>315</v>
-      </c>
       <c r="G128" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="129" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D129" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="130" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D130" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G130" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="131" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D131" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="132" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D132" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G132" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="133" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D133" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="134" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D134" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G134" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D135" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="136" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D136" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G136" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="137" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D137" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="G137" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="138" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="D138" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="G137" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="138" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B138" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C138" s="10" t="s">
+      <c r="G138" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="139" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B139" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C139" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="D138" s="5" t="s">
+      <c r="D139" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="G138" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="139" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D139" s="5" t="s">
-        <v>314</v>
-      </c>
       <c r="G139" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="140" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D140" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G140" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="141" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D141" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="142" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D142" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G142" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="143" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D143" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="144" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D144" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G144" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="145" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D145" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D146" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G146" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D147" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D148" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="149" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D149" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D150" s="5" t="s">
-        <v>463</v>
+        <v>324</v>
       </c>
       <c r="G150" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B151" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C151" s="10" t="s">
+      <c r="D151" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="G151" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="152" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B152" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C152" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D151" s="5" t="s">
+      <c r="D152" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="G151" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="152" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D152" s="5" t="s">
-        <v>314</v>
-      </c>
       <c r="G152" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="153" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D153" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="154" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D154" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G154" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D155" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="156" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D156" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G156" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="157" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D157" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="158" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D158" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G158" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D159" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D160" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G160" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="161" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D161" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="162" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D162" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G162" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="163" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D163" s="5" t="s">
-        <v>463</v>
+        <v>324</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="164" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B164" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C164" s="10" t="s">
+      <c r="D164" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="G164" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="165" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B165" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C165" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D164" s="5" t="s">
+      <c r="D165" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="G164" s="10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="165" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D165" s="5" t="s">
-        <v>314</v>
-      </c>
       <c r="G165" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="166" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D166" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G166" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="167" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D167" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="168" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D168" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G168" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="169" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D169" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G169" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="170" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D170" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G170" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="171" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D171" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="172" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D172" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G172" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="173" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D173" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="174" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D174" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G174" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="175" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D175" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="176" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D176" s="5" t="s">
-        <v>463</v>
+        <v>324</v>
       </c>
       <c r="G176" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
+      </c>
+    </row>
+    <row r="177" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D177" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="G177" s="10" t="s">
+        <v>376</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K176" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}"/>
-  <conditionalFormatting sqref="G43:I43">
+  <autoFilter ref="A1:L177" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}"/>
+  <conditionalFormatting sqref="G44:J44">
     <cfRule type="duplicateValues" dxfId="3" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15800,25 +15914,25 @@
         <v>369</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="H1" s="10" t="s">
         <v>464</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>439</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>465</v>
       </c>
       <c r="I1" s="10" t="s">
         <v>186</v>
@@ -15839,7 +15953,7 @@
         <v>181</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -15847,7 +15961,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>5</v>
@@ -15868,10 +15982,10 @@
         <v>191</v>
       </c>
       <c r="M2" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="N2" s="17" t="s">
         <v>377</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -15879,7 +15993,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
@@ -15897,13 +16011,13 @@
         <v>185</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -15911,7 +16025,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>14</v>
@@ -15932,10 +16046,10 @@
         <v>193</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -15943,7 +16057,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>16</v>
@@ -15958,10 +16072,10 @@
         <v>197</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -15969,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>20</v>
@@ -15990,10 +16104,10 @@
         <v>198</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16001,7 +16115,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>21</v>
@@ -16022,10 +16136,10 @@
         <v>199</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16033,7 +16147,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>22</v>
@@ -16042,7 +16156,7 @@
         <v>129</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>196</v>
@@ -16051,16 +16165,16 @@
         <v>201</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B9" s="12"/>
       <c r="C9" s="12" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>23</v>
@@ -16073,13 +16187,13 @@
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
       <c r="L9" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O9" s="12" t="s">
         <v>202</v>
@@ -16090,7 +16204,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>24</v>
@@ -16105,13 +16219,13 @@
         <v>326</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M10" s="11" t="s">
         <v>325</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16125,13 +16239,13 @@
         <v>327</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16145,13 +16259,13 @@
         <v>328</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16165,13 +16279,13 @@
         <v>329</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16179,16 +16293,16 @@
         <v>1</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16196,7 +16310,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>25</v>
@@ -16211,13 +16325,13 @@
         <v>332</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>330</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16231,13 +16345,13 @@
         <v>331</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="17" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16251,13 +16365,13 @@
         <v>333</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="18" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16271,13 +16385,13 @@
         <v>334</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16291,13 +16405,13 @@
         <v>335</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="20" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16311,13 +16425,13 @@
         <v>336</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="21" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16331,13 +16445,13 @@
         <v>335</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="22" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16351,13 +16465,13 @@
         <v>337</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="23" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16371,13 +16485,13 @@
         <v>338</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16391,13 +16505,13 @@
         <v>339</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="25" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16411,13 +16525,13 @@
         <v>341</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="26" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16431,13 +16545,13 @@
         <v>340</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="27" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16451,13 +16565,13 @@
         <v>342</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
@@ -16465,16 +16579,16 @@
         <v>230</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="29" spans="1:14" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -16488,13 +16602,13 @@
         <v>343</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="30" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16508,13 +16622,13 @@
         <v>344</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="31" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16528,13 +16642,13 @@
         <v>345</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="32" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16548,13 +16662,13 @@
         <v>346</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="33" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16568,13 +16682,13 @@
         <v>348</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N33" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="34" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16588,13 +16702,13 @@
         <v>347</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N34" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -16602,16 +16716,16 @@
         <v>237</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
@@ -16619,16 +16733,16 @@
         <v>238</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
@@ -16636,16 +16750,16 @@
         <v>239</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="38" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16659,13 +16773,13 @@
         <v>329</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M38" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="39" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16673,7 +16787,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>26</v>
@@ -16689,13 +16803,13 @@
         <v/>
       </c>
       <c r="L39" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M39" s="11" t="s">
         <v>349</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="40" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16710,13 +16824,13 @@
         <v/>
       </c>
       <c r="L40" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M40" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
@@ -16728,13 +16842,13 @@
         <v/>
       </c>
       <c r="L41" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N41" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
@@ -16746,13 +16860,13 @@
         <v/>
       </c>
       <c r="L42" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
@@ -16764,13 +16878,13 @@
         <v/>
       </c>
       <c r="L43" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
@@ -16782,13 +16896,13 @@
         <v/>
       </c>
       <c r="L44" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="45" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16803,13 +16917,13 @@
         <v/>
       </c>
       <c r="L45" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M45" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="46" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16824,13 +16938,13 @@
         <v/>
       </c>
       <c r="L46" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M46" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="47" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16845,13 +16959,13 @@
         <v/>
       </c>
       <c r="L47" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M47" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="48" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16866,13 +16980,13 @@
         <v/>
       </c>
       <c r="L48" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M48" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="49" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16887,13 +17001,13 @@
         <v/>
       </c>
       <c r="L49" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M49" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="50" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16908,13 +17022,13 @@
         <v/>
       </c>
       <c r="L50" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M50" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N50" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="51" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16929,13 +17043,13 @@
         <v/>
       </c>
       <c r="L51" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M51" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N51" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="52" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16950,13 +17064,13 @@
         <v/>
       </c>
       <c r="L52" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M52" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N52" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
@@ -16968,13 +17082,13 @@
         <v/>
       </c>
       <c r="L53" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M53" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N53" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="54" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16989,13 +17103,13 @@
         <v/>
       </c>
       <c r="L54" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M54" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N54" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="55" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17010,13 +17124,13 @@
         <v/>
       </c>
       <c r="L55" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M55" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N55" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="56" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17031,13 +17145,13 @@
         <v/>
       </c>
       <c r="L56" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M56" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N56" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="57" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17052,13 +17166,13 @@
         <v/>
       </c>
       <c r="L57" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M57" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N57" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="58" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17073,13 +17187,13 @@
         <v/>
       </c>
       <c r="L58" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M58" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N58" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
@@ -17091,13 +17205,13 @@
         <v/>
       </c>
       <c r="L59" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N59" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="60" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17112,13 +17226,13 @@
         <v/>
       </c>
       <c r="L60" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M60" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N60" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="61" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17133,13 +17247,13 @@
         <v/>
       </c>
       <c r="L61" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M61" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N61" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
@@ -17151,13 +17265,13 @@
         <v/>
       </c>
       <c r="L62" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M62" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N62" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="63" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17172,13 +17286,13 @@
         <v/>
       </c>
       <c r="L63" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M63" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N63" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
@@ -17190,13 +17304,13 @@
         <v/>
       </c>
       <c r="L64" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M64" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N64" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
@@ -17208,13 +17322,13 @@
         <v/>
       </c>
       <c r="L65" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N65" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
@@ -17226,13 +17340,13 @@
         <v/>
       </c>
       <c r="L66" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M66" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N66" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="67" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17247,13 +17361,13 @@
         <v/>
       </c>
       <c r="L67" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M67" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N67" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="68" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17268,13 +17382,13 @@
         <v/>
       </c>
       <c r="L68" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M68" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N68" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="69" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17289,13 +17403,13 @@
         <v/>
       </c>
       <c r="L69" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M69" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N69" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
@@ -17307,13 +17421,13 @@
         <v/>
       </c>
       <c r="L70" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M70" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N70" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
@@ -17325,13 +17439,13 @@
         <v/>
       </c>
       <c r="L71" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N71" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="72" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17339,7 +17453,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>27</v>
@@ -17364,10 +17478,10 @@
         <v>358</v>
       </c>
       <c r="M72" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N72" s="11" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="73" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17375,7 +17489,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>28</v>
@@ -17400,10 +17514,10 @@
         <v>359</v>
       </c>
       <c r="M73" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N73" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="74" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17411,7 +17525,7 @@
         <v>1</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D74" s="11" t="s">
         <v>29</v>
@@ -17436,10 +17550,10 @@
         <v>360</v>
       </c>
       <c r="M74" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N74" s="11" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="75" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17447,7 +17561,7 @@
         <v>1</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D75" s="11" t="s">
         <v>30</v>
@@ -17472,10 +17586,10 @@
         <v>361</v>
       </c>
       <c r="M75" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N75" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="76" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17483,7 +17597,7 @@
         <v>1</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D76" s="11" t="s">
         <v>31</v>
@@ -17502,13 +17616,13 @@
         <v>185</v>
       </c>
       <c r="L76" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M76" s="11" t="s">
         <v>362</v>
       </c>
       <c r="N76" s="11" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="77" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17516,7 +17630,7 @@
         <v>1</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D77" s="11" t="s">
         <v>32</v>
@@ -17529,13 +17643,13 @@
         <v/>
       </c>
       <c r="L77" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M77" s="11" t="s">
         <v>363</v>
       </c>
       <c r="N77" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="78" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17543,13 +17657,13 @@
         <v>1</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D78" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>175</v>
@@ -17559,13 +17673,13 @@
         <v/>
       </c>
       <c r="L78" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M78" s="11" t="s">
         <v>364</v>
       </c>
       <c r="N78" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
@@ -17577,13 +17691,13 @@
         <v/>
       </c>
       <c r="L79" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M79" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="80" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17598,13 +17712,13 @@
         <v/>
       </c>
       <c r="L80" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M80" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N80" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="81" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17619,13 +17733,13 @@
         <v/>
       </c>
       <c r="L81" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M81" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N81" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="82" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17640,13 +17754,13 @@
         <v/>
       </c>
       <c r="L82" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M82" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N82" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="83" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17661,13 +17775,13 @@
         <v/>
       </c>
       <c r="L83" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M83" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N83" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="84" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17682,13 +17796,13 @@
         <v/>
       </c>
       <c r="L84" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M84" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N84" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="85" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17703,13 +17817,13 @@
         <v/>
       </c>
       <c r="L85" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M85" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N85" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="86" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17724,13 +17838,13 @@
         <v/>
       </c>
       <c r="L86" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M86" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N86" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="87" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17745,13 +17859,13 @@
         <v/>
       </c>
       <c r="L87" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M87" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N87" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="88" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17766,13 +17880,13 @@
         <v/>
       </c>
       <c r="L88" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M88" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N88" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
@@ -17784,13 +17898,13 @@
         <v/>
       </c>
       <c r="L89" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M89" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
@@ -17802,13 +17916,13 @@
         <v/>
       </c>
       <c r="L90" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M90" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N90" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
@@ -17820,13 +17934,13 @@
         <v/>
       </c>
       <c r="L91" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M91" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="92" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17841,13 +17955,13 @@
         <v/>
       </c>
       <c r="L92" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M92" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N92" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="93" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17862,13 +17976,13 @@
         <v/>
       </c>
       <c r="L93" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M93" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N93" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="94" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17876,13 +17990,13 @@
         <v>1</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D94" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F94" s="11" t="s">
         <v>175</v>
@@ -17892,13 +18006,13 @@
         <v/>
       </c>
       <c r="L94" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M94" s="11" t="s">
         <v>365</v>
       </c>
       <c r="N94" s="11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="95" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17913,13 +18027,13 @@
         <v/>
       </c>
       <c r="L95" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M95" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N95" s="11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="96" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17934,13 +18048,13 @@
         <v/>
       </c>
       <c r="L96" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M96" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N96" s="11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="97" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17955,13 +18069,13 @@
         <v/>
       </c>
       <c r="L97" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M97" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N97" s="11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="98" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17976,13 +18090,13 @@
         <v/>
       </c>
       <c r="L98" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M98" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N98" s="11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="99" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17997,13 +18111,13 @@
         <v/>
       </c>
       <c r="L99" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M99" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N99" s="11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="100" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18018,13 +18132,13 @@
         <v/>
       </c>
       <c r="L100" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M100" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N100" s="11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="101" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18032,7 +18146,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D101" s="11" t="s">
         <v>35</v>
@@ -18045,10 +18159,10 @@
         <v/>
       </c>
       <c r="L101" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N101" s="11" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="102" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18056,7 +18170,7 @@
         <v>1</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D102" s="11" t="s">
         <v>36</v>
@@ -18069,13 +18183,13 @@
         <v/>
       </c>
       <c r="L102" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M102" s="11" t="s">
         <v>366</v>
       </c>
       <c r="N102" s="11" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="103" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18083,7 +18197,7 @@
         <v>1</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D103" s="11" t="s">
         <v>40</v>
@@ -18099,13 +18213,13 @@
         <v/>
       </c>
       <c r="L103" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M103" s="11" t="s">
         <v>350</v>
       </c>
       <c r="N103" s="11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="104" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18120,13 +18234,13 @@
         <v/>
       </c>
       <c r="L104" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M104" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N104" s="11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="105" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18141,13 +18255,13 @@
         <v/>
       </c>
       <c r="L105" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M105" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N105" s="11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="106" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18162,13 +18276,13 @@
         <v/>
       </c>
       <c r="L106" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M106" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N106" s="11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="107" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18183,13 +18297,13 @@
         <v/>
       </c>
       <c r="L107" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M107" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N107" s="11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="108" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18204,13 +18318,13 @@
         <v/>
       </c>
       <c r="L108" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M108" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N108" s="11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.2">
@@ -18225,19 +18339,19 @@
         <v/>
       </c>
       <c r="L109" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B110" s="12"/>
       <c r="C110" s="12" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D110" s="12" t="s">
         <v>42</v>
@@ -18260,10 +18374,10 @@
       <c r="K110" s="12"/>
       <c r="L110" s="12"/>
       <c r="M110" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N110" s="12" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O110" s="12" t="s">
         <v>367</v>
@@ -18284,10 +18398,10 @@
         <v>196</v>
       </c>
       <c r="M111" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.2">
@@ -18305,10 +18419,10 @@
         <v>196</v>
       </c>
       <c r="M112" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N112" s="10" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="113" spans="3:14" x14ac:dyDescent="0.2">
@@ -18326,10 +18440,10 @@
         <v>196</v>
       </c>
       <c r="M113" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="114" spans="3:14" x14ac:dyDescent="0.2">
@@ -18347,10 +18461,10 @@
         <v>196</v>
       </c>
       <c r="M114" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N114" s="10" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="115" spans="3:14" x14ac:dyDescent="0.2">
@@ -18368,15 +18482,15 @@
         <v>196</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="116" spans="3:14" x14ac:dyDescent="0.2">
       <c r="E116" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F116" s="10" t="s">
         <v>129</v>
@@ -18389,15 +18503,15 @@
         <v>196</v>
       </c>
       <c r="M116" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N116" s="10" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="117" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C117" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>44</v>
@@ -18416,10 +18530,10 @@
         <v>196</v>
       </c>
       <c r="M117" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="118" spans="3:14" x14ac:dyDescent="0.2">
@@ -18437,10 +18551,10 @@
         <v>196</v>
       </c>
       <c r="M118" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N118" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="119" spans="3:14" x14ac:dyDescent="0.2">
@@ -18458,10 +18572,10 @@
         <v>196</v>
       </c>
       <c r="M119" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="120" spans="3:14" x14ac:dyDescent="0.2">
@@ -18479,15 +18593,15 @@
         <v>196</v>
       </c>
       <c r="M120" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N120" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="121" spans="3:14" x14ac:dyDescent="0.2">
       <c r="E121" s="10" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>129</v>
@@ -18500,15 +18614,15 @@
         <v>196</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="122" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C122" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D122" s="10" t="s">
         <v>46</v>
@@ -18527,10 +18641,10 @@
         <v>196</v>
       </c>
       <c r="M122" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N122" s="12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="123" spans="3:14" x14ac:dyDescent="0.2">
@@ -18548,10 +18662,10 @@
         <v>196</v>
       </c>
       <c r="M123" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="124" spans="3:14" x14ac:dyDescent="0.2">
@@ -18569,10 +18683,10 @@
         <v>196</v>
       </c>
       <c r="M124" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N124" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="125" spans="3:14" x14ac:dyDescent="0.2">
@@ -18590,10 +18704,10 @@
         <v>196</v>
       </c>
       <c r="M125" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="126" spans="3:14" x14ac:dyDescent="0.2">
@@ -18611,10 +18725,10 @@
         <v>196</v>
       </c>
       <c r="M126" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N126" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="127" spans="3:14" x14ac:dyDescent="0.2">
@@ -18632,10 +18746,10 @@
         <v>196</v>
       </c>
       <c r="M127" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="128" spans="3:14" x14ac:dyDescent="0.2">
@@ -18653,10 +18767,10 @@
         <v>196</v>
       </c>
       <c r="M128" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N128" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.2">
@@ -18674,10 +18788,10 @@
         <v>196</v>
       </c>
       <c r="M129" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.2">
@@ -18695,10 +18809,10 @@
         <v>196</v>
       </c>
       <c r="M130" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N130" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.2">
@@ -18716,15 +18830,15 @@
         <v>196</v>
       </c>
       <c r="M131" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="E132" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F132" s="10" t="s">
         <v>129</v>
@@ -18737,15 +18851,15 @@
         <v>196</v>
       </c>
       <c r="M132" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N132" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C133" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D133" s="10" t="s">
         <v>48</v>
@@ -18761,13 +18875,13 @@
         <v/>
       </c>
       <c r="L133" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M133" s="10" t="s">
         <v>368</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.2">
@@ -18779,19 +18893,19 @@
         <v/>
       </c>
       <c r="L134" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M134" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N134" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B135" s="12"/>
       <c r="C135" s="12" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D135" s="12" t="s">
         <v>50</v>
@@ -18807,13 +18921,13 @@
       <c r="J135" s="12"/>
       <c r="K135" s="12"/>
       <c r="L135" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M135" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N135" s="12" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O135" s="12" t="s">
         <v>357</v>
@@ -18821,7 +18935,7 @@
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C136" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D136" s="10" t="s">
         <v>51</v>
@@ -18834,18 +18948,18 @@
         <v/>
       </c>
       <c r="L136" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M136" s="10">
         <v>0</v>
       </c>
       <c r="N136" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C137" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D137" s="10" t="s">
         <v>55</v>
@@ -18870,10 +18984,10 @@
         <v>205</v>
       </c>
       <c r="M137" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="138" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18881,7 +18995,7 @@
         <v>1</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D138" s="11" t="s">
         <v>56</v>
@@ -18906,10 +19020,10 @@
         <v>56</v>
       </c>
       <c r="M138" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N138" s="11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18917,7 +19031,7 @@
         <v>1</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D139" s="11" t="s">
         <v>57</v>
@@ -18942,10 +19056,10 @@
         <v>207</v>
       </c>
       <c r="M139" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N139" s="11" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18953,7 +19067,7 @@
         <v>1</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D140" s="11" t="s">
         <v>58</v>
@@ -18978,10 +19092,10 @@
         <v>58</v>
       </c>
       <c r="M140" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N140" s="11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18989,7 +19103,7 @@
         <v>1</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D141" s="11" t="s">
         <v>59</v>
@@ -19014,10 +19128,10 @@
         <v>211</v>
       </c>
       <c r="M141" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N141" s="11" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -19025,7 +19139,7 @@
         <v>1</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D142" s="11" t="s">
         <v>60</v>
@@ -19050,15 +19164,15 @@
         <v>212</v>
       </c>
       <c r="M142" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N142" s="11" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C143" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D143" s="10" t="s">
         <v>68</v>
@@ -19074,15 +19188,15 @@
         <v>196</v>
       </c>
       <c r="M143" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C144" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D144" s="10" t="s">
         <v>69</v>
@@ -19098,15 +19212,15 @@
         <v>196</v>
       </c>
       <c r="M144" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N144" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="145" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C145" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D145" s="10" t="s">
         <v>70</v>
@@ -19122,15 +19236,15 @@
         <v>196</v>
       </c>
       <c r="M145" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="146" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C146" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D146" s="10" t="s">
         <v>71</v>
@@ -19146,15 +19260,15 @@
         <v>196</v>
       </c>
       <c r="M146" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N146" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="147" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C147" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D147" s="10" t="s">
         <v>72</v>
@@ -19170,15 +19284,15 @@
         <v>196</v>
       </c>
       <c r="M147" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="148" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C148" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D148" s="10" t="s">
         <v>73</v>
@@ -19194,15 +19308,15 @@
         <v>196</v>
       </c>
       <c r="M148" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N148" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="149" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C149" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D149" s="10" t="s">
         <v>74</v>
@@ -19218,15 +19332,15 @@
         <v>196</v>
       </c>
       <c r="M149" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="150" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C150" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D150" s="10" t="s">
         <v>75</v>
@@ -19242,15 +19356,15 @@
         <v>196</v>
       </c>
       <c r="M150" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N150" s="10" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="151" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C151" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D151" s="10" t="s">
         <v>76</v>
@@ -19266,15 +19380,15 @@
         <v>196</v>
       </c>
       <c r="M151" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="152" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C152" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D152" s="10" t="s">
         <v>77</v>
@@ -19290,15 +19404,15 @@
         <v>196</v>
       </c>
       <c r="M152" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N152" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="153" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C153" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D153" s="10" t="s">
         <v>78</v>
@@ -19314,15 +19428,15 @@
         <v>196</v>
       </c>
       <c r="M153" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="154" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C154" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D154" s="10" t="s">
         <v>80</v>
@@ -19338,15 +19452,15 @@
         <v>196</v>
       </c>
       <c r="M154" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N154" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="155" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C155" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D155" s="10" t="s">
         <v>82</v>
@@ -19362,10 +19476,10 @@
         <v>196</v>
       </c>
       <c r="M155" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -19401,16 +19515,16 @@
         <v>369</v>
       </c>
       <c r="B1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D1" t="s">
         <v>431</v>
       </c>
-      <c r="C1" t="s">
-        <v>405</v>
-      </c>
-      <c r="D1" t="s">
-        <v>432</v>
-      </c>
       <c r="E1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -19418,13 +19532,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C2" t="s">
         <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E2" t="s">
         <v>87</v>
@@ -19600,13 +19714,13 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C18" t="s">
         <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E18" t="s">
         <v>94</v>

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44561DC-8D91-C144-A146-4D385E4DE7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F473A2CA-C820-0046-94BE-355E30642FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="280" yWindow="500" windowWidth="39840" windowHeight="19600" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="280" yWindow="500" windowWidth="39840" windowHeight="19600" activeTab="2" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2590" uniqueCount="769">
   <si>
     <t>Reporter</t>
   </si>
@@ -2231,30 +2231,18 @@
     <t>{"group": "{{pcr_target}}"}</t>
   </si>
   <si>
-    <t>Remove sourceEnum and set sourceSlot=pcr_gene_target</t>
-  </si>
-  <si>
     <t>vs_pcr_gene_target</t>
   </si>
   <si>
     <t>vs_pcr_target</t>
   </si>
   <si>
-    <t>Remove sourceEnum and set sourceSlot=pcr_target</t>
-  </si>
-  <si>
-    <t>Remove sourceEnum and set sourceSlot=hum_frac_target_mic</t>
-  </si>
-  <si>
     <t>vs_hum_frac_target_mic</t>
   </si>
   <si>
     <t>{"reflink": "{{hum_frac_target_mic_ref}}"}</t>
   </si>
   <si>
-    <t>Remove sourceEnum and set sourceSlot=hum_frac_target_chem</t>
-  </si>
-  <si>
     <t>vs_hum_frac_target_chem</t>
   </si>
   <si>
@@ -2264,25 +2252,16 @@
     <t>vs_other_norm_name</t>
   </si>
   <si>
-    <t>Remove sourceEnum and set sourceSlot=other_norm_name</t>
-  </si>
-  <si>
     <t>{"reflink": "{{other_norm_ref}}"}</t>
   </si>
   <si>
     <t>vs_mic_chem_units</t>
   </si>
   <si>
-    <t>Remove sourceEnum and set sourceSlot=pcr_target_units</t>
-  </si>
-  <si>
     <t>vs_mic_chem_units_e</t>
   </si>
   <si>
     <t>Applies to slots hum_frac_mic_unit, hum_frac_chem_unit, other_norm_unit</t>
-  </si>
-  <si>
-    <t>Is "ignore" correct targetValue?</t>
   </si>
   <si>
     <t>def get_collPer(sample_type: str) -&gt; str:
@@ -2376,6 +2355,24 @@
   </si>
   <si>
     <t>major_lab_method_desc is not in NWSS LinkML schema</t>
+  </si>
+  <si>
+    <t>For source slot pcr_target</t>
+  </si>
+  <si>
+    <t>For source slot pcr_gene_target</t>
+  </si>
+  <si>
+    <t>For source slot .hum_frac_target_mic</t>
+  </si>
+  <si>
+    <t>For source slot hum_frac_target_chem</t>
+  </si>
+  <si>
+    <t>For source slot other_norm_name</t>
+  </si>
+  <si>
+    <t>For source slot pcr_target_units</t>
   </si>
 </sst>
 </file>
@@ -2530,7 +2527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2569,6 +2566,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13898,7 +13896,7 @@
         <v>121</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -13932,7 +13930,7 @@
         <v>82</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -13961,7 +13959,7 @@
         <v>127</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -13992,7 +13990,7 @@
         <v>84</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -14021,7 +14019,7 @@
         <v>85</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -14124,7 +14122,7 @@
       <c r="J10" s="6"/>
       <c r="K10" s="2"/>
       <c r="L10" s="23" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -14138,7 +14136,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="23"/>
+      <c r="L11" s="24"/>
     </row>
     <row r="12" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="b">
@@ -14698,7 +14696,7 @@
         <v>122</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -14725,7 +14723,7 @@
         <v>121</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
@@ -14753,7 +14751,7 @@
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="21" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
@@ -14780,7 +14778,7 @@
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="21" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
@@ -14808,7 +14806,7 @@
         <v>126</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
@@ -15091,13 +15089,13 @@
         <v>160</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="19" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
@@ -15121,7 +15119,7 @@
         <v>160</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
@@ -15129,7 +15127,7 @@
         <v>596</v>
       </c>
       <c r="L47" s="19" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
@@ -15153,13 +15151,13 @@
         <v>160</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
       <c r="L48" s="23" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
@@ -15297,7 +15295,7 @@
         <v>146</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
@@ -15326,7 +15324,7 @@
         <v>150</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -15685,7 +15683,7 @@
         <v>169</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
@@ -16215,7 +16213,7 @@
         <v>486</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
@@ -16242,13 +16240,13 @@
         <v>488</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
       <c r="L91" s="23" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
     </row>
   </sheetData>
@@ -20945,7 +20943,7 @@
         <v>171</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
@@ -21166,7 +21164,7 @@
         <v>665</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>177</v>
@@ -21206,7 +21204,7 @@
         <v>665</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>177</v>
@@ -21246,7 +21244,7 @@
         <v>665</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>177</v>
@@ -21301,16 +21299,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC10C3F-0C27-5546-8767-E60C7CACEA9D}">
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:J201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="6" max="7" width="25.5" customWidth="1"/>
+    <col min="8" max="8" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>700</v>
       </c>
@@ -21327,16 +21326,22 @@
         <v>652</v>
       </c>
       <c r="F1" s="20" t="s">
+        <v>653</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>654</v>
+      </c>
+      <c r="H1" s="20" t="s">
         <v>720</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="I1" s="20" t="s">
         <v>655</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="J1" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="b">
         <v>0</v>
       </c>
@@ -21350,15 +21355,17 @@
       <c r="E2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="b">
         <v>0</v>
       </c>
@@ -21372,15 +21379,17 @@
       <c r="E3" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="b">
         <v>0</v>
       </c>
@@ -21394,15 +21403,17 @@
       <c r="E4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="b">
         <v>0</v>
       </c>
@@ -21416,15 +21427,17 @@
       <c r="E5" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="b">
         <v>0</v>
       </c>
@@ -21438,15 +21451,17 @@
       <c r="E6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="b">
         <v>0</v>
       </c>
@@ -21460,15 +21475,17 @@
       <c r="E7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="b">
         <v>0</v>
       </c>
@@ -21482,15 +21499,17 @@
       <c r="E8" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="b">
         <v>0</v>
       </c>
@@ -21504,15 +21523,17 @@
       <c r="E9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="b">
         <v>0</v>
       </c>
@@ -21526,15 +21547,17 @@
       <c r="E10" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="b">
         <v>0</v>
       </c>
@@ -21548,15 +21571,17 @@
       <c r="E11" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="b">
         <v>0</v>
       </c>
@@ -21570,15 +21595,17 @@
       <c r="E12" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="b">
         <v>0</v>
       </c>
@@ -21592,15 +21619,17 @@
       <c r="E13" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="b">
         <v>0</v>
       </c>
@@ -21614,15 +21643,17 @@
       <c r="E14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="b">
         <v>0</v>
       </c>
@@ -21636,15 +21667,17 @@
       <c r="E15" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="b">
         <v>0</v>
       </c>
@@ -21658,15 +21691,17 @@
       <c r="E16" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="b">
         <v>0</v>
       </c>
@@ -21680,3341 +21715,3941 @@
       <c r="E17" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="b">
         <v>1</v>
       </c>
-      <c r="B18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="F18" s="22"/>
-      <c r="G18" s="2" t="s">
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J18" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="b">
         <v>1</v>
       </c>
-      <c r="B19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>292</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="b">
         <v>1</v>
       </c>
-      <c r="B20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>293</v>
       </c>
       <c r="F20" s="2"/>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="b">
         <v>1</v>
       </c>
-      <c r="B21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>294</v>
       </c>
       <c r="F21" s="2"/>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="b">
         <v>1</v>
       </c>
-      <c r="B22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F22" s="2"/>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="H22" s="2"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="b">
         <v>1</v>
       </c>
-      <c r="B23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>296</v>
       </c>
       <c r="F23" s="2"/>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="b">
         <v>1</v>
       </c>
-      <c r="B24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>297</v>
       </c>
       <c r="F24" s="2"/>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="b">
         <v>1</v>
       </c>
-      <c r="B25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>298</v>
       </c>
       <c r="F25" s="2"/>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="b">
         <v>1</v>
       </c>
-      <c r="B26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>299</v>
       </c>
       <c r="F26" s="2"/>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="b">
         <v>1</v>
       </c>
-      <c r="B27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>300</v>
       </c>
       <c r="F27" s="2"/>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="H27" s="2"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="b">
         <v>1</v>
       </c>
-      <c r="B28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>301</v>
       </c>
       <c r="F28" s="2"/>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="b">
         <v>1</v>
       </c>
-      <c r="B29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>302</v>
       </c>
       <c r="F29" s="2"/>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="b">
         <v>1</v>
       </c>
-      <c r="B30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>303</v>
       </c>
       <c r="F30" s="2"/>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="b">
         <v>1</v>
       </c>
-      <c r="B31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>304</v>
       </c>
       <c r="F31" s="2"/>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="H31" s="2"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="b">
         <v>1</v>
       </c>
-      <c r="B32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>305</v>
       </c>
       <c r="F32" s="2"/>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="b">
         <v>1</v>
       </c>
-      <c r="B33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>306</v>
       </c>
       <c r="F33" s="2"/>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="b">
         <v>1</v>
       </c>
-      <c r="B34" s="2"/>
+      <c r="B34" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>307</v>
       </c>
       <c r="F34" s="2"/>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="H34" s="2"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="b">
         <v>1</v>
       </c>
-      <c r="B35" s="2"/>
+      <c r="B35" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>308</v>
       </c>
       <c r="F35" s="2"/>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="b">
         <v>1</v>
       </c>
-      <c r="B36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>309</v>
       </c>
       <c r="F36" s="2"/>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="H36" s="2"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="b">
         <v>1</v>
       </c>
-      <c r="B37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>310</v>
       </c>
       <c r="F37" s="2"/>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="H37" s="2"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="b">
         <v>1</v>
       </c>
-      <c r="B38" s="2"/>
+      <c r="B38" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>311</v>
       </c>
       <c r="F38" s="2"/>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="H38" s="2"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J38" s="2"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="b">
         <v>1</v>
       </c>
-      <c r="B39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>312</v>
       </c>
       <c r="F39" s="2"/>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="H39" s="2"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="b">
         <v>1</v>
       </c>
-      <c r="B40" s="2"/>
+      <c r="B40" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>313</v>
       </c>
       <c r="F40" s="2"/>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="H40" s="2"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J40" s="2"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="b">
         <v>1</v>
       </c>
-      <c r="B41" s="2"/>
+      <c r="B41" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>314</v>
       </c>
       <c r="F41" s="2"/>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="H41" s="2"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J41" s="2"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="b">
         <v>1</v>
       </c>
-      <c r="B42" s="2"/>
+      <c r="B42" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>315</v>
       </c>
       <c r="F42" s="2"/>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="H42" s="2"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J42" s="2"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="b">
         <v>1</v>
       </c>
-      <c r="B43" s="2"/>
+      <c r="B43" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>322</v>
       </c>
       <c r="F43" s="2"/>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="H43" s="2"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J43" s="2"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="b">
         <v>1</v>
       </c>
-      <c r="B44" s="2"/>
+      <c r="B44" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>339</v>
       </c>
       <c r="F44" s="2"/>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="H44" s="2"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J44" s="2"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="b">
         <v>1</v>
       </c>
-      <c r="B45" s="2"/>
+      <c r="B45" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>370</v>
       </c>
       <c r="F45" s="2"/>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="H45" s="2"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J45" s="2"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="b">
         <v>1</v>
       </c>
-      <c r="B46" s="2"/>
+      <c r="B46" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>344</v>
       </c>
       <c r="F46" s="2"/>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="H46" s="2"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J46" s="2"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="b">
         <v>1</v>
       </c>
-      <c r="B47" s="2"/>
+      <c r="B47" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>346</v>
       </c>
       <c r="F47" s="2"/>
-      <c r="G47" s="2" t="s">
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="H47" s="2"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J47" s="2"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="b">
         <v>1</v>
       </c>
-      <c r="B48" s="2"/>
+      <c r="B48" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>333</v>
       </c>
       <c r="F48" s="2"/>
-      <c r="G48" s="2" t="s">
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="H48" s="2"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J48" s="2"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="b">
         <v>1</v>
       </c>
-      <c r="B49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>368</v>
       </c>
       <c r="F49" s="2"/>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="H49" s="2"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J49" s="2"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="b">
         <v>1</v>
       </c>
-      <c r="B50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>330</v>
       </c>
       <c r="F50" s="2"/>
-      <c r="G50" s="2" t="s">
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="H50" s="2"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J50" s="2"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="b">
         <v>1</v>
       </c>
-      <c r="B51" s="2"/>
+      <c r="B51" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>362</v>
       </c>
       <c r="F51" s="2"/>
-      <c r="G51" s="2" t="s">
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="H51" s="2"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J51" s="2"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="b">
         <v>1</v>
       </c>
-      <c r="B52" s="2"/>
+      <c r="B52" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>328</v>
       </c>
       <c r="F52" s="2"/>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="H52" s="2"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J52" s="2"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="b">
         <v>1</v>
       </c>
-      <c r="B53" s="2"/>
+      <c r="B53" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>325</v>
       </c>
       <c r="F53" s="2"/>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="H53" s="2"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J53" s="2"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="b">
         <v>1</v>
       </c>
-      <c r="B54" s="2"/>
+      <c r="B54" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>372</v>
       </c>
       <c r="F54" s="2"/>
-      <c r="G54" s="2" t="s">
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="H54" s="2"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J54" s="2"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="b">
         <v>1</v>
       </c>
-      <c r="B55" s="2"/>
+      <c r="B55" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>347</v>
       </c>
       <c r="F55" s="2"/>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="H55" s="2"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J55" s="2"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="b">
         <v>1</v>
       </c>
-      <c r="B56" s="2"/>
+      <c r="B56" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>335</v>
       </c>
       <c r="F56" s="2"/>
-      <c r="G56" s="2" t="s">
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="H56" s="2"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J56" s="2"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="b">
         <v>1</v>
       </c>
-      <c r="B57" s="2"/>
+      <c r="B57" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>338</v>
       </c>
       <c r="F57" s="2"/>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="H57" s="2"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J57" s="2"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="b">
         <v>1</v>
       </c>
-      <c r="B58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>349</v>
       </c>
       <c r="F58" s="2"/>
-      <c r="G58" s="2" t="s">
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="H58" s="2"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J58" s="2"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="b">
         <v>1</v>
       </c>
-      <c r="B59" s="2"/>
+      <c r="B59" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>373</v>
       </c>
       <c r="F59" s="2"/>
-      <c r="G59" s="2" t="s">
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="H59" s="2"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J59" s="2"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="b">
         <v>1</v>
       </c>
-      <c r="B60" s="2"/>
+      <c r="B60" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F60" s="2"/>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="H60" s="2"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J60" s="2"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="b">
         <v>1</v>
       </c>
-      <c r="B61" s="2"/>
+      <c r="B61" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>345</v>
       </c>
       <c r="F61" s="2"/>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="H61" s="2"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J61" s="2"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="b">
         <v>1</v>
       </c>
-      <c r="B62" s="2"/>
+      <c r="B62" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>324</v>
       </c>
       <c r="F62" s="2"/>
-      <c r="G62" s="2" t="s">
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="H62" s="2"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J62" s="2"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="b">
         <v>1</v>
       </c>
-      <c r="B63" s="2"/>
+      <c r="B63" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>355</v>
       </c>
       <c r="F63" s="2"/>
-      <c r="G63" s="2" t="s">
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="H63" s="2"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J63" s="2"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="b">
         <v>1</v>
       </c>
-      <c r="B64" s="2"/>
+      <c r="B64" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>332</v>
       </c>
       <c r="F64" s="2"/>
-      <c r="G64" s="2" t="s">
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="H64" s="2"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J64" s="2"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="b">
         <v>1</v>
       </c>
-      <c r="B65" s="2"/>
+      <c r="B65" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>350</v>
       </c>
       <c r="F65" s="2"/>
-      <c r="G65" s="2" t="s">
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="H65" s="2"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J65" s="2"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" t="b">
         <v>1</v>
       </c>
-      <c r="B66" s="2"/>
+      <c r="B66" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>357</v>
       </c>
       <c r="F66" s="2"/>
-      <c r="G66" s="2" t="s">
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="H66" s="2"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J66" s="2"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="b">
         <v>1</v>
       </c>
-      <c r="B67" s="2"/>
+      <c r="B67" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F67" s="2"/>
-      <c r="G67" s="2" t="s">
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="H67" s="2"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J67" s="2"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" t="b">
         <v>1</v>
       </c>
-      <c r="B68" s="2"/>
+      <c r="B68" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>343</v>
       </c>
       <c r="F68" s="2"/>
-      <c r="G68" s="2" t="s">
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="H68" s="2"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J68" s="2"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" t="b">
         <v>1</v>
       </c>
-      <c r="B69" s="2"/>
+      <c r="B69" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>342</v>
       </c>
       <c r="F69" s="2"/>
-      <c r="G69" s="2" t="s">
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="H69" s="2"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J69" s="2"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" t="b">
         <v>1</v>
       </c>
-      <c r="B70" s="2"/>
+      <c r="B70" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>329</v>
       </c>
       <c r="F70" s="2"/>
-      <c r="G70" s="2" t="s">
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="H70" s="2"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J70" s="2"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" t="b">
         <v>1</v>
       </c>
-      <c r="B71" s="2"/>
+      <c r="B71" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>371</v>
       </c>
       <c r="F71" s="2"/>
-      <c r="G71" s="2" t="s">
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="H71" s="2"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J71" s="2"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" t="b">
         <v>1</v>
       </c>
-      <c r="B72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>336</v>
       </c>
       <c r="F72" s="2"/>
-      <c r="G72" s="2" t="s">
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="H72" s="2"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J72" s="2"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" t="b">
         <v>1</v>
       </c>
-      <c r="B73" s="2"/>
+      <c r="B73" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>374</v>
       </c>
       <c r="F73" s="2"/>
-      <c r="G73" s="2" t="s">
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="H73" s="2"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J73" s="2"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" t="b">
         <v>1</v>
       </c>
-      <c r="B74" s="2"/>
+      <c r="B74" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>326</v>
       </c>
       <c r="F74" s="2"/>
-      <c r="G74" s="2" t="s">
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="H74" s="2"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J74" s="2"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" t="b">
         <v>1</v>
       </c>
-      <c r="B75" s="2"/>
+      <c r="B75" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>366</v>
       </c>
       <c r="F75" s="2"/>
-      <c r="G75" s="2" t="s">
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="H75" s="2"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J75" s="2"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" t="b">
         <v>1</v>
       </c>
-      <c r="B76" s="2"/>
+      <c r="B76" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>375</v>
       </c>
       <c r="F76" s="2"/>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="H76" s="2"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J76" s="2"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" t="b">
         <v>1</v>
       </c>
-      <c r="B77" s="2"/>
+      <c r="B77" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>348</v>
       </c>
       <c r="F77" s="2"/>
-      <c r="G77" s="2" t="s">
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="H77" s="2"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J77" s="2"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" t="b">
         <v>1</v>
       </c>
-      <c r="B78" s="2"/>
+      <c r="B78" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>361</v>
       </c>
       <c r="F78" s="2"/>
-      <c r="G78" s="2" t="s">
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="H78" s="2"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J78" s="2"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" t="b">
         <v>1</v>
       </c>
-      <c r="B79" s="2"/>
+      <c r="B79" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>363</v>
       </c>
       <c r="F79" s="2"/>
-      <c r="G79" s="2" t="s">
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="H79" s="2"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J79" s="2"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" t="b">
         <v>1</v>
       </c>
-      <c r="B80" s="2"/>
+      <c r="B80" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>365</v>
       </c>
       <c r="F80" s="2"/>
-      <c r="G80" s="2" t="s">
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="H80" s="2"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J80" s="2"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" t="b">
         <v>1</v>
       </c>
-      <c r="B81" s="2"/>
+      <c r="B81" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>321</v>
       </c>
       <c r="F81" s="2"/>
-      <c r="G81" s="2" t="s">
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="H81" s="2"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J81" s="2"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" t="b">
         <v>1</v>
       </c>
-      <c r="B82" s="2"/>
+      <c r="B82" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>376</v>
       </c>
       <c r="F82" s="2"/>
-      <c r="G82" s="2" t="s">
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="H82" s="2"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J82" s="2"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" t="b">
         <v>1</v>
       </c>
-      <c r="B83" s="2"/>
+      <c r="B83" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>316</v>
       </c>
       <c r="F83" s="2"/>
-      <c r="G83" s="2" t="s">
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="H83" s="2"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J83" s="2"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" t="b">
         <v>1</v>
       </c>
-      <c r="B84" s="2"/>
+      <c r="B84" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>317</v>
       </c>
       <c r="F84" s="2"/>
-      <c r="G84" s="2" t="s">
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="H84" s="2"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J84" s="2"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" t="b">
         <v>1</v>
       </c>
-      <c r="B85" s="2"/>
+      <c r="B85" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>340</v>
       </c>
       <c r="F85" s="2"/>
-      <c r="G85" s="2" t="s">
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="H85" s="2"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J85" s="2"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" t="b">
         <v>1</v>
       </c>
-      <c r="B86" s="2"/>
+      <c r="B86" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>327</v>
       </c>
       <c r="F86" s="2"/>
-      <c r="G86" s="2" t="s">
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="H86" s="2"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J86" s="2"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="b">
         <v>1</v>
       </c>
-      <c r="B87" s="2"/>
+      <c r="B87" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>369</v>
       </c>
       <c r="F87" s="2"/>
-      <c r="G87" s="2" t="s">
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="H87" s="2"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J87" s="2"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" t="b">
         <v>1</v>
       </c>
-      <c r="B88" s="2"/>
+      <c r="B88" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>356</v>
       </c>
       <c r="F88" s="2"/>
-      <c r="G88" s="2" t="s">
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="H88" s="2"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J88" s="2"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" t="b">
         <v>1</v>
       </c>
-      <c r="B89" s="2"/>
+      <c r="B89" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>358</v>
       </c>
       <c r="F89" s="2"/>
-      <c r="G89" s="2" t="s">
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="H89" s="2"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J89" s="2"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" t="b">
         <v>1</v>
       </c>
-      <c r="B90" s="2"/>
+      <c r="B90" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>364</v>
       </c>
       <c r="F90" s="2"/>
-      <c r="G90" s="2" t="s">
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="H90" s="2"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J90" s="2"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" t="b">
         <v>1</v>
       </c>
-      <c r="B91" s="2"/>
+      <c r="B91" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>331</v>
       </c>
       <c r="F91" s="2"/>
-      <c r="G91" s="2" t="s">
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="H91" s="2"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J91" s="2"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" t="b">
         <v>1</v>
       </c>
-      <c r="B92" s="2"/>
+      <c r="B92" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>337</v>
       </c>
       <c r="F92" s="2"/>
-      <c r="G92" s="2" t="s">
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="H92" s="2"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J92" s="2"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" t="b">
         <v>1</v>
       </c>
-      <c r="B93" s="2"/>
+      <c r="B93" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>351</v>
       </c>
       <c r="F93" s="2"/>
-      <c r="G93" s="2" t="s">
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="H93" s="2"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J93" s="2"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" t="b">
         <v>1</v>
       </c>
-      <c r="B94" s="2"/>
+      <c r="B94" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>352</v>
       </c>
       <c r="F94" s="2"/>
-      <c r="G94" s="2" t="s">
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="H94" s="2"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J94" s="2"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" t="b">
         <v>1</v>
       </c>
-      <c r="B95" s="2"/>
+      <c r="B95" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>353</v>
       </c>
       <c r="F95" s="2"/>
-      <c r="G95" s="2" t="s">
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="H95" s="2"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J95" s="2"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" t="b">
         <v>1</v>
       </c>
-      <c r="B96" s="2"/>
+      <c r="B96" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>354</v>
       </c>
       <c r="F96" s="2"/>
-      <c r="G96" s="2" t="s">
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="H96" s="2"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J96" s="2"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" t="b">
         <v>1</v>
       </c>
-      <c r="B97" s="2"/>
+      <c r="B97" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>323</v>
       </c>
       <c r="F97" s="2"/>
-      <c r="G97" s="2" t="s">
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="H97" s="2"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J97" s="2"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" t="b">
         <v>1</v>
       </c>
-      <c r="B98" s="2"/>
+      <c r="B98" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>318</v>
       </c>
       <c r="F98" s="2"/>
-      <c r="G98" s="2" t="s">
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="H98" s="2"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J98" s="2"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" t="b">
         <v>1</v>
       </c>
-      <c r="B99" s="2"/>
+      <c r="B99" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>360</v>
       </c>
       <c r="F99" s="2"/>
-      <c r="G99" s="2" t="s">
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="H99" s="2"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J99" s="2"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" t="b">
         <v>1</v>
       </c>
-      <c r="B100" s="2"/>
+      <c r="B100" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>367</v>
       </c>
       <c r="F100" s="2"/>
-      <c r="G100" s="2" t="s">
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="H100" s="2"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J100" s="2"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" t="b">
         <v>1</v>
       </c>
-      <c r="B101" s="2"/>
+      <c r="B101" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>319</v>
       </c>
       <c r="F101" s="2"/>
-      <c r="G101" s="2" t="s">
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="H101" s="2"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J101" s="2"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" t="b">
         <v>1</v>
       </c>
-      <c r="B102" s="2"/>
+      <c r="B102" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>334</v>
       </c>
       <c r="F102" s="2"/>
-      <c r="G102" s="2" t="s">
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="H102" s="2"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J102" s="2"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" t="b">
         <v>1</v>
       </c>
-      <c r="B103" s="2"/>
+      <c r="B103" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>359</v>
       </c>
       <c r="F103" s="2"/>
-      <c r="G103" s="2" t="s">
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="H103" s="2"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J103" s="2"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" t="b">
         <v>1</v>
       </c>
-      <c r="B104" s="2"/>
+      <c r="B104" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>377</v>
       </c>
       <c r="F104" s="2"/>
-      <c r="G104" s="2" t="s">
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="H104" s="2"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J104" s="2"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" t="b">
         <v>1</v>
       </c>
-      <c r="B105" s="2"/>
+      <c r="B105" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>378</v>
       </c>
       <c r="F105" s="2"/>
-      <c r="G105" s="2" t="s">
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="H105" s="2"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J105" s="2"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" t="b">
         <v>1</v>
       </c>
-      <c r="B106" s="2"/>
+      <c r="B106" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>379</v>
       </c>
       <c r="F106" s="2"/>
-      <c r="G106" s="2" t="s">
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="H106" s="2"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J106" s="2"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" t="b">
         <v>1</v>
       </c>
-      <c r="B107" s="2"/>
+      <c r="B107" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>380</v>
       </c>
       <c r="F107" s="2"/>
-      <c r="G107" s="2" t="s">
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="H107" s="2"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J107" s="2"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" t="b">
         <v>1</v>
       </c>
-      <c r="B108" s="2"/>
+      <c r="B108" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>381</v>
       </c>
       <c r="F108" s="2"/>
-      <c r="G108" s="2" t="s">
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="H108" s="2"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J108" s="2"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" t="b">
         <v>1</v>
       </c>
-      <c r="B109" s="2"/>
+      <c r="B109" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>382</v>
       </c>
       <c r="F109" s="2"/>
-      <c r="G109" s="2" t="s">
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="H109" s="2"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J109" s="2"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" t="b">
         <v>1</v>
       </c>
-      <c r="B110" s="2"/>
+      <c r="B110" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>383</v>
       </c>
       <c r="F110" s="2"/>
-      <c r="G110" s="2" t="s">
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="H110" s="2"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J110" s="2"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" t="b">
         <v>1</v>
       </c>
-      <c r="B111" s="2"/>
+      <c r="B111" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>384</v>
       </c>
       <c r="F111" s="2"/>
-      <c r="G111" s="2" t="s">
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+      <c r="I111" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="H111" s="2"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J111" s="2"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" t="b">
         <v>1</v>
       </c>
-      <c r="B112" s="2"/>
+      <c r="B112" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>385</v>
       </c>
       <c r="F112" s="2"/>
-      <c r="G112" s="2" t="s">
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="H112" s="2"/>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J112" s="2"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" t="b">
         <v>1</v>
       </c>
-      <c r="B113" s="2"/>
+      <c r="B113" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>386</v>
       </c>
       <c r="F113" s="2"/>
-      <c r="G113" s="2" t="s">
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+      <c r="I113" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="H113" s="2"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J113" s="2"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" t="b">
         <v>1</v>
       </c>
-      <c r="B114" s="2"/>
+      <c r="B114" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F114" s="2"/>
-      <c r="G114" s="2" t="s">
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="H114" s="2"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J114" s="2"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" t="b">
         <v>1</v>
       </c>
-      <c r="B115" s="2"/>
+      <c r="B115" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>388</v>
       </c>
       <c r="F115" s="2"/>
-      <c r="G115" s="2" t="s">
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="H115" s="2"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J115" s="2"/>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" t="b">
         <v>1</v>
       </c>
-      <c r="B116" s="2"/>
+      <c r="B116" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>389</v>
       </c>
       <c r="F116" s="2"/>
-      <c r="G116" s="2" t="s">
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+      <c r="I116" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="H116" s="2"/>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J116" s="2"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" t="b">
         <v>1</v>
       </c>
-      <c r="B117" s="2"/>
+      <c r="B117" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>390</v>
       </c>
       <c r="F117" s="2"/>
-      <c r="G117" s="2" t="s">
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="H117" s="2"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J117" s="2"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" t="b">
         <v>1</v>
       </c>
-      <c r="B118" s="2"/>
+      <c r="B118" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>391</v>
       </c>
       <c r="F118" s="2"/>
-      <c r="G118" s="2" t="s">
+      <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+      <c r="I118" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="H118" s="2"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J118" s="2"/>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" t="b">
         <v>1</v>
       </c>
-      <c r="B119" s="2"/>
+      <c r="B119" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>392</v>
       </c>
       <c r="F119" s="2"/>
-      <c r="G119" s="2" t="s">
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+      <c r="I119" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="H119" s="2"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J119" s="2"/>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" t="b">
         <v>1</v>
       </c>
-      <c r="B120" s="2"/>
+      <c r="B120" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>393</v>
       </c>
       <c r="F120" s="2"/>
-      <c r="G120" s="2" t="s">
+      <c r="G120" s="2"/>
+      <c r="H120" s="2"/>
+      <c r="I120" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="H120" s="2"/>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J120" s="2"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" t="b">
         <v>1</v>
       </c>
-      <c r="B121" s="2"/>
+      <c r="B121" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>394</v>
       </c>
       <c r="F121" s="2"/>
-      <c r="G121" s="2" t="s">
+      <c r="G121" s="2"/>
+      <c r="H121" s="2"/>
+      <c r="I121" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="H121" s="2"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J121" s="2"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" t="b">
         <v>1</v>
       </c>
-      <c r="B122" s="2"/>
+      <c r="B122" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>395</v>
       </c>
       <c r="F122" s="2"/>
-      <c r="G122" s="2" t="s">
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+      <c r="I122" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="H122" s="2"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J122" s="2"/>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" t="b">
         <v>1</v>
       </c>
-      <c r="B123" s="2"/>
+      <c r="B123" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>396</v>
       </c>
       <c r="F123" s="2"/>
-      <c r="G123" s="2" t="s">
+      <c r="G123" s="2"/>
+      <c r="H123" s="2"/>
+      <c r="I123" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="H123" s="2"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J123" s="2"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" t="b">
         <v>1</v>
       </c>
-      <c r="B124" s="2"/>
+      <c r="B124" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>277</v>
       </c>
       <c r="F124" s="2"/>
-      <c r="G124" s="2" t="s">
+      <c r="G124" s="2"/>
+      <c r="H124" s="2"/>
+      <c r="I124" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="H124" s="2"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J124" s="2"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" t="b">
         <v>1</v>
       </c>
-      <c r="B125" s="2"/>
+      <c r="B125" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>278</v>
       </c>
       <c r="F125" s="2"/>
-      <c r="G125" s="2" t="s">
+      <c r="G125" s="2"/>
+      <c r="H125" s="2"/>
+      <c r="I125" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="H125" s="2"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J125" s="2"/>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" t="b">
         <v>1</v>
       </c>
-      <c r="B126" s="2"/>
+      <c r="B126" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>279</v>
       </c>
       <c r="F126" s="2"/>
-      <c r="G126" s="2" t="s">
+      <c r="G126" s="2"/>
+      <c r="H126" s="2"/>
+      <c r="I126" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="H126" s="2"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J126" s="2"/>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" t="b">
         <v>1</v>
       </c>
-      <c r="B127" s="2"/>
+      <c r="B127" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>397</v>
       </c>
       <c r="F127" s="2"/>
-      <c r="G127" s="2" t="s">
+      <c r="G127" s="2"/>
+      <c r="H127" s="2"/>
+      <c r="I127" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="H127" s="2"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J127" s="2"/>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" t="b">
         <v>1</v>
       </c>
-      <c r="B128" s="2"/>
+      <c r="B128" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>398</v>
       </c>
       <c r="F128" s="2"/>
-      <c r="G128" s="2" t="s">
+      <c r="G128" s="2"/>
+      <c r="H128" s="2"/>
+      <c r="I128" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="H128" s="2"/>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J128" s="2"/>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" t="b">
         <v>1</v>
       </c>
-      <c r="B129" s="2"/>
+      <c r="B129" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>399</v>
       </c>
       <c r="F129" s="2"/>
-      <c r="G129" s="2" t="s">
+      <c r="G129" s="2"/>
+      <c r="H129" s="2"/>
+      <c r="I129" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="H129" s="2"/>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J129" s="2"/>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" t="b">
         <v>1</v>
       </c>
-      <c r="B130" s="2"/>
+      <c r="B130" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C130" s="2"/>
       <c r="D130" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>400</v>
       </c>
       <c r="F130" s="2"/>
-      <c r="G130" s="2" t="s">
+      <c r="G130" s="2"/>
+      <c r="H130" s="2"/>
+      <c r="I130" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="H130" s="2"/>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J130" s="2"/>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" t="b">
         <v>1</v>
       </c>
-      <c r="B131" s="2"/>
+      <c r="B131" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C131" s="2"/>
       <c r="D131" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>283</v>
       </c>
       <c r="F131" s="2"/>
-      <c r="G131" s="2" t="s">
+      <c r="G131" s="2"/>
+      <c r="H131" s="2"/>
+      <c r="I131" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="H131" s="2"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J131" s="2"/>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" t="b">
         <v>1</v>
       </c>
-      <c r="B132" s="2"/>
+      <c r="B132" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>284</v>
       </c>
       <c r="F132" s="2"/>
-      <c r="G132" s="2" t="s">
+      <c r="G132" s="2"/>
+      <c r="H132" s="2"/>
+      <c r="I132" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="H132" s="2"/>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J132" s="2"/>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" t="b">
         <v>1</v>
       </c>
-      <c r="B133" s="2"/>
+      <c r="B133" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>401</v>
       </c>
       <c r="F133" s="2"/>
-      <c r="G133" s="2" t="s">
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+      <c r="I133" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="H133" s="2"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J133" s="2"/>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" t="b">
         <v>1</v>
       </c>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>271</v>
       </c>
       <c r="F134" s="2"/>
-      <c r="G134" s="2" t="s">
+      <c r="G134" s="2"/>
+      <c r="H134" s="2"/>
+      <c r="I134" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="H134" s="2" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J134" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" t="b">
         <v>1</v>
       </c>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>272</v>
       </c>
       <c r="F135" s="2"/>
-      <c r="G135" s="2" t="s">
+      <c r="G135" s="2"/>
+      <c r="H135" s="2"/>
+      <c r="I135" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="H135" s="2"/>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J135" s="2"/>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" t="b">
         <v>1</v>
       </c>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>273</v>
       </c>
       <c r="F136" s="2"/>
-      <c r="G136" s="2" t="s">
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+      <c r="I136" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="H136" s="2"/>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J136" s="2"/>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" t="b">
         <v>1</v>
       </c>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>274</v>
       </c>
       <c r="F137" s="2"/>
-      <c r="G137" s="2" t="s">
+      <c r="G137" s="2"/>
+      <c r="H137" s="2"/>
+      <c r="I137" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="H137" s="2"/>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J137" s="2"/>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" t="b">
         <v>1</v>
       </c>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>275</v>
       </c>
       <c r="F138" s="2"/>
-      <c r="G138" s="2" t="s">
+      <c r="G138" s="2"/>
+      <c r="H138" s="2"/>
+      <c r="I138" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="H138" s="2"/>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J138" s="2"/>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" t="b">
         <v>1</v>
       </c>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>276</v>
       </c>
       <c r="F139" s="2"/>
-      <c r="G139" s="2" t="s">
+      <c r="G139" s="2"/>
+      <c r="H139" s="2"/>
+      <c r="I139" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="H139" s="2"/>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J139" s="2"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" t="b">
         <v>1</v>
       </c>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>277</v>
       </c>
       <c r="F140" s="2"/>
-      <c r="G140" s="2" t="s">
+      <c r="G140" s="2"/>
+      <c r="H140" s="2"/>
+      <c r="I140" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="H140" s="2"/>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J140" s="2"/>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" t="b">
         <v>1</v>
       </c>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>278</v>
       </c>
       <c r="F141" s="2"/>
-      <c r="G141" s="2" t="s">
+      <c r="G141" s="2"/>
+      <c r="H141" s="2"/>
+      <c r="I141" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="H141" s="2"/>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J141" s="2"/>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" t="b">
         <v>1</v>
       </c>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>279</v>
       </c>
       <c r="F142" s="2"/>
-      <c r="G142" s="2" t="s">
+      <c r="G142" s="2"/>
+      <c r="H142" s="2"/>
+      <c r="I142" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="H142" s="2"/>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J142" s="2"/>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" t="b">
         <v>1</v>
       </c>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>280</v>
       </c>
       <c r="F143" s="2"/>
-      <c r="G143" s="2" t="s">
+      <c r="G143" s="2"/>
+      <c r="H143" s="2"/>
+      <c r="I143" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="H143" s="2"/>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J143" s="2"/>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" t="b">
         <v>1</v>
       </c>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>281</v>
       </c>
       <c r="F144" s="2"/>
-      <c r="G144" s="2" t="s">
+      <c r="G144" s="2"/>
+      <c r="H144" s="2"/>
+      <c r="I144" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="H144" s="2"/>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J144" s="2"/>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" t="b">
         <v>1</v>
       </c>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>282</v>
       </c>
       <c r="F145" s="2"/>
-      <c r="G145" s="2" t="s">
+      <c r="G145" s="2"/>
+      <c r="H145" s="2"/>
+      <c r="I145" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="H145" s="2"/>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J145" s="2"/>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" t="b">
         <v>1</v>
       </c>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>283</v>
       </c>
       <c r="F146" s="2"/>
-      <c r="G146" s="2" t="s">
+      <c r="G146" s="2"/>
+      <c r="H146" s="2"/>
+      <c r="I146" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="H146" s="2"/>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J146" s="2"/>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" t="b">
         <v>1</v>
       </c>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>284</v>
       </c>
       <c r="F147" s="2"/>
-      <c r="G147" s="2" t="s">
+      <c r="G147" s="2"/>
+      <c r="H147" s="2"/>
+      <c r="I147" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="H147" s="2"/>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J147" s="2"/>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" t="b">
         <v>1</v>
       </c>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>285</v>
       </c>
       <c r="F148" s="2"/>
-      <c r="G148" s="2" t="s">
+      <c r="G148" s="2"/>
+      <c r="H148" s="2"/>
+      <c r="I148" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="H148" s="2"/>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J148" s="2"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" t="b">
         <v>1</v>
       </c>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
       <c r="D149" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>286</v>
       </c>
       <c r="F149" s="2"/>
-      <c r="G149" s="2" t="s">
+      <c r="G149" s="2"/>
+      <c r="H149" s="2"/>
+      <c r="I149" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="H149" s="2"/>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J149" s="2"/>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" t="b">
         <v>1</v>
       </c>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>287</v>
       </c>
       <c r="F150" s="2"/>
-      <c r="G150" s="2" t="s">
+      <c r="G150" s="2"/>
+      <c r="H150" s="2"/>
+      <c r="I150" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="H150" s="2"/>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J150" s="2"/>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" t="b">
         <v>1</v>
       </c>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>288</v>
       </c>
       <c r="F151" s="2"/>
-      <c r="G151" s="2" t="s">
+      <c r="G151" s="2"/>
+      <c r="H151" s="2"/>
+      <c r="I151" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="H151" s="2"/>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J151" s="2"/>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" t="b">
         <v>1</v>
       </c>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>289</v>
       </c>
       <c r="F152" s="2"/>
-      <c r="G152" s="2" t="s">
+      <c r="G152" s="2"/>
+      <c r="H152" s="2"/>
+      <c r="I152" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="H152" s="2"/>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J152" s="2"/>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" t="b">
         <v>1</v>
       </c>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>290</v>
       </c>
       <c r="F153" s="2"/>
-      <c r="G153" s="2" t="s">
+      <c r="G153" s="2"/>
+      <c r="H153" s="2"/>
+      <c r="I153" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="H153" s="2"/>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J153" s="2"/>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" t="b">
         <v>1</v>
       </c>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>409</v>
       </c>
       <c r="F154" s="2"/>
-      <c r="G154" s="2" t="s">
+      <c r="G154" s="2"/>
+      <c r="H154" s="2"/>
+      <c r="I154" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="H154" s="2" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J154" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" t="b">
         <v>1</v>
       </c>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>410</v>
       </c>
       <c r="F155" s="2"/>
-      <c r="G155" s="2" t="s">
+      <c r="G155" s="2"/>
+      <c r="H155" s="2"/>
+      <c r="I155" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="H155" s="2"/>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J155" s="2"/>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156" t="b">
         <v>1</v>
       </c>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>411</v>
       </c>
       <c r="F156" s="2"/>
-      <c r="G156" s="2" t="s">
+      <c r="G156" s="2"/>
+      <c r="H156" s="2"/>
+      <c r="I156" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="H156" s="2"/>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J156" s="2"/>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" t="b">
         <v>1</v>
       </c>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>412</v>
       </c>
       <c r="F157" s="2"/>
-      <c r="G157" s="2" t="s">
+      <c r="G157" s="2"/>
+      <c r="H157" s="2"/>
+      <c r="I157" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="H157" s="2"/>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J157" s="2"/>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" t="b">
         <v>1</v>
       </c>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>413</v>
       </c>
       <c r="F158" s="2"/>
-      <c r="G158" s="2" t="s">
+      <c r="G158" s="2"/>
+      <c r="H158" s="2"/>
+      <c r="I158" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="H158" s="2"/>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J158" s="2"/>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" t="b">
         <v>1</v>
       </c>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
       <c r="D159" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>414</v>
       </c>
       <c r="F159" s="2"/>
-      <c r="G159" s="2" t="s">
+      <c r="G159" s="2"/>
+      <c r="H159" s="2"/>
+      <c r="I159" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="H159" s="2"/>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J159" s="2"/>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160" t="b">
         <v>1</v>
       </c>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>149</v>
       </c>
       <c r="F160" s="2"/>
-      <c r="G160" s="2" t="s">
+      <c r="G160" s="2"/>
+      <c r="H160" s="2"/>
+      <c r="I160" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="H160" s="2"/>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J160" s="2"/>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" t="b">
         <v>1</v>
       </c>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>415</v>
       </c>
       <c r="F161" s="2"/>
-      <c r="G161" s="2" t="s">
+      <c r="G161" s="2"/>
+      <c r="H161" s="2"/>
+      <c r="I161" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="H161" s="2" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J161" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" t="b">
         <v>1</v>
       </c>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>416</v>
       </c>
       <c r="F162" s="2"/>
-      <c r="G162" s="2" t="s">
+      <c r="G162" s="2"/>
+      <c r="H162" s="2"/>
+      <c r="I162" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="H162" s="2"/>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J162" s="2"/>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" t="b">
         <v>1</v>
       </c>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>417</v>
       </c>
       <c r="F163" s="2"/>
-      <c r="G163" s="2" t="s">
+      <c r="G163" s="2"/>
+      <c r="H163" s="2"/>
+      <c r="I163" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="H163" s="2"/>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J163" s="2"/>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" t="b">
         <v>1</v>
       </c>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>418</v>
       </c>
       <c r="F164" s="2"/>
-      <c r="G164" s="2" t="s">
+      <c r="G164" s="2"/>
+      <c r="H164" s="2"/>
+      <c r="I164" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="H164" s="2"/>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J164" s="2"/>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" t="b">
         <v>1</v>
       </c>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>149</v>
       </c>
       <c r="F165" s="2"/>
-      <c r="G165" s="2" t="s">
+      <c r="G165" s="2"/>
+      <c r="H165" s="2"/>
+      <c r="I165" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="H165" s="2"/>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J165" s="2"/>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" t="b">
         <v>1</v>
       </c>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>409</v>
       </c>
       <c r="F166" s="2"/>
-      <c r="G166" s="2" t="s">
+      <c r="G166" s="2"/>
+      <c r="H166" s="2"/>
+      <c r="I166" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="H166" s="2" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J166" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" t="b">
         <v>1</v>
       </c>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>410</v>
       </c>
       <c r="F167" s="2"/>
-      <c r="G167" s="2" t="s">
+      <c r="G167" s="2"/>
+      <c r="H167" s="2"/>
+      <c r="I167" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="H167" s="2"/>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J167" s="2"/>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" t="b">
         <v>1</v>
       </c>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>411</v>
       </c>
       <c r="F168" s="2"/>
-      <c r="G168" s="2" t="s">
+      <c r="G168" s="2"/>
+      <c r="H168" s="2"/>
+      <c r="I168" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="H168" s="2"/>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J168" s="2"/>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" t="b">
         <v>1</v>
       </c>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>412</v>
       </c>
       <c r="F169" s="2"/>
-      <c r="G169" s="2" t="s">
+      <c r="G169" s="2"/>
+      <c r="H169" s="2"/>
+      <c r="I169" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="H169" s="2"/>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J169" s="2"/>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" t="b">
         <v>1</v>
       </c>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>413</v>
       </c>
       <c r="F170" s="2"/>
-      <c r="G170" s="2" t="s">
+      <c r="G170" s="2"/>
+      <c r="H170" s="2"/>
+      <c r="I170" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="H170" s="2"/>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J170" s="2"/>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171" t="b">
         <v>1</v>
       </c>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>419</v>
       </c>
       <c r="F171" s="2"/>
-      <c r="G171" s="2" t="s">
+      <c r="G171" s="2"/>
+      <c r="H171" s="2"/>
+      <c r="I171" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="H171" s="2"/>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J171" s="2"/>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172" t="b">
         <v>1</v>
       </c>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>416</v>
       </c>
       <c r="F172" s="2"/>
-      <c r="G172" s="2" t="s">
+      <c r="G172" s="2"/>
+      <c r="H172" s="2"/>
+      <c r="I172" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="H172" s="2"/>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J172" s="2"/>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A173" t="b">
         <v>1</v>
       </c>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>417</v>
       </c>
       <c r="F173" s="2"/>
-      <c r="G173" s="2" t="s">
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
+      <c r="I173" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="H173" s="2"/>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J173" s="2"/>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174" t="b">
         <v>1</v>
       </c>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>418</v>
       </c>
       <c r="F174" s="2"/>
-      <c r="G174" s="2" t="s">
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+      <c r="I174" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="H174" s="2"/>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J174" s="2"/>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175" t="b">
         <v>1</v>
       </c>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
       <c r="D175" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>420</v>
       </c>
       <c r="F175" s="2"/>
-      <c r="G175" s="2" t="s">
+      <c r="G175" s="2"/>
+      <c r="H175" s="2"/>
+      <c r="I175" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="H175" s="2"/>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J175" s="2"/>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A176" t="b">
         <v>1</v>
       </c>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
       <c r="D176" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>149</v>
       </c>
       <c r="F176" s="2"/>
-      <c r="G176" s="2" t="s">
+      <c r="G176" s="2"/>
+      <c r="H176" s="2"/>
+      <c r="I176" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="H176" s="2"/>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J176" s="2"/>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A177" t="b">
         <v>1</v>
       </c>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>423</v>
       </c>
       <c r="F177" s="2"/>
-      <c r="G177" s="2" t="s">
+      <c r="G177" s="2"/>
+      <c r="H177" s="2"/>
+      <c r="I177" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="H177" s="2" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J177" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A178" t="b">
         <v>1</v>
       </c>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>424</v>
       </c>
       <c r="F178" s="2"/>
-      <c r="G178" s="2" t="s">
+      <c r="G178" s="2"/>
+      <c r="H178" s="2"/>
+      <c r="I178" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="H178" s="2"/>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J178" s="2"/>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A179" t="b">
         <v>1</v>
       </c>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>425</v>
       </c>
       <c r="F179" s="2"/>
-      <c r="G179" s="2" t="s">
+      <c r="G179" s="2"/>
+      <c r="H179" s="2"/>
+      <c r="I179" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="H179" s="2"/>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J179" s="2"/>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A180" t="b">
         <v>1</v>
       </c>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>426</v>
       </c>
       <c r="F180" s="2"/>
-      <c r="G180" s="2" t="s">
+      <c r="G180" s="2"/>
+      <c r="H180" s="2"/>
+      <c r="I180" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="H180" s="2"/>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J180" s="2"/>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A181" t="b">
         <v>1</v>
       </c>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>427</v>
       </c>
       <c r="F181" s="2"/>
-      <c r="G181" s="2" t="s">
+      <c r="G181" s="2"/>
+      <c r="H181" s="2"/>
+      <c r="I181" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="H181" s="2"/>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J181" s="2"/>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A182" t="b">
         <v>1</v>
       </c>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>428</v>
       </c>
       <c r="F182" s="2"/>
-      <c r="G182" s="2" t="s">
+      <c r="G182" s="2"/>
+      <c r="H182" s="2"/>
+      <c r="I182" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="H182" s="2"/>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J182" s="2"/>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A183" t="b">
         <v>1</v>
       </c>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>429</v>
       </c>
       <c r="F183" s="2"/>
-      <c r="G183" s="2" t="s">
+      <c r="G183" s="2"/>
+      <c r="H183" s="2"/>
+      <c r="I183" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="H183" s="2"/>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J183" s="2"/>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A184" t="b">
         <v>1</v>
       </c>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>430</v>
       </c>
       <c r="F184" s="2"/>
-      <c r="G184" s="2" t="s">
+      <c r="G184" s="2"/>
+      <c r="H184" s="2"/>
+      <c r="I184" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="H184" s="2"/>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J184" s="2"/>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A185" t="b">
         <v>1</v>
       </c>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>431</v>
       </c>
       <c r="F185" s="2"/>
-      <c r="G185" s="2" t="s">
+      <c r="G185" s="2"/>
+      <c r="H185" s="2"/>
+      <c r="I185" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="H185" s="2"/>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J185" s="2"/>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A186" t="b">
         <v>1</v>
       </c>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>432</v>
       </c>
       <c r="F186" s="2"/>
-      <c r="G186" s="2" t="s">
+      <c r="G186" s="2"/>
+      <c r="H186" s="2"/>
+      <c r="I186" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="H186" s="2"/>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J186" s="2"/>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A187" t="b">
         <v>1</v>
       </c>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
       <c r="D187" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>433</v>
       </c>
       <c r="F187" s="2"/>
-      <c r="G187" s="2" t="s">
+      <c r="G187" s="2"/>
+      <c r="H187" s="2"/>
+      <c r="I187" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="H187" s="2"/>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J187" s="2"/>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A188" t="b">
         <v>1</v>
       </c>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
       <c r="D188" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>434</v>
       </c>
       <c r="F188" s="2"/>
-      <c r="G188" s="2" t="s">
+      <c r="G188" s="2"/>
+      <c r="H188" s="2"/>
+      <c r="I188" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="H188" s="2"/>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J188" s="2"/>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A189" t="b">
         <v>1</v>
       </c>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>423</v>
       </c>
       <c r="F189" s="2"/>
-      <c r="G189" s="2" t="s">
+      <c r="G189" s="2"/>
+      <c r="H189" s="2"/>
+      <c r="I189" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="H189" s="2" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J189" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A190" t="b">
         <v>1</v>
       </c>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
       <c r="D190" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>424</v>
       </c>
       <c r="F190" s="2"/>
-      <c r="G190" s="2" t="s">
+      <c r="G190" s="2"/>
+      <c r="H190" s="2"/>
+      <c r="I190" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="H190" s="2"/>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J190" s="2"/>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A191" t="b">
         <v>1</v>
       </c>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
       <c r="D191" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>425</v>
       </c>
       <c r="F191" s="2"/>
-      <c r="G191" s="2" t="s">
+      <c r="G191" s="2"/>
+      <c r="H191" s="2"/>
+      <c r="I191" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="H191" s="2"/>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J191" s="2"/>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A192" t="b">
         <v>1</v>
       </c>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>426</v>
       </c>
       <c r="F192" s="2"/>
-      <c r="G192" s="2" t="s">
+      <c r="G192" s="2"/>
+      <c r="H192" s="2"/>
+      <c r="I192" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="H192" s="2"/>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J192" s="2"/>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A193" t="b">
         <v>1</v>
       </c>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>427</v>
       </c>
       <c r="F193" s="2"/>
-      <c r="G193" s="2" t="s">
+      <c r="G193" s="2"/>
+      <c r="H193" s="2"/>
+      <c r="I193" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="H193" s="2"/>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J193" s="2"/>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A194" t="b">
         <v>1</v>
       </c>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
       <c r="D194" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>428</v>
       </c>
       <c r="F194" s="2"/>
-      <c r="G194" s="2" t="s">
+      <c r="G194" s="2"/>
+      <c r="H194" s="2"/>
+      <c r="I194" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="H194" s="2"/>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J194" s="2"/>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A195" t="b">
         <v>1</v>
       </c>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
       <c r="D195" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>429</v>
       </c>
       <c r="F195" s="2"/>
-      <c r="G195" s="2" t="s">
+      <c r="G195" s="2"/>
+      <c r="H195" s="2"/>
+      <c r="I195" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="H195" s="2"/>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J195" s="2"/>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A196" t="b">
         <v>1</v>
       </c>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
       <c r="D196" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>430</v>
       </c>
       <c r="F196" s="2"/>
-      <c r="G196" s="2" t="s">
+      <c r="G196" s="2"/>
+      <c r="H196" s="2"/>
+      <c r="I196" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="H196" s="2"/>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J196" s="2"/>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A197" t="b">
         <v>1</v>
       </c>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
       <c r="D197" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>431</v>
       </c>
       <c r="F197" s="2"/>
-      <c r="G197" s="2" t="s">
+      <c r="G197" s="2"/>
+      <c r="H197" s="2"/>
+      <c r="I197" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="H197" s="2"/>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J197" s="2"/>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A198" t="b">
         <v>1</v>
       </c>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>432</v>
       </c>
       <c r="F198" s="2"/>
-      <c r="G198" s="2" t="s">
+      <c r="G198" s="2"/>
+      <c r="H198" s="2"/>
+      <c r="I198" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="H198" s="2"/>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J198" s="2"/>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A199" t="b">
         <v>1</v>
       </c>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>433</v>
       </c>
       <c r="F199" s="2"/>
-      <c r="G199" s="2" t="s">
+      <c r="G199" s="2"/>
+      <c r="H199" s="2"/>
+      <c r="I199" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="H199" s="2"/>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J199" s="2"/>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A200" t="b">
         <v>1</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>434</v>
       </c>
       <c r="F200" s="2"/>
-      <c r="G200" s="2" t="s">
+      <c r="G200" s="2"/>
+      <c r="H200" s="2"/>
+      <c r="I200" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="H200" s="2"/>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J200" s="2"/>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A201" t="b">
         <v>1</v>
       </c>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
       <c r="D201" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>149</v>
       </c>
       <c r="F201" s="2"/>
-      <c r="G201" s="2" t="s">
+      <c r="G201" s="2"/>
+      <c r="H201" s="2"/>
+      <c r="I201" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="H201" s="2" t="s">
-        <v>745</v>
-      </c>
+      <c r="J201" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F473A2CA-C820-0046-94BE-355E30642FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1816F2-5BAC-5D45-A7BD-F675F4EBA2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="39840" windowHeight="19600" activeTab="2" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2590" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2507" uniqueCount="766">
   <si>
     <t>Reporter</t>
   </si>
@@ -2156,9 +2156,6 @@
     <t>customData</t>
   </si>
   <si>
-    <t>---</t>
-  </si>
-  <si>
     <t>collPer</t>
   </si>
   <si>
@@ -2208,12 +2205,6 @@
   </si>
   <si>
     <t>targetEnum</t>
-  </si>
-  <si>
-    <t>shedSet</t>
-  </si>
-  <si>
-    <t>other?</t>
   </si>
   <si>
     <t>Same targets: reporting_jurisdiction, wwtp_jurisdiction</t>
@@ -2478,7 +2469,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -2523,11 +2514,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2560,13 +2588,16 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13838,8 +13869,8 @@
     <col min="12" max="12" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" s="24" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
         <v>700</v>
       </c>
       <c r="B1" s="8" t="s">
@@ -13896,7 +13927,7 @@
         <v>121</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -13904,7 +13935,7 @@
         <v>490</v>
       </c>
       <c r="L2" s="19" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -13930,7 +13961,7 @@
         <v>82</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -13959,7 +13990,7 @@
         <v>127</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -13990,7 +14021,7 @@
         <v>84</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -14019,7 +14050,7 @@
         <v>85</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -14121,8 +14152,8 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="23" t="s">
-        <v>757</v>
+      <c r="L10" s="22" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -14136,7 +14167,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="24"/>
+      <c r="L11" s="23"/>
     </row>
     <row r="12" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="b">
@@ -14643,7 +14674,7 @@
         <v>123</v>
       </c>
       <c r="L29" s="19" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
@@ -14696,7 +14727,7 @@
         <v>122</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -14723,7 +14754,7 @@
         <v>121</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
@@ -14739,19 +14770,17 @@
       <c r="C33" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>703</v>
-      </c>
+      <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
         <v>124</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H33" s="6"/>
-      <c r="I33" s="21" t="s">
-        <v>739</v>
+      <c r="I33" s="20" t="s">
+        <v>736</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
@@ -14766,9 +14795,7 @@
       <c r="C34" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="D34" s="22" t="s">
-        <v>703</v>
-      </c>
+      <c r="D34" s="21"/>
       <c r="E34" s="3"/>
       <c r="F34" s="2" t="s">
         <v>124</v>
@@ -14777,8 +14804,8 @@
         <v>125</v>
       </c>
       <c r="H34" s="2"/>
-      <c r="I34" s="21" t="s">
-        <v>740</v>
+      <c r="I34" s="20" t="s">
+        <v>737</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
@@ -14806,7 +14833,7 @@
         <v>126</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
@@ -15089,13 +15116,13 @@
         <v>160</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="19" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
@@ -15119,7 +15146,7 @@
         <v>160</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
@@ -15127,7 +15154,7 @@
         <v>596</v>
       </c>
       <c r="L47" s="19" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
@@ -15151,13 +15178,13 @@
         <v>160</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
-      <c r="L48" s="23" t="s">
-        <v>759</v>
+      <c r="L48" s="22" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
@@ -15171,7 +15198,7 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
-      <c r="L49" s="23"/>
+      <c r="L49" s="22"/>
     </row>
     <row r="50" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="b">
@@ -15183,7 +15210,7 @@
       <c r="C50" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="D50" s="22" t="s">
+      <c r="D50" s="21" t="s">
         <v>49</v>
       </c>
       <c r="E50" s="2" t="s">
@@ -15295,7 +15322,7 @@
         <v>146</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
@@ -15324,7 +15351,7 @@
         <v>150</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -15373,7 +15400,7 @@
         <v>157</v>
       </c>
       <c r="L57" s="19" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
@@ -15460,9 +15487,7 @@
       <c r="C61" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>61</v>
-      </c>
+      <c r="D61" s="2"/>
       <c r="E61" s="2" t="s">
         <v>147</v>
       </c>
@@ -15474,7 +15499,7 @@
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="1" t="s">
@@ -15683,7 +15708,7 @@
         <v>169</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
@@ -15905,7 +15930,7 @@
         <v>621</v>
       </c>
       <c r="L78" s="19" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -16213,7 +16238,7 @@
         <v>486</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
@@ -16240,13 +16265,13 @@
         <v>488</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
-      <c r="L91" s="23" t="s">
-        <v>762</v>
+      <c r="L91" s="22" t="s">
+        <v>759</v>
       </c>
     </row>
   </sheetData>
@@ -16275,11 +16300,11 @@
     <col min="14" max="14" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14" s="24" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
         <v>700</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>695</v>
       </c>
       <c r="C1" s="9" t="s">
@@ -16288,14 +16313,14 @@
       <c r="D1" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>698</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H1" s="11" t="s">
         <v>167</v>
@@ -16565,7 +16590,7 @@
         <v>665</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>177</v>
@@ -16632,7 +16657,7 @@
         <v>435</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>80</v>
@@ -16839,7 +16864,7 @@
         <v>440</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>80</v>
@@ -17766,7 +17791,7 @@
         <v>459</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>80</v>
@@ -19280,7 +19305,7 @@
         <v>498</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>80</v>
@@ -19905,7 +19930,7 @@
         <v>499</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>80</v>
@@ -20279,7 +20304,7 @@
         <v>481</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>80</v>
@@ -20558,7 +20583,7 @@
         <v>520</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="L118" s="2" t="s">
         <v>80</v>
@@ -20630,7 +20655,7 @@
         <v>665</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
@@ -20664,7 +20689,7 @@
         <v>597</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="L121" s="2" t="s">
         <v>185</v>
@@ -20673,7 +20698,7 @@
         <v>171</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
@@ -20922,7 +20947,7 @@
         <v>665</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>177</v>
@@ -20943,7 +20968,7 @@
         <v>171</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
@@ -21164,7 +21189,7 @@
         <v>665</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>177</v>
@@ -21204,7 +21229,7 @@
         <v>665</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>177</v>
@@ -21244,7 +21269,7 @@
         <v>665</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>177</v>
@@ -21299,7 +21324,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC10C3F-0C27-5546-8767-E60C7CACEA9D}">
-  <dimension ref="A1:J201"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
@@ -21309,419 +21334,389 @@
     <col min="8" max="8" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:10" s="24" customFormat="1" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
         <v>700</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="25" t="s">
         <v>649</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="26" t="s">
         <v>651</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="26" t="s">
+        <v>718</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>652</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>653</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>654</v>
+      </c>
+      <c r="H1" s="26" t="s">
         <v>719</v>
       </c>
-      <c r="E1" s="20" t="s">
-        <v>652</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>653</v>
-      </c>
-      <c r="G1" s="20" t="s">
-        <v>654</v>
-      </c>
-      <c r="H1" s="20" t="s">
-        <v>720</v>
-      </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="26" t="s">
         <v>655</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="27" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E2" s="2" t="s">
-        <v>89</v>
+        <v>291</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H2" s="21"/>
       <c r="I2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J2" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>761</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E3" s="2" t="s">
-        <v>90</v>
+        <v>292</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>106</v>
+        <v>522</v>
       </c>
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E4" s="2" t="s">
-        <v>91</v>
+        <v>293</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>107</v>
+        <v>523</v>
       </c>
       <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>92</v>
+        <v>294</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>108</v>
+        <v>525</v>
       </c>
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E6" s="2" t="s">
-        <v>93</v>
+        <v>295</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>109</v>
+        <v>524</v>
       </c>
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E7" s="2" t="s">
-        <v>94</v>
+        <v>296</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>118</v>
+        <v>528</v>
       </c>
       <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E8" s="2" t="s">
-        <v>95</v>
+        <v>297</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>117</v>
+        <v>529</v>
       </c>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E9" s="2" t="s">
-        <v>96</v>
+        <v>298</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>114</v>
+        <v>526</v>
       </c>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E10" s="2" t="s">
-        <v>97</v>
+        <v>299</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>113</v>
+        <v>527</v>
       </c>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E11" s="2" t="s">
-        <v>98</v>
+        <v>300</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>112</v>
+        <v>530</v>
       </c>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E12" s="2" t="s">
-        <v>99</v>
+        <v>301</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>111</v>
+        <v>531</v>
       </c>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E13" s="2" t="s">
-        <v>100</v>
+        <v>302</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>110</v>
+        <v>302</v>
       </c>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E14" s="2" t="s">
-        <v>101</v>
+        <v>303</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>115</v>
+        <v>303</v>
       </c>
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E15" s="2" t="s">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>102</v>
+        <v>532</v>
       </c>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E16" s="2" t="s">
-        <v>103</v>
+        <v>305</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>116</v>
+        <v>305</v>
       </c>
       <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="E17" s="2" t="s">
-        <v>104</v>
+        <v>306</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="2" t="s">
-        <v>721</v>
-      </c>
+      <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>722</v>
+        <v>533</v>
       </c>
       <c r="J17" s="2"/>
     </row>
@@ -21734,20 +21729,18 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="22"/>
+      <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>764</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="b">
@@ -21758,16 +21751,16 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="J19" s="2"/>
     </row>
@@ -21780,16 +21773,16 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="J20" s="2"/>
     </row>
@@ -21802,16 +21795,16 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="J21" s="2"/>
     </row>
@@ -21824,16 +21817,16 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="J22" s="2"/>
     </row>
@@ -21846,16 +21839,16 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="J23" s="2"/>
     </row>
@@ -21868,16 +21861,16 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="J24" s="2"/>
     </row>
@@ -21890,16 +21883,16 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="J25" s="2"/>
     </row>
@@ -21912,16 +21905,16 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>527</v>
+        <v>315</v>
       </c>
       <c r="J26" s="2"/>
     </row>
@@ -21934,16 +21927,16 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>530</v>
+        <v>322</v>
       </c>
       <c r="J27" s="2"/>
     </row>
@@ -21956,16 +21949,16 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="J28" s="2"/>
     </row>
@@ -21978,16 +21971,16 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>302</v>
+        <v>370</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2" t="s">
-        <v>302</v>
+        <v>538</v>
       </c>
       <c r="J29" s="2"/>
     </row>
@@ -22000,16 +21993,16 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
-        <v>303</v>
+        <v>539</v>
       </c>
       <c r="J30" s="2"/>
     </row>
@@ -22022,16 +22015,16 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>304</v>
+        <v>346</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
-        <v>532</v>
+        <v>590</v>
       </c>
       <c r="J31" s="2"/>
     </row>
@@ -22044,16 +22037,16 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="J32" s="2"/>
     </row>
@@ -22066,16 +22059,16 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>306</v>
+        <v>368</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
-        <v>533</v>
+        <v>368</v>
       </c>
       <c r="J33" s="2"/>
     </row>
@@ -22088,16 +22081,16 @@
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="J34" s="2"/>
     </row>
@@ -22110,16 +22103,16 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>308</v>
+        <v>362</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="s">
-        <v>534</v>
+        <v>362</v>
       </c>
       <c r="J35" s="2"/>
     </row>
@@ -22132,16 +22125,16 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2" t="s">
-        <v>535</v>
+        <v>328</v>
       </c>
       <c r="J36" s="2"/>
     </row>
@@ -22154,16 +22147,16 @@
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="J37" s="2"/>
     </row>
@@ -22176,16 +22169,16 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>311</v>
+        <v>372</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
-        <v>521</v>
+        <v>567</v>
       </c>
       <c r="J38" s="2"/>
     </row>
@@ -22198,16 +22191,16 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="J39" s="2"/>
     </row>
@@ -22220,16 +22213,16 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2" t="s">
-        <v>522</v>
+        <v>568</v>
       </c>
       <c r="J40" s="2"/>
     </row>
@@ -22242,16 +22235,16 @@
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="J41" s="2"/>
     </row>
@@ -22264,16 +22257,16 @@
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>315</v>
+        <v>349</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2" t="s">
-        <v>315</v>
+        <v>543</v>
       </c>
       <c r="J42" s="2"/>
     </row>
@@ -22286,16 +22279,16 @@
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2" t="s">
-        <v>322</v>
+        <v>569</v>
       </c>
       <c r="J43" s="2"/>
     </row>
@@ -22308,16 +22301,16 @@
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="J44" s="2"/>
     </row>
@@ -22330,16 +22323,16 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="J45" s="2"/>
     </row>
@@ -22352,16 +22345,16 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
-        <v>539</v>
+        <v>324</v>
       </c>
       <c r="J46" s="2"/>
     </row>
@@ -22374,16 +22367,16 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
-        <v>590</v>
+        <v>355</v>
       </c>
       <c r="J47" s="2"/>
     </row>
@@ -22396,16 +22389,16 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J48" s="2"/>
     </row>
@@ -22418,16 +22411,16 @@
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="J49" s="2"/>
     </row>
@@ -22440,16 +22433,16 @@
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="J50" s="2"/>
     </row>
@@ -22462,16 +22455,16 @@
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>362</v>
+        <v>320</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2" t="s">
-        <v>362</v>
+        <v>320</v>
       </c>
       <c r="J51" s="2"/>
     </row>
@@ -22484,16 +22477,16 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="J52" s="2"/>
     </row>
@@ -22506,16 +22499,16 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J53" s="2"/>
     </row>
@@ -22528,16 +22521,16 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>372</v>
+        <v>329</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2" t="s">
-        <v>567</v>
+        <v>329</v>
       </c>
       <c r="J54" s="2"/>
     </row>
@@ -22550,16 +22543,16 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
-        <v>541</v>
+        <v>371</v>
       </c>
       <c r="J55" s="2"/>
     </row>
@@ -22572,16 +22565,16 @@
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">
-        <v>568</v>
+        <v>336</v>
       </c>
       <c r="J56" s="2"/>
     </row>
@@ -22594,16 +22587,16 @@
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>338</v>
+        <v>374</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2" t="s">
-        <v>542</v>
+        <v>374</v>
       </c>
       <c r="J57" s="2"/>
     </row>
@@ -22616,16 +22609,16 @@
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2" t="s">
-        <v>543</v>
+        <v>326</v>
       </c>
       <c r="J58" s="2"/>
     </row>
@@ -22638,16 +22631,16 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2" t="s">
-        <v>569</v>
+        <v>366</v>
       </c>
       <c r="J59" s="2"/>
     </row>
@@ -22660,16 +22653,16 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2" t="s">
-        <v>544</v>
+        <v>375</v>
       </c>
       <c r="J60" s="2"/>
     </row>
@@ -22682,16 +22675,16 @@
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2" t="s">
-        <v>545</v>
+        <v>348</v>
       </c>
       <c r="J61" s="2"/>
     </row>
@@ -22704,16 +22697,16 @@
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>324</v>
+        <v>361</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2" t="s">
-        <v>324</v>
+        <v>361</v>
       </c>
       <c r="J62" s="2"/>
     </row>
@@ -22726,16 +22719,16 @@
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="J63" s="2"/>
     </row>
@@ -22748,16 +22741,16 @@
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2" t="s">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="J64" s="2"/>
     </row>
@@ -22770,16 +22763,16 @@
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
       <c r="J65" s="2"/>
     </row>
@@ -22792,16 +22785,16 @@
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="J66" s="2"/>
     </row>
@@ -22814,16 +22807,16 @@
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="J67" s="2"/>
     </row>
@@ -22836,16 +22829,16 @@
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="J68" s="2"/>
     </row>
@@ -22858,16 +22851,16 @@
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="J69" s="2"/>
     </row>
@@ -22880,16 +22873,16 @@
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J70" s="2"/>
     </row>
@@ -22902,16 +22895,16 @@
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J71" s="2"/>
     </row>
@@ -22924,16 +22917,16 @@
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="J72" s="2"/>
     </row>
@@ -22946,16 +22939,16 @@
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="J73" s="2"/>
     </row>
@@ -22968,16 +22961,16 @@
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="J74" s="2"/>
     </row>
@@ -22990,16 +22983,16 @@
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="J75" s="2"/>
     </row>
@@ -23012,16 +23005,16 @@
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2" t="s">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="J76" s="2"/>
     </row>
@@ -23034,16 +23027,16 @@
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J77" s="2"/>
     </row>
@@ -23056,16 +23049,16 @@
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="J78" s="2"/>
     </row>
@@ -23078,16 +23071,16 @@
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="J79" s="2"/>
     </row>
@@ -23100,16 +23093,16 @@
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="J80" s="2"/>
     </row>
@@ -23122,16 +23115,16 @@
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J81" s="2"/>
     </row>
@@ -23144,16 +23137,16 @@
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>376</v>
+        <v>318</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2" t="s">
-        <v>376</v>
+        <v>318</v>
       </c>
       <c r="J82" s="2"/>
     </row>
@@ -23166,16 +23159,16 @@
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2" t="s">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="J83" s="2"/>
     </row>
@@ -23188,16 +23181,16 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>317</v>
+        <v>367</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2" t="s">
-        <v>317</v>
+        <v>367</v>
       </c>
       <c r="J84" s="2"/>
     </row>
@@ -23210,16 +23203,16 @@
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="J85" s="2"/>
     </row>
@@ -23232,16 +23225,16 @@
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="J86" s="2"/>
     </row>
@@ -23254,16 +23247,16 @@
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="J87" s="2"/>
     </row>
@@ -23276,16 +23269,16 @@
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2" t="s">
-        <v>356</v>
+        <v>570</v>
       </c>
       <c r="J88" s="2"/>
     </row>
@@ -23298,16 +23291,16 @@
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
       <c r="I89" s="2" t="s">
-        <v>358</v>
+        <v>571</v>
       </c>
       <c r="J89" s="2"/>
     </row>
@@ -23320,16 +23313,16 @@
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2" t="s">
-        <v>364</v>
+        <v>572</v>
       </c>
       <c r="J90" s="2"/>
     </row>
@@ -23342,16 +23335,16 @@
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>331</v>
+        <v>380</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="2" t="s">
-        <v>331</v>
+        <v>573</v>
       </c>
       <c r="J91" s="2"/>
     </row>
@@ -23364,16 +23357,16 @@
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>337</v>
+        <v>381</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2" t="s">
-        <v>337</v>
+        <v>574</v>
       </c>
       <c r="J92" s="2"/>
     </row>
@@ -23386,16 +23379,16 @@
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2" t="s">
-        <v>351</v>
+        <v>575</v>
       </c>
       <c r="J93" s="2"/>
     </row>
@@ -23408,16 +23401,16 @@
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2" t="s">
-        <v>352</v>
+        <v>576</v>
       </c>
       <c r="J94" s="2"/>
     </row>
@@ -23430,16 +23423,16 @@
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>353</v>
+        <v>384</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2" t="s">
-        <v>353</v>
+        <v>577</v>
       </c>
       <c r="J95" s="2"/>
     </row>
@@ -23452,16 +23445,16 @@
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2" t="s">
-        <v>354</v>
+        <v>578</v>
       </c>
       <c r="J96" s="2"/>
     </row>
@@ -23474,16 +23467,16 @@
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>323</v>
+        <v>386</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2" t="s">
-        <v>323</v>
+        <v>386</v>
       </c>
       <c r="J97" s="2"/>
     </row>
@@ -23496,16 +23489,16 @@
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>318</v>
+        <v>387</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2" t="s">
-        <v>318</v>
+        <v>387</v>
       </c>
       <c r="J98" s="2"/>
     </row>
@@ -23518,16 +23511,16 @@
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="2" t="s">
-        <v>360</v>
+        <v>580</v>
       </c>
       <c r="J99" s="2"/>
     </row>
@@ -23540,16 +23533,16 @@
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="J100" s="2"/>
     </row>
@@ -23562,16 +23555,16 @@
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>319</v>
+        <v>390</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2" t="s">
-        <v>319</v>
+        <v>579</v>
       </c>
       <c r="J101" s="2"/>
     </row>
@@ -23584,16 +23577,16 @@
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>334</v>
+        <v>391</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
       <c r="I102" s="2" t="s">
-        <v>334</v>
+        <v>391</v>
       </c>
       <c r="J102" s="2"/>
     </row>
@@ -23606,16 +23599,16 @@
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="2" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="J103" s="2"/>
     </row>
@@ -23628,16 +23621,16 @@
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
       <c r="I104" s="2" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="J104" s="2"/>
     </row>
@@ -23650,16 +23643,16 @@
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2" t="s">
-        <v>571</v>
+        <v>394</v>
       </c>
       <c r="J105" s="2"/>
     </row>
@@ -23672,16 +23665,16 @@
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
       <c r="I106" s="2" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="J106" s="2"/>
     </row>
@@ -23694,16 +23687,16 @@
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
       <c r="I107" s="2" t="s">
-        <v>573</v>
+        <v>396</v>
       </c>
       <c r="J107" s="2"/>
     </row>
@@ -23716,16 +23709,16 @@
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>381</v>
+        <v>277</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
       <c r="I108" s="2" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="J108" s="2"/>
     </row>
@@ -23738,16 +23731,16 @@
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>382</v>
+        <v>278</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
       <c r="I109" s="2" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="J109" s="2"/>
     </row>
@@ -23760,16 +23753,16 @@
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>383</v>
+        <v>279</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
       <c r="I110" s="2" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="J110" s="2"/>
     </row>
@@ -23782,16 +23775,16 @@
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="2" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="J111" s="2"/>
     </row>
@@ -23804,16 +23797,16 @@
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="J112" s="2"/>
     </row>
@@ -23826,16 +23819,16 @@
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2" t="s">
-        <v>386</v>
+        <v>589</v>
       </c>
       <c r="J113" s="2"/>
     </row>
@@ -23848,16 +23841,16 @@
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2" t="s">
-        <v>387</v>
+        <v>588</v>
       </c>
       <c r="J114" s="2"/>
     </row>
@@ -23870,16 +23863,16 @@
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>388</v>
+        <v>283</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="J115" s="2"/>
     </row>
@@ -23892,16 +23885,16 @@
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>389</v>
+        <v>284</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
       <c r="I116" s="2" t="s">
-        <v>389</v>
+        <v>593</v>
       </c>
       <c r="J116" s="2"/>
     </row>
@@ -23914,16 +23907,16 @@
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
       <c r="I117" s="2" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="J117" s="2"/>
     </row>
@@ -23931,43 +23924,41 @@
       <c r="A118" t="b">
         <v>1</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>391</v>
+        <v>271</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
       <c r="I118" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="J118" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>760</v>
+      </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" t="b">
         <v>1</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>392</v>
+        <v>272</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
       <c r="I119" s="2" t="s">
-        <v>392</v>
+        <v>552</v>
       </c>
       <c r="J119" s="2"/>
     </row>
@@ -23975,21 +23966,19 @@
       <c r="A120" t="b">
         <v>1</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>393</v>
+        <v>273</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
       <c r="I120" s="2" t="s">
-        <v>582</v>
+        <v>553</v>
       </c>
       <c r="J120" s="2"/>
     </row>
@@ -23997,21 +23986,19 @@
       <c r="A121" t="b">
         <v>1</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>394</v>
+        <v>274</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
       <c r="I121" s="2" t="s">
-        <v>394</v>
+        <v>554</v>
       </c>
       <c r="J121" s="2"/>
     </row>
@@ -24019,21 +24006,19 @@
       <c r="A122" t="b">
         <v>1</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>395</v>
+        <v>275</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
       <c r="I122" s="2" t="s">
-        <v>581</v>
+        <v>555</v>
       </c>
       <c r="J122" s="2"/>
     </row>
@@ -24041,21 +24026,19 @@
       <c r="A123" t="b">
         <v>1</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>396</v>
+        <v>276</v>
       </c>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
       <c r="I123" s="2" t="s">
-        <v>396</v>
+        <v>556</v>
       </c>
       <c r="J123" s="2"/>
     </row>
@@ -24063,12 +24046,10 @@
       <c r="A124" t="b">
         <v>1</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>277</v>
@@ -24077,7 +24058,7 @@
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
       <c r="I124" s="2" t="s">
-        <v>583</v>
+        <v>557</v>
       </c>
       <c r="J124" s="2"/>
     </row>
@@ -24085,12 +24066,10 @@
       <c r="A125" t="b">
         <v>1</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>278</v>
@@ -24099,7 +24078,7 @@
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
       <c r="I125" s="2" t="s">
-        <v>584</v>
+        <v>558</v>
       </c>
       <c r="J125" s="2"/>
     </row>
@@ -24107,12 +24086,10 @@
       <c r="A126" t="b">
         <v>1</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>279</v>
@@ -24121,7 +24098,7 @@
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
       <c r="I126" s="2" t="s">
-        <v>585</v>
+        <v>559</v>
       </c>
       <c r="J126" s="2"/>
     </row>
@@ -24129,21 +24106,19 @@
       <c r="A127" t="b">
         <v>1</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>397</v>
+        <v>280</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
       <c r="I127" s="2" t="s">
-        <v>586</v>
+        <v>549</v>
       </c>
       <c r="J127" s="2"/>
     </row>
@@ -24151,21 +24126,19 @@
       <c r="A128" t="b">
         <v>1</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>398</v>
+        <v>281</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
       <c r="I128" s="2" t="s">
-        <v>587</v>
+        <v>550</v>
       </c>
       <c r="J128" s="2"/>
     </row>
@@ -24173,21 +24146,19 @@
       <c r="A129" t="b">
         <v>1</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>399</v>
+        <v>282</v>
       </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
       <c r="I129" s="2" t="s">
-        <v>589</v>
+        <v>566</v>
       </c>
       <c r="J129" s="2"/>
     </row>
@@ -24195,21 +24166,19 @@
       <c r="A130" t="b">
         <v>1</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>400</v>
+        <v>283</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
       <c r="I130" s="2" t="s">
-        <v>588</v>
+        <v>560</v>
       </c>
       <c r="J130" s="2"/>
     </row>
@@ -24217,21 +24186,19 @@
       <c r="A131" t="b">
         <v>1</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
       <c r="I131" s="2" t="s">
-        <v>592</v>
+        <v>551</v>
       </c>
       <c r="J131" s="2"/>
     </row>
@@ -24239,21 +24206,19 @@
       <c r="A132" t="b">
         <v>1</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B132" s="2"/>
       <c r="C132" s="2"/>
       <c r="D132" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
       <c r="I132" s="2" t="s">
-        <v>593</v>
+        <v>561</v>
       </c>
       <c r="J132" s="2"/>
     </row>
@@ -24261,21 +24226,19 @@
       <c r="A133" t="b">
         <v>1</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B133" s="2"/>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>401</v>
+        <v>286</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
       <c r="I133" s="2" t="s">
-        <v>591</v>
+        <v>562</v>
       </c>
       <c r="J133" s="2"/>
     </row>
@@ -24286,20 +24249,18 @@
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
       <c r="I134" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="J134" s="2" t="s">
-        <v>763</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="J134" s="2"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" t="b">
@@ -24308,16 +24269,16 @@
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
       <c r="I135" s="2" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="J135" s="2"/>
     </row>
@@ -24328,16 +24289,16 @@
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
       <c r="I136" s="2" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="J136" s="2"/>
     </row>
@@ -24348,16 +24309,16 @@
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
       <c r="I137" s="2" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="J137" s="2"/>
     </row>
@@ -24368,18 +24329,20 @@
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>275</v>
+        <v>409</v>
       </c>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
       <c r="I138" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="J138" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>762</v>
+      </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" t="b">
@@ -24388,16 +24351,16 @@
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>276</v>
+        <v>410</v>
       </c>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
       <c r="I139" s="2" t="s">
-        <v>556</v>
+        <v>519</v>
       </c>
       <c r="J139" s="2"/>
     </row>
@@ -24408,16 +24371,16 @@
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>277</v>
+        <v>411</v>
       </c>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
       <c r="I140" s="2" t="s">
-        <v>557</v>
+        <v>411</v>
       </c>
       <c r="J140" s="2"/>
     </row>
@@ -24428,16 +24391,16 @@
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>278</v>
+        <v>412</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
       <c r="I141" s="2" t="s">
-        <v>558</v>
+        <v>622</v>
       </c>
       <c r="J141" s="2"/>
     </row>
@@ -24448,16 +24411,16 @@
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>279</v>
+        <v>413</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
       <c r="I142" s="2" t="s">
-        <v>559</v>
+        <v>623</v>
       </c>
       <c r="J142" s="2"/>
     </row>
@@ -24468,16 +24431,16 @@
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>280</v>
+        <v>414</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
       <c r="I143" s="2" t="s">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="J143" s="2"/>
     </row>
@@ -24488,16 +24451,16 @@
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>281</v>
+        <v>149</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
       <c r="I144" s="2" t="s">
-        <v>550</v>
+        <v>612</v>
       </c>
       <c r="J144" s="2"/>
     </row>
@@ -24511,15 +24474,17 @@
         <v>729</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>282</v>
+        <v>415</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
       <c r="I145" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="J145" s="2"/>
+        <v>624</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>763</v>
+      </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" t="b">
@@ -24531,13 +24496,13 @@
         <v>729</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>283</v>
+        <v>416</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
       <c r="I146" s="2" t="s">
-        <v>560</v>
+        <v>625</v>
       </c>
       <c r="J146" s="2"/>
     </row>
@@ -24551,13 +24516,13 @@
         <v>729</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>284</v>
+        <v>417</v>
       </c>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
       <c r="I147" s="2" t="s">
-        <v>551</v>
+        <v>626</v>
       </c>
       <c r="J147" s="2"/>
     </row>
@@ -24571,13 +24536,13 @@
         <v>729</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>285</v>
+        <v>418</v>
       </c>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
       <c r="I148" s="2" t="s">
-        <v>561</v>
+        <v>627</v>
       </c>
       <c r="J148" s="2"/>
     </row>
@@ -24591,13 +24556,13 @@
         <v>729</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>286</v>
+        <v>149</v>
       </c>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
       <c r="I149" s="2" t="s">
-        <v>562</v>
+        <v>612</v>
       </c>
       <c r="J149" s="2"/>
     </row>
@@ -24608,18 +24573,20 @@
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>287</v>
+        <v>409</v>
       </c>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
       <c r="I150" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="J150" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" t="b">
@@ -24628,16 +24595,16 @@
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>288</v>
+        <v>410</v>
       </c>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
       <c r="I151" s="2" t="s">
-        <v>564</v>
+        <v>519</v>
       </c>
       <c r="J151" s="2"/>
     </row>
@@ -24648,16 +24615,16 @@
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>289</v>
+        <v>411</v>
       </c>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
       <c r="I152" s="2" t="s">
-        <v>565</v>
+        <v>411</v>
       </c>
       <c r="J152" s="2"/>
     </row>
@@ -24668,16 +24635,16 @@
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>290</v>
+        <v>412</v>
       </c>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
       <c r="I153" s="2" t="s">
-        <v>548</v>
+        <v>622</v>
       </c>
       <c r="J153" s="2"/>
     </row>
@@ -24688,20 +24655,18 @@
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
       <c r="I154" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="J154" s="2" t="s">
-        <v>765</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="J154" s="2"/>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" t="b">
@@ -24710,16 +24675,16 @@
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
       <c r="I155" s="2" t="s">
-        <v>519</v>
+        <v>624</v>
       </c>
       <c r="J155" s="2"/>
     </row>
@@ -24730,16 +24695,16 @@
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
       <c r="I156" s="2" t="s">
-        <v>411</v>
+        <v>625</v>
       </c>
       <c r="J156" s="2"/>
     </row>
@@ -24750,16 +24715,16 @@
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
       <c r="I157" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="J157" s="2"/>
     </row>
@@ -24770,16 +24735,16 @@
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
       <c r="I158" s="2" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="J158" s="2"/>
     </row>
@@ -24790,16 +24755,16 @@
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
       <c r="D159" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
       <c r="I159" s="2" t="s">
-        <v>518</v>
+        <v>628</v>
       </c>
       <c r="J159" s="2"/>
     </row>
@@ -24810,7 +24775,7 @@
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>149</v>
@@ -24830,19 +24795,19 @@
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
       <c r="I161" s="2" t="s">
-        <v>624</v>
+        <v>598</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.2">
@@ -24852,16 +24817,16 @@
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
       <c r="I162" s="2" t="s">
-        <v>625</v>
+        <v>602</v>
       </c>
       <c r="J162" s="2"/>
     </row>
@@ -24872,16 +24837,16 @@
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
       <c r="I163" s="2" t="s">
-        <v>626</v>
+        <v>599</v>
       </c>
       <c r="J163" s="2"/>
     </row>
@@ -24892,16 +24857,16 @@
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
       <c r="I164" s="2" t="s">
-        <v>627</v>
+        <v>603</v>
       </c>
       <c r="J164" s="2"/>
     </row>
@@ -24912,16 +24877,16 @@
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>149</v>
+        <v>427</v>
       </c>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
       <c r="I165" s="2" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="J165" s="2"/>
     </row>
@@ -24932,20 +24897,18 @@
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
       <c r="I166" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="J166" s="2" t="s">
-        <v>767</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="J166" s="2"/>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" t="b">
@@ -24954,16 +24917,16 @@
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
       <c r="I167" s="2" t="s">
-        <v>519</v>
+        <v>600</v>
       </c>
       <c r="J167" s="2"/>
     </row>
@@ -24974,16 +24937,16 @@
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
       <c r="I168" s="2" t="s">
-        <v>411</v>
+        <v>604</v>
       </c>
       <c r="J168" s="2"/>
     </row>
@@ -24994,16 +24957,16 @@
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
       <c r="I169" s="2" t="s">
-        <v>622</v>
+        <v>601</v>
       </c>
       <c r="J169" s="2"/>
     </row>
@@ -25014,16 +24977,16 @@
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
       <c r="I170" s="2" t="s">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="J170" s="2"/>
     </row>
@@ -25034,16 +24997,16 @@
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
       <c r="I171" s="2" t="s">
-        <v>624</v>
+        <v>601</v>
       </c>
       <c r="J171" s="2"/>
     </row>
@@ -25054,16 +25017,16 @@
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
       <c r="I172" s="2" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
       <c r="J172" s="2"/>
     </row>
@@ -25077,15 +25040,17 @@
         <v>734</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
       <c r="I173" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="J173" s="2"/>
+        <v>598</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174" t="b">
@@ -25097,13 +25062,13 @@
         <v>734</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="2" t="s">
-        <v>627</v>
+        <v>602</v>
       </c>
       <c r="J174" s="2"/>
     </row>
@@ -25117,13 +25082,13 @@
         <v>734</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
       <c r="I175" s="2" t="s">
-        <v>628</v>
+        <v>599</v>
       </c>
       <c r="J175" s="2"/>
     </row>
@@ -25137,13 +25102,13 @@
         <v>734</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>149</v>
+        <v>426</v>
       </c>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
       <c r="I176" s="2" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="J176" s="2"/>
     </row>
@@ -25154,20 +25119,18 @@
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
       <c r="I177" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="J177" s="2" t="s">
-        <v>768</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="J177" s="2"/>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A178" t="b">
@@ -25176,16 +25139,16 @@
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
       <c r="I178" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J178" s="2"/>
     </row>
@@ -25196,16 +25159,16 @@
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
       <c r="I179" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="J179" s="2"/>
     </row>
@@ -25216,16 +25179,16 @@
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
       <c r="I180" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J180" s="2"/>
     </row>
@@ -25236,16 +25199,16 @@
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
       <c r="I181" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="J181" s="2"/>
     </row>
@@ -25256,16 +25219,16 @@
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
       <c r="I182" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="J182" s="2"/>
     </row>
@@ -25276,16 +25239,16 @@
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
       <c r="I183" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="J183" s="2"/>
     </row>
@@ -25296,16 +25259,16 @@
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
       <c r="I184" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J184" s="2"/>
     </row>
@@ -25316,340 +25279,18 @@
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>431</v>
+        <v>149</v>
       </c>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
       <c r="I185" s="2" t="s">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="J185" s="2"/>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A186" t="b">
-        <v>1</v>
-      </c>
-      <c r="B186" s="2"/>
-      <c r="C186" s="2"/>
-      <c r="D186" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F186" s="2"/>
-      <c r="G186" s="2"/>
-      <c r="H186" s="2"/>
-      <c r="I186" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="J186" s="2"/>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A187" t="b">
-        <v>1</v>
-      </c>
-      <c r="B187" s="2"/>
-      <c r="C187" s="2"/>
-      <c r="D187" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="F187" s="2"/>
-      <c r="G187" s="2"/>
-      <c r="H187" s="2"/>
-      <c r="I187" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="J187" s="2"/>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A188" t="b">
-        <v>1</v>
-      </c>
-      <c r="B188" s="2"/>
-      <c r="C188" s="2"/>
-      <c r="D188" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F188" s="2"/>
-      <c r="G188" s="2"/>
-      <c r="H188" s="2"/>
-      <c r="I188" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="J188" s="2"/>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A189" t="b">
-        <v>1</v>
-      </c>
-      <c r="B189" s="2"/>
-      <c r="C189" s="2"/>
-      <c r="D189" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="F189" s="2"/>
-      <c r="G189" s="2"/>
-      <c r="H189" s="2"/>
-      <c r="I189" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="J189" s="2" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A190" t="b">
-        <v>1</v>
-      </c>
-      <c r="B190" s="2"/>
-      <c r="C190" s="2"/>
-      <c r="D190" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E190" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F190" s="2"/>
-      <c r="G190" s="2"/>
-      <c r="H190" s="2"/>
-      <c r="I190" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="J190" s="2"/>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A191" t="b">
-        <v>1</v>
-      </c>
-      <c r="B191" s="2"/>
-      <c r="C191" s="2"/>
-      <c r="D191" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="F191" s="2"/>
-      <c r="G191" s="2"/>
-      <c r="H191" s="2"/>
-      <c r="I191" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="J191" s="2"/>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A192" t="b">
-        <v>1</v>
-      </c>
-      <c r="B192" s="2"/>
-      <c r="C192" s="2"/>
-      <c r="D192" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="F192" s="2"/>
-      <c r="G192" s="2"/>
-      <c r="H192" s="2"/>
-      <c r="I192" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="J192" s="2"/>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A193" t="b">
-        <v>1</v>
-      </c>
-      <c r="B193" s="2"/>
-      <c r="C193" s="2"/>
-      <c r="D193" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F193" s="2"/>
-      <c r="G193" s="2"/>
-      <c r="H193" s="2"/>
-      <c r="I193" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="J193" s="2"/>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A194" t="b">
-        <v>1</v>
-      </c>
-      <c r="B194" s="2"/>
-      <c r="C194" s="2"/>
-      <c r="D194" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="F194" s="2"/>
-      <c r="G194" s="2"/>
-      <c r="H194" s="2"/>
-      <c r="I194" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="J194" s="2"/>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A195" t="b">
-        <v>1</v>
-      </c>
-      <c r="B195" s="2"/>
-      <c r="C195" s="2"/>
-      <c r="D195" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F195" s="2"/>
-      <c r="G195" s="2"/>
-      <c r="H195" s="2"/>
-      <c r="I195" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="J195" s="2"/>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A196" t="b">
-        <v>1</v>
-      </c>
-      <c r="B196" s="2"/>
-      <c r="C196" s="2"/>
-      <c r="D196" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="F196" s="2"/>
-      <c r="G196" s="2"/>
-      <c r="H196" s="2"/>
-      <c r="I196" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="J196" s="2"/>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A197" t="b">
-        <v>1</v>
-      </c>
-      <c r="B197" s="2"/>
-      <c r="C197" s="2"/>
-      <c r="D197" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F197" s="2"/>
-      <c r="G197" s="2"/>
-      <c r="H197" s="2"/>
-      <c r="I197" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="J197" s="2"/>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A198" t="b">
-        <v>1</v>
-      </c>
-      <c r="B198" s="2"/>
-      <c r="C198" s="2"/>
-      <c r="D198" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F198" s="2"/>
-      <c r="G198" s="2"/>
-      <c r="H198" s="2"/>
-      <c r="I198" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="J198" s="2"/>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A199" t="b">
-        <v>1</v>
-      </c>
-      <c r="B199" s="2"/>
-      <c r="C199" s="2"/>
-      <c r="D199" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="F199" s="2"/>
-      <c r="G199" s="2"/>
-      <c r="H199" s="2"/>
-      <c r="I199" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="J199" s="2"/>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A200" t="b">
-        <v>1</v>
-      </c>
-      <c r="B200" s="2"/>
-      <c r="C200" s="2"/>
-      <c r="D200" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F200" s="2"/>
-      <c r="G200" s="2"/>
-      <c r="H200" s="2"/>
-      <c r="I200" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="J200" s="2"/>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A201" t="b">
-        <v>1</v>
-      </c>
-      <c r="B201" s="2"/>
-      <c r="C201" s="2"/>
-      <c r="D201" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F201" s="2"/>
-      <c r="G201" s="2"/>
-      <c r="H201" s="2"/>
-      <c r="I201" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="J201" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1816F2-5BAC-5D45-A7BD-F675F4EBA2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AADC31C-A064-044E-A948-9802024BE138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="280" yWindow="500" windowWidth="39840" windowHeight="19600" activeTab="2" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="280" yWindow="500" windowWidth="39840" windowHeight="19600" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maps!$B$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maps!$A$1:$L$6</definedName>
     <definedName name="partID">[1]parts!$A:$A</definedName>
     <definedName name="partLabel">[1]parts!$B:$B</definedName>
   </definedNames>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2507" uniqueCount="766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2391" uniqueCount="768">
   <si>
     <t>Reporter</t>
   </si>
@@ -2208,9 +2208,6 @@
   </si>
   <si>
     <t>Same targets: reporting_jurisdiction, wwtp_jurisdiction</t>
-  </si>
-  <si>
-    <t>Same targets: epaid, epa_registry_id</t>
   </si>
   <si>
     <t>wideOtherSlots</t>
@@ -2364,6 +2361,15 @@
   </si>
   <si>
     <t>For source slot pcr_target_units</t>
+  </si>
+  <si>
+    <t>{{epaid}}</t>
+  </si>
+  <si>
+    <t>{{epa_registry_id}}</t>
+  </si>
+  <si>
+    <t>Same targets: epaid, epa_registry_id, epaid, epaid_registry_id</t>
   </si>
 </sst>
 </file>
@@ -13510,30 +13516,30 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -13927,7 +13933,7 @@
         <v>121</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -13961,7 +13967,7 @@
         <v>82</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -13990,13 +13996,16 @@
         <v>127</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="1" t="s">
         <v>629</v>
       </c>
+      <c r="L4" s="19" t="s">
+        <v>767</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="b">
@@ -14021,7 +14030,7 @@
         <v>84</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -14050,7 +14059,7 @@
         <v>85</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -14153,7 +14162,7 @@
       <c r="J10" s="6"/>
       <c r="K10" s="2"/>
       <c r="L10" s="22" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -14314,7 +14323,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="b">
         <v>1</v>
       </c>
@@ -14343,7 +14352,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="b">
         <v>1</v>
       </c>
@@ -14372,7 +14381,7 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="b">
         <v>1</v>
       </c>
@@ -14401,7 +14410,7 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="b">
         <v>1</v>
       </c>
@@ -14430,7 +14439,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="b">
         <v>1</v>
       </c>
@@ -14459,7 +14468,7 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="b">
         <v>1</v>
       </c>
@@ -14488,7 +14497,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="b">
         <v>1</v>
       </c>
@@ -14517,7 +14526,7 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="b">
         <v>1</v>
       </c>
@@ -14546,7 +14555,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="b">
         <v>1</v>
       </c>
@@ -14575,7 +14584,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="b">
         <v>1</v>
       </c>
@@ -14604,7 +14613,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="b">
         <v>1</v>
       </c>
@@ -14633,7 +14642,7 @@
       <c r="J27" s="6"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -14645,9 +14654,9 @@
       <c r="J28" s="6"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>2</v>
@@ -14663,21 +14672,18 @@
         <v>81</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>127</v>
+        <v>765</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="L29" s="19" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="b">
         <v>0</v>
       </c>
@@ -14695,10 +14701,10 @@
         <v>81</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>127</v>
+        <v>766</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -14706,7 +14712,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="b">
         <v>1</v>
       </c>
@@ -14727,13 +14733,13 @@
         <v>122</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="b">
         <v>0</v>
       </c>
@@ -14754,7 +14760,7 @@
         <v>121</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
@@ -14780,7 +14786,7 @@
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="20" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
@@ -14805,7 +14811,7 @@
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="20" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
@@ -14833,7 +14839,7 @@
         <v>126</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
@@ -15116,13 +15122,13 @@
         <v>160</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="19" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
@@ -15146,7 +15152,7 @@
         <v>160</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
@@ -15154,7 +15160,7 @@
         <v>596</v>
       </c>
       <c r="L47" s="19" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
@@ -15178,13 +15184,13 @@
         <v>160</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
       <c r="L48" s="22" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
@@ -15322,7 +15328,7 @@
         <v>146</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
@@ -15351,7 +15357,7 @@
         <v>150</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -15708,7 +15714,7 @@
         <v>169</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
@@ -16238,7 +16244,7 @@
         <v>486</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
@@ -16265,17 +16271,17 @@
         <v>488</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
       <c r="L91" s="22" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:K1" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}"/>
+  <autoFilter ref="A1:L6" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}"/>
   <conditionalFormatting sqref="H37:J37">
     <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
@@ -16320,7 +16326,7 @@
         <v>704</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1" s="11" t="s">
         <v>167</v>
@@ -16590,7 +16596,7 @@
         <v>665</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>177</v>
@@ -20947,7 +20953,7 @@
         <v>665</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>177</v>
@@ -20968,7 +20974,7 @@
         <v>171</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
@@ -21189,7 +21195,7 @@
         <v>665</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>177</v>
@@ -21229,7 +21235,7 @@
         <v>665</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>177</v>
@@ -21269,7 +21275,7 @@
         <v>665</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>177</v>
@@ -21327,11 +21333,13 @@
   <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.5" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="25.5" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="24" customFormat="1" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -21370,12 +21378,10 @@
       <c r="A2" t="b">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>291</v>
@@ -21387,19 +21393,17 @@
         <v>521</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="b">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>292</v>
@@ -21416,12 +21420,10 @@
       <c r="A4" t="b">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>293</v>
@@ -21438,12 +21440,10 @@
       <c r="A5" t="b">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>294</v>
@@ -21460,12 +21460,10 @@
       <c r="A6" t="b">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>295</v>
@@ -21482,12 +21480,10 @@
       <c r="A7" t="b">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>296</v>
@@ -21504,12 +21500,10 @@
       <c r="A8" t="b">
         <v>1</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>297</v>
@@ -21526,12 +21520,10 @@
       <c r="A9" t="b">
         <v>1</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>298</v>
@@ -21548,12 +21540,10 @@
       <c r="A10" t="b">
         <v>1</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>299</v>
@@ -21570,12 +21560,10 @@
       <c r="A11" t="b">
         <v>1</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>300</v>
@@ -21592,12 +21580,10 @@
       <c r="A12" t="b">
         <v>1</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>301</v>
@@ -21614,12 +21600,10 @@
       <c r="A13" t="b">
         <v>1</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>302</v>
@@ -21636,12 +21620,10 @@
       <c r="A14" t="b">
         <v>1</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>303</v>
@@ -21658,12 +21640,10 @@
       <c r="A15" t="b">
         <v>1</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>304</v>
@@ -21680,12 +21660,10 @@
       <c r="A16" t="b">
         <v>1</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>305</v>
@@ -21702,12 +21680,10 @@
       <c r="A17" t="b">
         <v>1</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>306</v>
@@ -21724,12 +21700,10 @@
       <c r="A18" t="b">
         <v>1</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>307</v>
@@ -21746,12 +21720,10 @@
       <c r="A19" t="b">
         <v>1</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>308</v>
@@ -21768,12 +21740,10 @@
       <c r="A20" t="b">
         <v>1</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>309</v>
@@ -21790,12 +21760,10 @@
       <c r="A21" t="b">
         <v>1</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>310</v>
@@ -21812,12 +21780,10 @@
       <c r="A22" t="b">
         <v>1</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>311</v>
@@ -21834,12 +21800,10 @@
       <c r="A23" t="b">
         <v>1</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>312</v>
@@ -21856,12 +21820,10 @@
       <c r="A24" t="b">
         <v>1</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>313</v>
@@ -21878,12 +21840,10 @@
       <c r="A25" t="b">
         <v>1</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>314</v>
@@ -21900,12 +21860,10 @@
       <c r="A26" t="b">
         <v>1</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>315</v>
@@ -21922,12 +21880,10 @@
       <c r="A27" t="b">
         <v>1</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>322</v>
@@ -21944,12 +21900,10 @@
       <c r="A28" t="b">
         <v>1</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>339</v>
@@ -21966,12 +21920,10 @@
       <c r="A29" t="b">
         <v>1</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>370</v>
@@ -21988,12 +21940,10 @@
       <c r="A30" t="b">
         <v>1</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>344</v>
@@ -22010,12 +21960,10 @@
       <c r="A31" t="b">
         <v>1</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>346</v>
@@ -22032,12 +21980,10 @@
       <c r="A32" t="b">
         <v>1</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>333</v>
@@ -22054,12 +22000,10 @@
       <c r="A33" t="b">
         <v>1</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>368</v>
@@ -22076,12 +22020,10 @@
       <c r="A34" t="b">
         <v>1</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>330</v>
@@ -22098,12 +22040,10 @@
       <c r="A35" t="b">
         <v>1</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>362</v>
@@ -22120,12 +22060,10 @@
       <c r="A36" t="b">
         <v>1</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>328</v>
@@ -22142,12 +22080,10 @@
       <c r="A37" t="b">
         <v>1</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>325</v>
@@ -22164,12 +22100,10 @@
       <c r="A38" t="b">
         <v>1</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>372</v>
@@ -22186,12 +22120,10 @@
       <c r="A39" t="b">
         <v>1</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>347</v>
@@ -22208,12 +22140,10 @@
       <c r="A40" t="b">
         <v>1</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>335</v>
@@ -22230,12 +22160,10 @@
       <c r="A41" t="b">
         <v>1</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>338</v>
@@ -22252,12 +22180,10 @@
       <c r="A42" t="b">
         <v>1</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>349</v>
@@ -22274,12 +22200,10 @@
       <c r="A43" t="b">
         <v>1</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>373</v>
@@ -22296,12 +22220,10 @@
       <c r="A44" t="b">
         <v>1</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>341</v>
@@ -22318,12 +22240,10 @@
       <c r="A45" t="b">
         <v>1</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>345</v>
@@ -22340,12 +22260,10 @@
       <c r="A46" t="b">
         <v>1</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>324</v>
@@ -22362,12 +22280,10 @@
       <c r="A47" t="b">
         <v>1</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>355</v>
@@ -22384,12 +22300,10 @@
       <c r="A48" t="b">
         <v>1</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>332</v>
@@ -22406,12 +22320,10 @@
       <c r="A49" t="b">
         <v>1</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>350</v>
@@ -22428,12 +22340,10 @@
       <c r="A50" t="b">
         <v>1</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>357</v>
@@ -22450,12 +22360,10 @@
       <c r="A51" t="b">
         <v>1</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>320</v>
@@ -22472,12 +22380,10 @@
       <c r="A52" t="b">
         <v>1</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>343</v>
@@ -22494,12 +22400,10 @@
       <c r="A53" t="b">
         <v>1</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>342</v>
@@ -22516,12 +22420,10 @@
       <c r="A54" t="b">
         <v>1</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>329</v>
@@ -22538,12 +22440,10 @@
       <c r="A55" t="b">
         <v>1</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>371</v>
@@ -22560,12 +22460,10 @@
       <c r="A56" t="b">
         <v>1</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>336</v>
@@ -22582,12 +22480,10 @@
       <c r="A57" t="b">
         <v>1</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>374</v>
@@ -22604,12 +22500,10 @@
       <c r="A58" t="b">
         <v>1</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>326</v>
@@ -22626,12 +22520,10 @@
       <c r="A59" t="b">
         <v>1</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>366</v>
@@ -22648,12 +22540,10 @@
       <c r="A60" t="b">
         <v>1</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>375</v>
@@ -22670,12 +22560,10 @@
       <c r="A61" t="b">
         <v>1</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>348</v>
@@ -22692,12 +22580,10 @@
       <c r="A62" t="b">
         <v>1</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>361</v>
@@ -22714,12 +22600,10 @@
       <c r="A63" t="b">
         <v>1</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>363</v>
@@ -22736,12 +22620,10 @@
       <c r="A64" t="b">
         <v>1</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>365</v>
@@ -22758,12 +22640,10 @@
       <c r="A65" t="b">
         <v>1</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>321</v>
@@ -22780,12 +22660,10 @@
       <c r="A66" t="b">
         <v>1</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>376</v>
@@ -22802,12 +22680,10 @@
       <c r="A67" t="b">
         <v>1</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>316</v>
@@ -22824,12 +22700,10 @@
       <c r="A68" t="b">
         <v>1</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>317</v>
@@ -22846,12 +22720,10 @@
       <c r="A69" t="b">
         <v>1</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>340</v>
@@ -22868,12 +22740,10 @@
       <c r="A70" t="b">
         <v>1</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>327</v>
@@ -22890,12 +22760,10 @@
       <c r="A71" t="b">
         <v>1</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>369</v>
@@ -22912,12 +22780,10 @@
       <c r="A72" t="b">
         <v>1</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>356</v>
@@ -22934,12 +22800,10 @@
       <c r="A73" t="b">
         <v>1</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>358</v>
@@ -22956,12 +22820,10 @@
       <c r="A74" t="b">
         <v>1</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>364</v>
@@ -22978,12 +22840,10 @@
       <c r="A75" t="b">
         <v>1</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>331</v>
@@ -23000,12 +22860,10 @@
       <c r="A76" t="b">
         <v>1</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>337</v>
@@ -23022,12 +22880,10 @@
       <c r="A77" t="b">
         <v>1</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>351</v>
@@ -23044,12 +22900,10 @@
       <c r="A78" t="b">
         <v>1</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>352</v>
@@ -23066,12 +22920,10 @@
       <c r="A79" t="b">
         <v>1</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>353</v>
@@ -23088,12 +22940,10 @@
       <c r="A80" t="b">
         <v>1</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>354</v>
@@ -23110,12 +22960,10 @@
       <c r="A81" t="b">
         <v>1</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>323</v>
@@ -23132,12 +22980,10 @@
       <c r="A82" t="b">
         <v>1</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>318</v>
@@ -23154,12 +23000,10 @@
       <c r="A83" t="b">
         <v>1</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>360</v>
@@ -23176,12 +23020,10 @@
       <c r="A84" t="b">
         <v>1</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>367</v>
@@ -23198,12 +23040,10 @@
       <c r="A85" t="b">
         <v>1</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>319</v>
@@ -23220,12 +23060,10 @@
       <c r="A86" t="b">
         <v>1</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>334</v>
@@ -23242,12 +23080,10 @@
       <c r="A87" t="b">
         <v>1</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>359</v>
@@ -23264,12 +23100,10 @@
       <c r="A88" t="b">
         <v>1</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>377</v>
@@ -23286,12 +23120,10 @@
       <c r="A89" t="b">
         <v>1</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>378</v>
@@ -23308,12 +23140,10 @@
       <c r="A90" t="b">
         <v>1</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>379</v>
@@ -23330,12 +23160,10 @@
       <c r="A91" t="b">
         <v>1</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>380</v>
@@ -23352,12 +23180,10 @@
       <c r="A92" t="b">
         <v>1</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>381</v>
@@ -23374,12 +23200,10 @@
       <c r="A93" t="b">
         <v>1</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>382</v>
@@ -23396,12 +23220,10 @@
       <c r="A94" t="b">
         <v>1</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>383</v>
@@ -23418,12 +23240,10 @@
       <c r="A95" t="b">
         <v>1</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>384</v>
@@ -23440,12 +23260,10 @@
       <c r="A96" t="b">
         <v>1</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>385</v>
@@ -23462,12 +23280,10 @@
       <c r="A97" t="b">
         <v>1</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>386</v>
@@ -23484,12 +23300,10 @@
       <c r="A98" t="b">
         <v>1</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>387</v>
@@ -23506,12 +23320,10 @@
       <c r="A99" t="b">
         <v>1</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>388</v>
@@ -23528,12 +23340,10 @@
       <c r="A100" t="b">
         <v>1</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>389</v>
@@ -23550,12 +23360,10 @@
       <c r="A101" t="b">
         <v>1</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>390</v>
@@ -23572,12 +23380,10 @@
       <c r="A102" t="b">
         <v>1</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>391</v>
@@ -23594,12 +23400,10 @@
       <c r="A103" t="b">
         <v>1</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>392</v>
@@ -23616,12 +23420,10 @@
       <c r="A104" t="b">
         <v>1</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>393</v>
@@ -23638,12 +23440,10 @@
       <c r="A105" t="b">
         <v>1</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>394</v>
@@ -23660,12 +23460,10 @@
       <c r="A106" t="b">
         <v>1</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>395</v>
@@ -23682,12 +23480,10 @@
       <c r="A107" t="b">
         <v>1</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>396</v>
@@ -23704,12 +23500,10 @@
       <c r="A108" t="b">
         <v>1</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>277</v>
@@ -23726,12 +23520,10 @@
       <c r="A109" t="b">
         <v>1</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B109" s="2"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>278</v>
@@ -23748,12 +23540,10 @@
       <c r="A110" t="b">
         <v>1</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>279</v>
@@ -23770,12 +23560,10 @@
       <c r="A111" t="b">
         <v>1</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>397</v>
@@ -23792,12 +23580,10 @@
       <c r="A112" t="b">
         <v>1</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>398</v>
@@ -23814,12 +23600,10 @@
       <c r="A113" t="b">
         <v>1</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>399</v>
@@ -23836,12 +23620,10 @@
       <c r="A114" t="b">
         <v>1</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>400</v>
@@ -23858,12 +23640,10 @@
       <c r="A115" t="b">
         <v>1</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>283</v>
@@ -23880,12 +23660,10 @@
       <c r="A116" t="b">
         <v>1</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>284</v>
@@ -23902,12 +23680,10 @@
       <c r="A117" t="b">
         <v>1</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>401</v>
@@ -23927,7 +23703,7 @@
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>271</v>
@@ -23939,7 +23715,7 @@
         <v>547</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
@@ -23949,7 +23725,7 @@
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>272</v>
@@ -23969,7 +23745,7 @@
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>273</v>
@@ -23989,7 +23765,7 @@
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>274</v>
@@ -24009,7 +23785,7 @@
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>275</v>
@@ -24029,7 +23805,7 @@
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>276</v>
@@ -24049,7 +23825,7 @@
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>277</v>
@@ -24069,7 +23845,7 @@
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>278</v>
@@ -24089,7 +23865,7 @@
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>279</v>
@@ -24109,7 +23885,7 @@
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>280</v>
@@ -24129,7 +23905,7 @@
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>281</v>
@@ -24149,7 +23925,7 @@
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>282</v>
@@ -24169,7 +23945,7 @@
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>283</v>
@@ -24189,7 +23965,7 @@
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>284</v>
@@ -24209,7 +23985,7 @@
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
       <c r="D132" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>285</v>
@@ -24229,7 +24005,7 @@
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>286</v>
@@ -24249,7 +24025,7 @@
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>287</v>
@@ -24269,7 +24045,7 @@
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>288</v>
@@ -24289,7 +24065,7 @@
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>289</v>
@@ -24309,7 +24085,7 @@
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>290</v>
@@ -24329,7 +24105,7 @@
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>409</v>
@@ -24341,7 +24117,7 @@
         <v>518</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
@@ -24351,7 +24127,7 @@
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>410</v>
@@ -24371,7 +24147,7 @@
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>411</v>
@@ -24391,7 +24167,7 @@
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>412</v>
@@ -24411,7 +24187,7 @@
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>413</v>
@@ -24431,7 +24207,7 @@
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>414</v>
@@ -24451,7 +24227,7 @@
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>149</v>
@@ -24471,7 +24247,7 @@
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>415</v>
@@ -24483,7 +24259,7 @@
         <v>624</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
@@ -24493,7 +24269,7 @@
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>416</v>
@@ -24513,7 +24289,7 @@
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>417</v>
@@ -24533,7 +24309,7 @@
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>418</v>
@@ -24553,7 +24329,7 @@
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
       <c r="D149" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>149</v>
@@ -24573,7 +24349,7 @@
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>409</v>
@@ -24585,7 +24361,7 @@
         <v>518</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
@@ -24595,7 +24371,7 @@
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>410</v>
@@ -24615,7 +24391,7 @@
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>411</v>
@@ -24635,7 +24411,7 @@
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>412</v>
@@ -24655,7 +24431,7 @@
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>413</v>
@@ -24675,7 +24451,7 @@
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>419</v>
@@ -24695,7 +24471,7 @@
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>416</v>
@@ -24715,7 +24491,7 @@
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>417</v>
@@ -24735,7 +24511,7 @@
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>418</v>
@@ -24755,7 +24531,7 @@
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
       <c r="D159" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>420</v>
@@ -24775,7 +24551,7 @@
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>149</v>
@@ -24795,7 +24571,7 @@
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>423</v>
@@ -24807,7 +24583,7 @@
         <v>598</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.2">
@@ -24817,7 +24593,7 @@
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>424</v>
@@ -24837,7 +24613,7 @@
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>425</v>
@@ -24857,7 +24633,7 @@
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>426</v>
@@ -24877,7 +24653,7 @@
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>427</v>
@@ -24897,7 +24673,7 @@
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>428</v>
@@ -24917,7 +24693,7 @@
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>429</v>
@@ -24937,7 +24713,7 @@
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>430</v>
@@ -24957,7 +24733,7 @@
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>431</v>
@@ -24977,7 +24753,7 @@
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>432</v>
@@ -24997,7 +24773,7 @@
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>433</v>
@@ -25017,7 +24793,7 @@
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>434</v>
@@ -25037,7 +24813,7 @@
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>423</v>
@@ -25049,7 +24825,7 @@
         <v>598</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.2">
@@ -25059,7 +24835,7 @@
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>424</v>
@@ -25079,7 +24855,7 @@
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
       <c r="D175" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>425</v>
@@ -25099,7 +24875,7 @@
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
       <c r="D176" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>426</v>
@@ -25119,7 +24895,7 @@
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>427</v>
@@ -25139,7 +24915,7 @@
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>428</v>
@@ -25159,7 +24935,7 @@
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>429</v>
@@ -25179,7 +24955,7 @@
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>430</v>
@@ -25199,7 +24975,7 @@
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>431</v>
@@ -25219,7 +24995,7 @@
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>432</v>
@@ -25239,7 +25015,7 @@
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>433</v>
@@ -25259,7 +25035,7 @@
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>434</v>
@@ -25279,7 +25055,7 @@
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>149</v>

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AADC31C-A064-044E-A948-9802024BE138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7342C3BD-CDA0-914D-BE9F-959B5DED16CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="39840" windowHeight="19600" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2391" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2390" uniqueCount="768">
   <si>
     <t>Reporter</t>
   </si>
@@ -15494,9 +15494,7 @@
         <v>650</v>
       </c>
       <c r="D61" s="2"/>
-      <c r="E61" s="2" t="s">
-        <v>147</v>
-      </c>
+      <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
         <v>124</v>
       </c>

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69609E77-4339-CA48-B7EC-B56850147210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F613E1-6D96-B64B-9A2F-54244DCC1AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="220" yWindow="500" windowWidth="39840" windowHeight="19600" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15880" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,9 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maps!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">enums!$A$1:$J$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maps!$A$1:$L$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">wide!$A$1:$N$136</definedName>
     <definedName name="partID">[1]parts!$A:$A</definedName>
     <definedName name="partLabel">[1]parts!$B:$B</definedName>
   </definedNames>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="761">
   <si>
     <t>Reporter</t>
   </si>
@@ -2252,9 +2254,6 @@
     <t>{{site_id}}</t>
   </si>
   <si>
-    <t>{{county_names}}</t>
-  </si>
-  <si>
     <t>{{zipcode}}</t>
   </si>
   <si>
@@ -2288,9 +2287,6 @@
     <t>See row 67 in original maps sheet</t>
   </si>
   <si>
-    <t>major_lab_method_desc is not in NWSS LinkML schema</t>
-  </si>
-  <si>
     <t>For source slot pcr_target</t>
   </si>
   <si>
@@ -2321,9 +2317,6 @@
     <t>contactID</t>
   </si>
   <si>
-    <t>Same targets: Concatenate: "EPA_id: value, EPA_registry_id: epaid_registry_id"</t>
-  </si>
-  <si>
     <t>{{sample_location_specify}}</t>
   </si>
   <si>
@@ -2349,6 +2342,15 @@
   </si>
   <si>
     <t>What about for other combinations of inhibition_adjust and inhibition_detect? All other cases: empty</t>
+  </si>
+  <si>
+    <t>"County names=" + county_names + "; EPA_id=" + epaid + "; EPA_registry_id=" + epa_registry_id</t>
+  </si>
+  <si>
+    <t>Good! Same targets: Concatenate: "EPA_id: value, EPA_registry_id: epaid_registry_id"</t>
+  </si>
+  <si>
+    <t>Fixed! major_lab_method_desc is not in NWSS LinkML schema: Is in data dictionary, rerun schema generator</t>
   </si>
 </sst>
 </file>
@@ -13909,7 +13911,7 @@
         <v>115</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>726</v>
@@ -13920,7 +13922,7 @@
         <v>483</v>
       </c>
       <c r="L2" s="19" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -13965,25 +13967,23 @@
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="E4" s="2"/>
       <c r="F4" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="I4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="21" t="s">
+        <v>758</v>
+      </c>
       <c r="J4" s="2"/>
       <c r="K4" s="1" t="s">
         <v>621</v>
       </c>
       <c r="L4" s="19" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -14009,7 +14009,7 @@
         <v>80</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -14038,7 +14038,7 @@
         <v>81</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -14135,13 +14135,13 @@
         <v>121</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="2"/>
       <c r="L10" s="22" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -14654,7 +14654,7 @@
         <v>121</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -14683,7 +14683,7 @@
         <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -14712,7 +14712,7 @@
         <v>116</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -14720,7 +14720,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>2</v>
@@ -14736,10 +14736,10 @@
         <v>77</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
@@ -14818,7 +14818,7 @@
         <v>120</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
@@ -15202,7 +15202,7 @@
         <v>140</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
@@ -15231,7 +15231,7 @@
         <v>144</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -15588,7 +15588,7 @@
         <v>162</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
@@ -15807,10 +15807,10 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="1" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="L74" s="19" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
@@ -16118,7 +16118,7 @@
         <v>479</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
@@ -16145,17 +16145,17 @@
         <v>481</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
       <c r="L87" s="22" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L6" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}"/>
+  <autoFilter ref="A1:L87" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}"/>
   <conditionalFormatting sqref="H37:J37">
     <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
@@ -20453,7 +20453,7 @@
         <v>414</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>76</v>
@@ -20829,7 +20829,7 @@
         <v>657</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>170</v>
@@ -20850,7 +20850,7 @@
         <v>164</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
@@ -20871,7 +20871,7 @@
         <v>657</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>170</v>
@@ -20913,7 +20913,7 @@
         <v>657</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>170</v>
@@ -20955,7 +20955,7 @@
         <v>657</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>170</v>
@@ -20997,7 +20997,7 @@
         <v>657</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>170</v>
@@ -21182,6 +21182,7 @@
       <c r="N136" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N136" xr:uid="{B39AC7DD-3F73-2C47-925D-21E5B4EBE6FC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D99:D105">
     <sortCondition ref="D99:D105"/>
   </sortState>
@@ -21277,7 +21278,7 @@
         <v>514</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -23599,7 +23600,7 @@
         <v>540</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
@@ -24001,7 +24002,7 @@
         <v>511</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
@@ -24143,7 +24144,7 @@
         <v>616</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
@@ -24245,7 +24246,7 @@
         <v>511</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
@@ -24467,7 +24468,7 @@
         <v>590</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.2">
@@ -24953,6 +24954,7 @@
       <c r="J185" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J185" xr:uid="{1BC10C3F-0C27-5546-8767-E60C7CACEA9D}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F613E1-6D96-B64B-9A2F-54244DCC1AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E86748A-8541-034B-9FB4-A040D435AB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15880" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="0" yWindow="520" windowWidth="28800" windowHeight="15880" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="759">
   <si>
     <t>Reporter</t>
   </si>
@@ -1883,9 +1883,6 @@
   </si>
   <si>
     <t>flagFI</t>
-  </si>
-  <si>
-    <t>flagAI OR flagFI</t>
   </si>
   <si>
     <t>Notice that inhibition_detect and inhibition_adjust are collapsed into a single variable in ODM. A "yes" in both  fields will be taken as a "flagAI" for "qualityFlag". A "Yes" in inhibition_detect and "No" in inhibition_adjust give a "flagFI" value for "qualityFlag". "Not Tested should be ignored. ALSO - needs to have the qualityReports table measureRepID field match the measureRepID for pcr_target_avg_conc</t>
@@ -2326,9 +2323,6 @@
     <t>{"reflink": "{{pcr_gene_target_ref}}", "group": "{{pcr_target}}"}</t>
   </si>
   <si>
-    <t>Good! Same targets: reporting_jurisdiction, wwtp_jurisdiction</t>
-  </si>
-  <si>
     <t>Good! Same targetSlot as sample_location. Map to notes</t>
   </si>
   <si>
@@ -2341,23 +2335,29 @@
     <t>Notice that inhibition_detect and inhibition_adjust are collapsed into a single variable in ODM. A "yes" in both  fields will be taken as a "flagAI" for "qualityFlag". A "Yes" in inhibition_detect and "No" in inhibition_adjust give a "flagFI" value for "qualityFlag". "Not Tested" should be ignored. ALSO - needs to have the qualityReports table measureRepID field match the measureRepID for pcr_target_avg_conc</t>
   </si>
   <si>
-    <t>What about for other combinations of inhibition_adjust and inhibition_detect? All other cases: empty</t>
-  </si>
-  <si>
     <t>"County names=" + county_names + "; EPA_id=" + epaid + "; EPA_registry_id=" + epa_registry_id</t>
   </si>
   <si>
     <t>Good! Same targets: Concatenate: "EPA_id: value, EPA_registry_id: epaid_registry_id"</t>
   </si>
   <si>
-    <t>Fixed! major_lab_method_desc is not in NWSS LinkML schema: Is in data dictionary, rerun schema generator</t>
+    <t>def get_qualityFlag(inhibition_detect: str, inhibition_adjust: str) -&gt; str:
+    if inhibition_detect == "yes" and inhibition_adjust == "yes":
+        return "flagAI"
+    elif inhibition_detect == "yes" and inhibition_adjust == "no":
+        return "flagFI"
+    return ""
+target = get_qualityFlag(src.inhibition_detect, src.inhibition_adjust)</t>
+  </si>
+  <si>
+    <t>Good! What about for other combinations of inhibition_adjust and inhibition_detect? All other cases: empty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2420,6 +2420,19 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -2542,7 +2555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2585,6 +2598,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13858,34 +13879,34 @@
   <sheetData>
     <row r="1" spans="1:12" s="24" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D1" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>643</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>645</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>646</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>647</v>
-      </c>
       <c r="I1" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>693</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>694</v>
       </c>
       <c r="K1" s="10" t="s">
         <v>121</v>
@@ -13899,7 +13920,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -13911,19 +13932,17 @@
         <v>115</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="L2" s="19" t="s">
-        <v>752</v>
-      </c>
+      <c r="L2" s="23"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="b">
@@ -13933,7 +13952,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -13948,7 +13967,7 @@
         <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -13962,7 +13981,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
@@ -13976,14 +13995,14 @@
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="21" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="L4" s="19" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -13994,7 +14013,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
@@ -14009,7 +14028,7 @@
         <v>80</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -14023,7 +14042,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -14038,7 +14057,7 @@
         <v>81</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -14064,7 +14083,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>13</v>
@@ -14093,7 +14112,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>13</v>
@@ -14122,7 +14141,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -14135,13 +14154,13 @@
         <v>121</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="2"/>
       <c r="L10" s="22" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -14157,34 +14176,34 @@
       <c r="K11" s="2"/>
       <c r="L11" s="23"/>
     </row>
-    <row r="12" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="D12" s="2" t="s">
+    <row r="12" spans="1:12" s="23" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>641</v>
+      </c>
+      <c r="D12" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="b">
@@ -14194,7 +14213,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>15</v>
@@ -14223,7 +14242,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>15</v>
@@ -14252,7 +14271,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>15</v>
@@ -14281,7 +14300,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>15</v>
@@ -14310,7 +14329,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>15</v>
@@ -14339,7 +14358,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>15</v>
@@ -14368,7 +14387,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>15</v>
@@ -14397,7 +14416,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>15</v>
@@ -14426,7 +14445,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>15</v>
@@ -14455,7 +14474,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>15</v>
@@ -14484,7 +14503,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>15</v>
@@ -14513,7 +14532,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>15</v>
@@ -14542,7 +14561,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>15</v>
@@ -14571,7 +14590,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>15</v>
@@ -14592,34 +14611,34 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" t="b">
-        <v>1</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="D27" s="2" t="s">
+    <row r="27" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>641</v>
+      </c>
+      <c r="D27" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="31" t="s">
         <v>539</v>
       </c>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="2"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="28"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B28" s="2"/>
@@ -14641,7 +14660,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>16</v>
@@ -14654,7 +14673,7 @@
         <v>121</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -14670,7 +14689,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>17</v>
@@ -14683,7 +14702,7 @@
         <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -14699,7 +14718,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
@@ -14712,7 +14731,7 @@
         <v>116</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -14726,7 +14745,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>19</v>
@@ -14736,10 +14755,10 @@
         <v>77</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
@@ -14753,7 +14772,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -14761,11 +14780,11 @@
         <v>118</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="20" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
@@ -14778,7 +14797,7 @@
         <v>3</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D34" s="21"/>
       <c r="E34" s="3"/>
@@ -14790,7 +14809,7 @@
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="20" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
@@ -14803,7 +14822,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>23</v>
@@ -14818,7 +14837,7 @@
         <v>120</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
@@ -14844,7 +14863,7 @@
         <v>3</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>24</v>
@@ -14873,7 +14892,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>24</v>
@@ -14902,7 +14921,7 @@
         <v>3</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>24</v>
@@ -14931,7 +14950,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>24</v>
@@ -14960,7 +14979,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>24</v>
@@ -14989,7 +15008,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>24</v>
@@ -15018,7 +15037,7 @@
         <v>3</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>24</v>
@@ -15047,7 +15066,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>24</v>
@@ -15088,7 +15107,7 @@
         <v>4</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D46" s="21" t="s">
         <v>45</v>
@@ -15117,7 +15136,7 @@
         <v>4</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>46</v>
@@ -15146,7 +15165,7 @@
         <v>4</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>47</v>
@@ -15187,7 +15206,7 @@
         <v>4</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>54</v>
@@ -15202,7 +15221,7 @@
         <v>140</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
@@ -15216,7 +15235,7 @@
         <v>4</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>55</v>
@@ -15231,7 +15250,7 @@
         <v>144</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -15251,13 +15270,13 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>56</v>
@@ -15280,18 +15299,18 @@
         <v>151</v>
       </c>
       <c r="L53" s="19" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>56</v>
@@ -15316,13 +15335,13 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>56</v>
@@ -15365,11 +15384,9 @@
         <v>4</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>57</v>
-      </c>
+        <v>641</v>
+      </c>
+      <c r="D57" s="2"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
         <v>118</v>
@@ -15379,7 +15396,7 @@
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="1" t="s">
@@ -15394,7 +15411,7 @@
         <v>4</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>57</v>
@@ -15425,7 +15442,7 @@
         <v>4</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>57</v>
@@ -15468,7 +15485,7 @@
         <v>4</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>58</v>
@@ -15499,7 +15516,7 @@
         <v>4</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>58</v>
@@ -15530,7 +15547,7 @@
         <v>4</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>58</v>
@@ -15573,7 +15590,7 @@
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>59</v>
@@ -15588,7 +15605,7 @@
         <v>162</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
@@ -15614,7 +15631,7 @@
         <v>5</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>64</v>
@@ -15645,7 +15662,7 @@
         <v>5</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>64</v>
@@ -15674,7 +15691,7 @@
         <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>64</v>
@@ -15715,7 +15732,7 @@
         <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>66</v>
@@ -15746,7 +15763,7 @@
         <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>66</v>
@@ -15779,38 +15796,34 @@
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>141</v>
-      </c>
+        <v>641</v>
+      </c>
+      <c r="D74" s="2"/>
+      <c r="E74" s="3"/>
       <c r="F74" s="2" t="s">
         <v>147</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="H74" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="I74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="17" t="s">
+        <v>757</v>
+      </c>
       <c r="J74" s="2"/>
       <c r="K74" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="L74" s="19" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
@@ -15821,7 +15834,7 @@
         <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>68</v>
@@ -15841,7 +15854,7 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
@@ -15852,7 +15865,7 @@
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>68</v>
@@ -15872,7 +15885,7 @@
       <c r="I76" s="6"/>
       <c r="J76" s="6"/>
       <c r="K76" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
@@ -15895,7 +15908,7 @@
         <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>69</v>
@@ -15915,7 +15928,7 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -15926,7 +15939,7 @@
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>69</v>
@@ -15946,7 +15959,7 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
@@ -15957,7 +15970,7 @@
         <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>69</v>
@@ -15977,7 +15990,7 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
@@ -16000,7 +16013,7 @@
         <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>73</v>
@@ -16031,7 +16044,7 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>73</v>
@@ -16062,7 +16075,7 @@
         <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>73</v>
@@ -16105,7 +16118,7 @@
         <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>74</v>
@@ -16118,7 +16131,7 @@
         <v>479</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
@@ -16132,7 +16145,7 @@
         <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>75</v>
@@ -16145,14 +16158,12 @@
         <v>481</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
-      <c r="L87" s="22" t="s">
-        <v>760</v>
-      </c>
+      <c r="L87" s="23"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L87" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}"/>
@@ -16182,25 +16193,25 @@
   <sheetData>
     <row r="1" spans="1:14" s="24" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>687</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>688</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>689</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>690</v>
-      </c>
       <c r="F1" s="9" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1" s="11" t="s">
         <v>160</v>
@@ -16221,7 +16232,7 @@
         <v>157</v>
       </c>
       <c r="N1" s="12" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -16229,7 +16240,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>12</v>
@@ -16239,7 +16250,7 @@
         <v>115</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="13" t="s">
@@ -16249,10 +16260,10 @@
         <v>165</v>
       </c>
       <c r="J2" s="13" t="s">
+        <v>656</v>
+      </c>
+      <c r="K2" s="13" t="s">
         <v>657</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>658</v>
       </c>
       <c r="L2" s="13" t="s">
         <v>163</v>
@@ -16267,7 +16278,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -16277,7 +16288,7 @@
         <v>115</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
@@ -16287,10 +16298,10 @@
         <v>166</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>167</v>
@@ -16305,7 +16316,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>21</v>
@@ -16315,7 +16326,7 @@
         <v>115</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
@@ -16325,10 +16336,10 @@
         <v>168</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>169</v>
@@ -16343,7 +16354,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>22</v>
@@ -16353,7 +16364,7 @@
         <v>115</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
@@ -16363,10 +16374,10 @@
         <v>171</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>76</v>
@@ -16381,7 +16392,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>25</v>
@@ -16391,7 +16402,7 @@
         <v>115</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
@@ -16401,10 +16412,10 @@
         <v>172</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>163</v>
@@ -16419,7 +16430,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>26</v>
@@ -16429,7 +16440,7 @@
         <v>115</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
@@ -16439,10 +16450,10 @@
         <v>173</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>174</v>
@@ -16457,7 +16468,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>27</v>
@@ -16467,10 +16478,10 @@
         <v>115</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>170</v>
@@ -16479,10 +16490,10 @@
         <v>175</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>76</v>
@@ -16512,7 +16523,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>28</v>
@@ -16531,13 +16542,13 @@
         <v>76</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>428</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>76</v>
@@ -16552,7 +16563,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>28</v>
@@ -16569,13 +16580,13 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>76</v>
@@ -16590,7 +16601,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>28</v>
@@ -16607,13 +16618,13 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>76</v>
@@ -16628,7 +16639,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>28</v>
@@ -16645,13 +16656,13 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>76</v>
@@ -16666,7 +16677,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>28</v>
@@ -16683,13 +16694,13 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>76</v>
@@ -16719,7 +16730,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -16738,13 +16749,13 @@
         <v>76</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>433</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>76</v>
@@ -16759,7 +16770,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>29</v>
@@ -16776,13 +16787,13 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>76</v>
@@ -16797,7 +16808,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>29</v>
@@ -16814,13 +16825,13 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>76</v>
@@ -16835,7 +16846,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>29</v>
@@ -16852,13 +16863,13 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>76</v>
@@ -16873,7 +16884,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>29</v>
@@ -16890,10 +16901,10 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2" t="s">
@@ -16909,7 +16920,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>29</v>
@@ -16926,13 +16937,13 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>76</v>
@@ -16947,7 +16958,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>29</v>
@@ -16964,13 +16975,13 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>76</v>
@@ -16985,7 +16996,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -17002,13 +17013,13 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>76</v>
@@ -17023,7 +17034,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>29</v>
@@ -17040,13 +17051,13 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>76</v>
@@ -17061,7 +17072,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>29</v>
@@ -17078,13 +17089,13 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>76</v>
@@ -17099,7 +17110,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>29</v>
@@ -17116,13 +17127,13 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>76</v>
@@ -17137,7 +17148,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>29</v>
@@ -17154,13 +17165,13 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>76</v>
@@ -17175,7 +17186,7 @@
         <v>1</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>29</v>
@@ -17192,13 +17203,13 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>76</v>
@@ -17213,7 +17224,7 @@
         <v>1</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>29</v>
@@ -17225,18 +17236,18 @@
         <v>152</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>76</v>
@@ -17251,7 +17262,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -17268,13 +17279,13 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>76</v>
@@ -17289,7 +17300,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>29</v>
@@ -17306,13 +17317,13 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>76</v>
@@ -17327,7 +17338,7 @@
         <v>1</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>29</v>
@@ -17344,13 +17355,13 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>76</v>
@@ -17365,7 +17376,7 @@
         <v>1</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>29</v>
@@ -17382,13 +17393,13 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>76</v>
@@ -17403,7 +17414,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>29</v>
@@ -17420,13 +17431,13 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>76</v>
@@ -17441,7 +17452,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>29</v>
@@ -17458,13 +17469,13 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>76</v>
@@ -17479,7 +17490,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>29</v>
@@ -17491,18 +17502,18 @@
         <v>152</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>76</v>
@@ -17517,7 +17528,7 @@
         <v>1</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -17529,18 +17540,18 @@
         <v>152</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>76</v>
@@ -17555,7 +17566,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>29</v>
@@ -17567,18 +17578,18 @@
         <v>152</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>76</v>
@@ -17593,7 +17604,7 @@
         <v>1</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>29</v>
@@ -17610,13 +17621,13 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>76</v>
@@ -17646,7 +17657,7 @@
         <v>1</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>30</v>
@@ -17665,13 +17676,13 @@
         <v>76</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>452</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>76</v>
@@ -17686,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>30</v>
@@ -17703,13 +17714,13 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>76</v>
@@ -17724,7 +17735,7 @@
         <v>1</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>30</v>
@@ -17736,18 +17747,18 @@
         <v>152</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>76</v>
@@ -17762,7 +17773,7 @@
         <v>1</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>30</v>
@@ -17774,18 +17785,18 @@
         <v>152</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>76</v>
@@ -17800,7 +17811,7 @@
         <v>1</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>30</v>
@@ -17812,18 +17823,18 @@
         <v>152</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>76</v>
@@ -17838,7 +17849,7 @@
         <v>1</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>30</v>
@@ -17850,18 +17861,18 @@
         <v>152</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>76</v>
@@ -17876,7 +17887,7 @@
         <v>1</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>30</v>
@@ -17893,13 +17904,13 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>76</v>
@@ -17914,7 +17925,7 @@
         <v>1</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>30</v>
@@ -17931,13 +17942,13 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>76</v>
@@ -17952,7 +17963,7 @@
         <v>1</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>30</v>
@@ -17969,13 +17980,13 @@
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>76</v>
@@ -17990,7 +18001,7 @@
         <v>1</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>30</v>
@@ -18007,13 +18018,13 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>76</v>
@@ -18028,7 +18039,7 @@
         <v>1</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>30</v>
@@ -18045,13 +18056,13 @@
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>76</v>
@@ -18066,7 +18077,7 @@
         <v>1</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>30</v>
@@ -18083,13 +18094,13 @@
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>76</v>
@@ -18104,7 +18115,7 @@
         <v>1</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>30</v>
@@ -18121,13 +18132,13 @@
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>76</v>
@@ -18142,7 +18153,7 @@
         <v>1</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>30</v>
@@ -18159,13 +18170,13 @@
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>76</v>
@@ -18180,7 +18191,7 @@
         <v>1</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>30</v>
@@ -18192,18 +18203,18 @@
         <v>152</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>76</v>
@@ -18218,7 +18229,7 @@
         <v>1</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>30</v>
@@ -18235,13 +18246,13 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>76</v>
@@ -18256,7 +18267,7 @@
         <v>1</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>30</v>
@@ -18273,13 +18284,13 @@
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>76</v>
@@ -18294,7 +18305,7 @@
         <v>1</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>30</v>
@@ -18311,13 +18322,13 @@
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>76</v>
@@ -18332,7 +18343,7 @@
         <v>1</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>30</v>
@@ -18349,13 +18360,13 @@
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>76</v>
@@ -18370,7 +18381,7 @@
         <v>1</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>30</v>
@@ -18387,13 +18398,13 @@
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>76</v>
@@ -18408,7 +18419,7 @@
         <v>1</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>30</v>
@@ -18420,18 +18431,18 @@
         <v>152</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>76</v>
@@ -18446,7 +18457,7 @@
         <v>1</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>30</v>
@@ -18463,13 +18474,13 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>76</v>
@@ -18484,7 +18495,7 @@
         <v>1</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>30</v>
@@ -18501,13 +18512,13 @@
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>76</v>
@@ -18522,7 +18533,7 @@
         <v>1</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>30</v>
@@ -18534,18 +18545,18 @@
         <v>152</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>76</v>
@@ -18560,7 +18571,7 @@
         <v>1</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>30</v>
@@ -18577,13 +18588,13 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>76</v>
@@ -18598,7 +18609,7 @@
         <v>1</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>30</v>
@@ -18610,18 +18621,18 @@
         <v>152</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>76</v>
@@ -18636,7 +18647,7 @@
         <v>1</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>30</v>
@@ -18648,18 +18659,18 @@
         <v>152</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>76</v>
@@ -18674,7 +18685,7 @@
         <v>1</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>30</v>
@@ -18686,18 +18697,18 @@
         <v>152</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>76</v>
@@ -18712,7 +18723,7 @@
         <v>1</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>30</v>
@@ -18729,13 +18740,13 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>76</v>
@@ -18750,7 +18761,7 @@
         <v>1</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>30</v>
@@ -18767,13 +18778,13 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>76</v>
@@ -18788,7 +18799,7 @@
         <v>1</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>30</v>
@@ -18805,13 +18816,13 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>76</v>
@@ -18826,7 +18837,7 @@
         <v>1</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>30</v>
@@ -18838,18 +18849,18 @@
         <v>152</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>76</v>
@@ -18864,7 +18875,7 @@
         <v>1</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>30</v>
@@ -18876,18 +18887,18 @@
         <v>152</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>76</v>
@@ -18917,7 +18928,7 @@
         <v>1</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>31</v>
@@ -18927,7 +18938,7 @@
         <v>152</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2" t="s">
@@ -18937,10 +18948,10 @@
         <v>485</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>163</v>
@@ -18955,7 +18966,7 @@
         <v>1</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>32</v>
@@ -18965,7 +18976,7 @@
         <v>152</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2" t="s">
@@ -18975,10 +18986,10 @@
         <v>486</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>174</v>
@@ -18993,7 +19004,7 @@
         <v>1</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>33</v>
@@ -19003,7 +19014,7 @@
         <v>152</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2" t="s">
@@ -19013,10 +19024,10 @@
         <v>487</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>163</v>
@@ -19031,7 +19042,7 @@
         <v>1</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>34</v>
@@ -19041,7 +19052,7 @@
         <v>152</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2" t="s">
@@ -19051,10 +19062,10 @@
         <v>488</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>174</v>
@@ -19069,7 +19080,7 @@
         <v>1</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>35</v>
@@ -19079,20 +19090,20 @@
         <v>152</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2" t="s">
         <v>76</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>489</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>158</v>
@@ -19107,7 +19118,7 @@
         <v>1</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>36</v>
@@ -19117,20 +19128,20 @@
         <v>152</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2" t="s">
         <v>76</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>490</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>76</v>
@@ -19160,7 +19171,7 @@
         <v>1</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>37</v>
@@ -19179,13 +19190,13 @@
         <v>76</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>491</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>76</v>
@@ -19200,7 +19211,7 @@
         <v>1</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>37</v>
@@ -19212,18 +19223,18 @@
         <v>152</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>76</v>
@@ -19238,7 +19249,7 @@
         <v>1</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>37</v>
@@ -19255,13 +19266,13 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>76</v>
@@ -19276,7 +19287,7 @@
         <v>1</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>37</v>
@@ -19293,13 +19304,13 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>76</v>
@@ -19314,7 +19325,7 @@
         <v>1</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>37</v>
@@ -19331,13 +19342,13 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>76</v>
@@ -19352,7 +19363,7 @@
         <v>1</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>37</v>
@@ -19369,13 +19380,13 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>76</v>
@@ -19390,7 +19401,7 @@
         <v>1</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>37</v>
@@ -19407,13 +19418,13 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>76</v>
@@ -19428,7 +19439,7 @@
         <v>1</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>37</v>
@@ -19445,13 +19456,13 @@
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
       <c r="I89" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>76</v>
@@ -19466,7 +19477,7 @@
         <v>1</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>37</v>
@@ -19483,13 +19494,13 @@
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>76</v>
@@ -19504,7 +19515,7 @@
         <v>1</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>37</v>
@@ -19521,13 +19532,13 @@
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>76</v>
@@ -19542,7 +19553,7 @@
         <v>1</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>37</v>
@@ -19559,13 +19570,13 @@
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>76</v>
@@ -19580,7 +19591,7 @@
         <v>1</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>37</v>
@@ -19592,18 +19603,18 @@
         <v>152</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>76</v>
@@ -19618,7 +19629,7 @@
         <v>1</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>37</v>
@@ -19635,13 +19646,13 @@
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>76</v>
@@ -19656,7 +19667,7 @@
         <v>1</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>37</v>
@@ -19668,18 +19679,18 @@
         <v>152</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>76</v>
@@ -19694,7 +19705,7 @@
         <v>1</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>37</v>
@@ -19711,13 +19722,13 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>76</v>
@@ -19732,7 +19743,7 @@
         <v>1</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>37</v>
@@ -19749,13 +19760,13 @@
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>76</v>
@@ -19785,7 +19796,7 @@
         <v>1</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>38</v>
@@ -19804,13 +19815,13 @@
         <v>76</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>492</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>76</v>
@@ -19825,7 +19836,7 @@
         <v>1</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>38</v>
@@ -19842,13 +19853,13 @@
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>76</v>
@@ -19863,7 +19874,7 @@
         <v>1</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>38</v>
@@ -19880,13 +19891,13 @@
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>76</v>
@@ -19901,7 +19912,7 @@
         <v>1</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>38</v>
@@ -19918,13 +19929,13 @@
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
       <c r="I102" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>76</v>
@@ -19939,7 +19950,7 @@
         <v>1</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>38</v>
@@ -19956,13 +19967,13 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>76</v>
@@ -19977,7 +19988,7 @@
         <v>1</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>38</v>
@@ -19994,13 +20005,13 @@
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
       <c r="I104" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>76</v>
@@ -20015,7 +20026,7 @@
         <v>1</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>38</v>
@@ -20032,13 +20043,13 @@
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>76</v>
@@ -20068,7 +20079,7 @@
         <v>1</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>39</v>
@@ -20078,7 +20089,7 @@
         <v>115</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2" t="s">
@@ -20088,10 +20099,10 @@
         <v>587</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>588</v>
@@ -20106,7 +20117,7 @@
         <v>1</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>40</v>
@@ -20116,20 +20127,20 @@
         <v>152</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2" t="s">
         <v>76</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>510</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>76</v>
@@ -20159,7 +20170,7 @@
         <v>1</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>41</v>
@@ -20178,13 +20189,13 @@
         <v>76</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>474</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>76</v>
@@ -20199,7 +20210,7 @@
         <v>1</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>41</v>
@@ -20216,13 +20227,13 @@
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>76</v>
@@ -20237,7 +20248,7 @@
         <v>1</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>41</v>
@@ -20254,13 +20265,13 @@
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>76</v>
@@ -20275,7 +20286,7 @@
         <v>1</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>41</v>
@@ -20292,13 +20303,13 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L113" s="2" t="s">
         <v>76</v>
@@ -20313,7 +20324,7 @@
         <v>1</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>41</v>
@@ -20330,13 +20341,13 @@
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>76</v>
@@ -20351,7 +20362,7 @@
         <v>1</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>41</v>
@@ -20368,13 +20379,13 @@
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L115" s="2" t="s">
         <v>76</v>
@@ -20389,7 +20400,7 @@
         <v>1</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>41</v>
@@ -20406,13 +20417,13 @@
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
       <c r="I116" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -20438,7 +20449,7 @@
         <v>1</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>42</v>
@@ -20453,19 +20464,19 @@
         <v>414</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>76</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>513</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="L118" s="2" t="s">
         <v>76</v>
@@ -20480,7 +20491,7 @@
         <v>1</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>42</v>
@@ -20497,13 +20508,13 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
       <c r="I119" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L119" s="2" t="s">
         <v>76</v>
@@ -20518,7 +20529,7 @@
         <v>1</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>43</v>
@@ -20531,13 +20542,13 @@
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
       <c r="I120" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
@@ -20550,7 +20561,7 @@
         <v>1</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>44</v>
@@ -20565,13 +20576,13 @@
         <v>76</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>589</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="L121" s="2" t="s">
         <v>178</v>
@@ -20580,7 +20591,7 @@
         <v>164</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
@@ -20588,7 +20599,7 @@
         <v>1</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>48</v>
@@ -20598,7 +20609,7 @@
         <v>115</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2" t="s">
@@ -20608,10 +20619,10 @@
         <v>177</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="L122" s="2" t="s">
         <v>167</v>
@@ -20626,7 +20637,7 @@
         <v>1</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>49</v>
@@ -20636,7 +20647,7 @@
         <v>115</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2" t="s">
@@ -20646,10 +20657,10 @@
         <v>49</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="L123" s="2" t="s">
         <v>178</v>
@@ -20664,7 +20675,7 @@
         <v>1</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>50</v>
@@ -20674,7 +20685,7 @@
         <v>115</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2" t="s">
@@ -20684,10 +20695,10 @@
         <v>179</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="L124" s="2" t="s">
         <v>180</v>
@@ -20702,7 +20713,7 @@
         <v>1</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>51</v>
@@ -20712,7 +20723,7 @@
         <v>115</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2" t="s">
@@ -20722,10 +20733,10 @@
         <v>51</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="L125" s="2" t="s">
         <v>181</v>
@@ -20740,7 +20751,7 @@
         <v>1</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>52</v>
@@ -20750,7 +20761,7 @@
         <v>115</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2" t="s">
@@ -20760,10 +20771,10 @@
         <v>183</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="L126" s="2" t="s">
         <v>174</v>
@@ -20778,7 +20789,7 @@
         <v>1</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>53</v>
@@ -20788,7 +20799,7 @@
         <v>115</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2" t="s">
@@ -20798,10 +20809,10 @@
         <v>184</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="L127" s="2" t="s">
         <v>182</v>
@@ -20816,7 +20827,7 @@
         <v>1</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>60</v>
@@ -20826,31 +20837,31 @@
         <v>115</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>170</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="M128" s="2" t="s">
         <v>164</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
@@ -20858,7 +20869,7 @@
         <v>1</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>61</v>
@@ -20868,25 +20879,25 @@
         <v>115</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>170</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K129" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="M129" s="2" t="s">
         <v>598</v>
@@ -20900,7 +20911,7 @@
         <v>1</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>62</v>
@@ -20910,25 +20921,25 @@
         <v>115</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>170</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K130" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="M130" s="2" t="s">
         <v>600</v>
@@ -20942,7 +20953,7 @@
         <v>1</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>63</v>
@@ -20952,25 +20963,25 @@
         <v>115</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>170</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K131" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="M131" s="2" t="s">
         <v>601</v>
@@ -20984,7 +20995,7 @@
         <v>1</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>65</v>
@@ -20994,10 +21005,10 @@
         <v>115</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>170</v>
@@ -21006,13 +21017,13 @@
         <v>605</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K132" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="L132" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="M132" s="2" t="s">
         <v>164</v>
@@ -21026,7 +21037,7 @@
         <v>1</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>67</v>
@@ -21036,7 +21047,7 @@
         <v>115</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="2" t="s">
@@ -21046,10 +21057,10 @@
         <v>607</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K133" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="L133" s="2" t="s">
         <v>169</v>
@@ -21066,7 +21077,7 @@
         <v>1</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>70</v>
@@ -21076,25 +21087,25 @@
         <v>115</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>170</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K134" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M134" s="2" t="s">
         <v>164</v>
@@ -21106,7 +21117,7 @@
         <v>1</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>71</v>
@@ -21116,25 +21127,25 @@
         <v>115</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>170</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K135" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="M135" s="2" t="s">
         <v>164</v>
@@ -21146,7 +21157,7 @@
         <v>1</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>72</v>
@@ -21156,25 +21167,25 @@
         <v>115</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>170</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K136" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="M136" s="2" t="s">
         <v>164</v>
@@ -21190,8 +21201,8 @@
     <cfRule type="duplicateValues" dxfId="7" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K94">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K121:M121">
     <cfRule type="duplicateValues" dxfId="4" priority="7"/>
@@ -21229,31 +21240,31 @@
   <sheetData>
     <row r="1" spans="1:10" s="24" customFormat="1" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C1" s="26" t="s">
+        <v>642</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>708</v>
+      </c>
+      <c r="E1" s="26" t="s">
         <v>643</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="F1" s="26" t="s">
+        <v>644</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>645</v>
+      </c>
+      <c r="H1" s="26" t="s">
         <v>709</v>
       </c>
-      <c r="E1" s="26" t="s">
-        <v>644</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>645</v>
-      </c>
-      <c r="G1" s="26" t="s">
+      <c r="I1" s="26" t="s">
         <v>646</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>710</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>647</v>
       </c>
       <c r="J1" s="27" t="s">
         <v>121</v>
@@ -21266,7 +21277,7 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>284</v>
@@ -21278,7 +21289,7 @@
         <v>514</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -21288,7 +21299,7 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>285</v>
@@ -21308,7 +21319,7 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>286</v>
@@ -21328,7 +21339,7 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>287</v>
@@ -21348,7 +21359,7 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>288</v>
@@ -21368,7 +21379,7 @@
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>289</v>
@@ -21388,7 +21399,7 @@
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>290</v>
@@ -21408,7 +21419,7 @@
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>291</v>
@@ -21428,7 +21439,7 @@
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>292</v>
@@ -21448,7 +21459,7 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>293</v>
@@ -21468,7 +21479,7 @@
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>294</v>
@@ -21488,7 +21499,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>295</v>
@@ -21508,7 +21519,7 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>296</v>
@@ -21528,7 +21539,7 @@
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>297</v>
@@ -21548,7 +21559,7 @@
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>298</v>
@@ -21568,7 +21579,7 @@
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>299</v>
@@ -21588,7 +21599,7 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>300</v>
@@ -21608,7 +21619,7 @@
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>301</v>
@@ -21628,7 +21639,7 @@
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>302</v>
@@ -21648,7 +21659,7 @@
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>303</v>
@@ -21668,7 +21679,7 @@
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>304</v>
@@ -21688,7 +21699,7 @@
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>305</v>
@@ -21708,7 +21719,7 @@
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>306</v>
@@ -21728,7 +21739,7 @@
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>307</v>
@@ -21748,7 +21759,7 @@
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>308</v>
@@ -21768,7 +21779,7 @@
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>315</v>
@@ -21788,7 +21799,7 @@
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>332</v>
@@ -21808,7 +21819,7 @@
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>363</v>
@@ -21828,7 +21839,7 @@
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>337</v>
@@ -21848,7 +21859,7 @@
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>339</v>
@@ -21868,7 +21879,7 @@
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>326</v>
@@ -21888,7 +21899,7 @@
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>361</v>
@@ -21908,7 +21919,7 @@
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>323</v>
@@ -21928,7 +21939,7 @@
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>355</v>
@@ -21948,7 +21959,7 @@
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>321</v>
@@ -21968,7 +21979,7 @@
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>318</v>
@@ -21988,7 +21999,7 @@
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>365</v>
@@ -22008,7 +22019,7 @@
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>340</v>
@@ -22028,7 +22039,7 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>328</v>
@@ -22048,7 +22059,7 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>331</v>
@@ -22068,7 +22079,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>342</v>
@@ -22088,7 +22099,7 @@
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>366</v>
@@ -22108,7 +22119,7 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>334</v>
@@ -22128,7 +22139,7 @@
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>338</v>
@@ -22148,7 +22159,7 @@
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>317</v>
@@ -22168,7 +22179,7 @@
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>348</v>
@@ -22188,7 +22199,7 @@
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>325</v>
@@ -22208,7 +22219,7 @@
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>343</v>
@@ -22228,7 +22239,7 @@
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>350</v>
@@ -22248,7 +22259,7 @@
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>313</v>
@@ -22268,7 +22279,7 @@
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>336</v>
@@ -22288,7 +22299,7 @@
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>335</v>
@@ -22308,7 +22319,7 @@
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>322</v>
@@ -22328,7 +22339,7 @@
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>364</v>
@@ -22348,7 +22359,7 @@
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>329</v>
@@ -22368,7 +22379,7 @@
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>367</v>
@@ -22388,7 +22399,7 @@
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>319</v>
@@ -22408,7 +22419,7 @@
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>359</v>
@@ -22428,7 +22439,7 @@
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>368</v>
@@ -22448,7 +22459,7 @@
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>341</v>
@@ -22468,7 +22479,7 @@
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>354</v>
@@ -22488,7 +22499,7 @@
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>356</v>
@@ -22508,7 +22519,7 @@
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>358</v>
@@ -22528,7 +22539,7 @@
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>314</v>
@@ -22548,7 +22559,7 @@
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>369</v>
@@ -22568,7 +22579,7 @@
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>309</v>
@@ -22588,7 +22599,7 @@
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>310</v>
@@ -22608,7 +22619,7 @@
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>333</v>
@@ -22628,7 +22639,7 @@
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>320</v>
@@ -22648,7 +22659,7 @@
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>362</v>
@@ -22668,7 +22679,7 @@
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>349</v>
@@ -22688,7 +22699,7 @@
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>351</v>
@@ -22708,7 +22719,7 @@
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>357</v>
@@ -22728,7 +22739,7 @@
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>324</v>
@@ -22748,7 +22759,7 @@
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>330</v>
@@ -22768,7 +22779,7 @@
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>344</v>
@@ -22788,7 +22799,7 @@
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>345</v>
@@ -22808,7 +22819,7 @@
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>346</v>
@@ -22828,7 +22839,7 @@
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>347</v>
@@ -22848,7 +22859,7 @@
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>316</v>
@@ -22868,7 +22879,7 @@
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>311</v>
@@ -22888,7 +22899,7 @@
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>353</v>
@@ -22908,7 +22919,7 @@
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>360</v>
@@ -22928,7 +22939,7 @@
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>312</v>
@@ -22948,7 +22959,7 @@
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>327</v>
@@ -22968,7 +22979,7 @@
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>352</v>
@@ -22988,7 +22999,7 @@
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>370</v>
@@ -23008,7 +23019,7 @@
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>371</v>
@@ -23028,7 +23039,7 @@
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>372</v>
@@ -23048,7 +23059,7 @@
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>373</v>
@@ -23068,7 +23079,7 @@
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>374</v>
@@ -23088,7 +23099,7 @@
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>375</v>
@@ -23108,7 +23119,7 @@
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>376</v>
@@ -23128,7 +23139,7 @@
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>377</v>
@@ -23148,7 +23159,7 @@
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>378</v>
@@ -23168,7 +23179,7 @@
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>379</v>
@@ -23188,7 +23199,7 @@
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>380</v>
@@ -23208,7 +23219,7 @@
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>381</v>
@@ -23228,7 +23239,7 @@
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>382</v>
@@ -23248,7 +23259,7 @@
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>383</v>
@@ -23268,7 +23279,7 @@
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>384</v>
@@ -23288,7 +23299,7 @@
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>385</v>
@@ -23308,7 +23319,7 @@
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>386</v>
@@ -23328,7 +23339,7 @@
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>387</v>
@@ -23348,7 +23359,7 @@
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>388</v>
@@ -23368,7 +23379,7 @@
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>389</v>
@@ -23388,7 +23399,7 @@
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>270</v>
@@ -23408,7 +23419,7 @@
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>271</v>
@@ -23428,7 +23439,7 @@
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>272</v>
@@ -23448,7 +23459,7 @@
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>390</v>
@@ -23468,7 +23479,7 @@
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>391</v>
@@ -23488,7 +23499,7 @@
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>392</v>
@@ -23508,7 +23519,7 @@
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>393</v>
@@ -23528,7 +23539,7 @@
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>276</v>
@@ -23548,7 +23559,7 @@
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>277</v>
@@ -23568,7 +23579,7 @@
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>394</v>
@@ -23588,7 +23599,7 @@
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>264</v>
@@ -23600,7 +23611,7 @@
         <v>540</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
@@ -23610,7 +23621,7 @@
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>265</v>
@@ -23630,7 +23641,7 @@
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>266</v>
@@ -23650,7 +23661,7 @@
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>267</v>
@@ -23670,7 +23681,7 @@
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>268</v>
@@ -23690,7 +23701,7 @@
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>269</v>
@@ -23710,7 +23721,7 @@
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>270</v>
@@ -23730,7 +23741,7 @@
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>271</v>
@@ -23750,7 +23761,7 @@
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>272</v>
@@ -23770,7 +23781,7 @@
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>273</v>
@@ -23790,7 +23801,7 @@
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>274</v>
@@ -23810,7 +23821,7 @@
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>275</v>
@@ -23830,7 +23841,7 @@
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>276</v>
@@ -23850,7 +23861,7 @@
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>277</v>
@@ -23870,7 +23881,7 @@
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
       <c r="D132" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>278</v>
@@ -23890,7 +23901,7 @@
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>279</v>
@@ -23910,7 +23921,7 @@
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>280</v>
@@ -23930,7 +23941,7 @@
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>281</v>
@@ -23950,7 +23961,7 @@
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>282</v>
@@ -23970,7 +23981,7 @@
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>283</v>
@@ -23990,7 +24001,7 @@
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>402</v>
@@ -24002,7 +24013,7 @@
         <v>511</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
@@ -24012,7 +24023,7 @@
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>403</v>
@@ -24032,7 +24043,7 @@
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>404</v>
@@ -24052,7 +24063,7 @@
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>405</v>
@@ -24061,7 +24072,7 @@
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
       <c r="I141" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J141" s="2"/>
     </row>
@@ -24072,7 +24083,7 @@
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>406</v>
@@ -24081,7 +24092,7 @@
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
       <c r="I142" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J142" s="2"/>
     </row>
@@ -24092,7 +24103,7 @@
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>407</v>
@@ -24112,7 +24123,7 @@
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>143</v>
@@ -24132,7 +24143,7 @@
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>408</v>
@@ -24141,10 +24152,10 @@
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
       <c r="I145" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
@@ -24154,7 +24165,7 @@
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>409</v>
@@ -24163,7 +24174,7 @@
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
       <c r="I146" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J146" s="2"/>
     </row>
@@ -24174,7 +24185,7 @@
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>410</v>
@@ -24183,7 +24194,7 @@
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
       <c r="I147" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J147" s="2"/>
     </row>
@@ -24194,7 +24205,7 @@
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>411</v>
@@ -24203,7 +24214,7 @@
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
       <c r="I148" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J148" s="2"/>
     </row>
@@ -24214,7 +24225,7 @@
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
       <c r="D149" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>143</v>
@@ -24234,7 +24245,7 @@
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>402</v>
@@ -24246,7 +24257,7 @@
         <v>511</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
@@ -24256,7 +24267,7 @@
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>403</v>
@@ -24276,7 +24287,7 @@
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>404</v>
@@ -24296,7 +24307,7 @@
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>405</v>
@@ -24305,7 +24316,7 @@
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
       <c r="I153" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J153" s="2"/>
     </row>
@@ -24316,7 +24327,7 @@
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>406</v>
@@ -24325,7 +24336,7 @@
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
       <c r="I154" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J154" s="2"/>
     </row>
@@ -24336,7 +24347,7 @@
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>412</v>
@@ -24345,7 +24356,7 @@
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
       <c r="I155" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J155" s="2"/>
     </row>
@@ -24356,7 +24367,7 @@
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>409</v>
@@ -24365,7 +24376,7 @@
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
       <c r="I156" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J156" s="2"/>
     </row>
@@ -24376,7 +24387,7 @@
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>410</v>
@@ -24385,7 +24396,7 @@
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
       <c r="I157" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J157" s="2"/>
     </row>
@@ -24396,7 +24407,7 @@
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>411</v>
@@ -24405,7 +24416,7 @@
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
       <c r="I158" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J158" s="2"/>
     </row>
@@ -24416,7 +24427,7 @@
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
       <c r="D159" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>413</v>
@@ -24425,7 +24436,7 @@
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
       <c r="I159" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J159" s="2"/>
     </row>
@@ -24436,7 +24447,7 @@
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>143</v>
@@ -24456,7 +24467,7 @@
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>416</v>
@@ -24468,7 +24479,7 @@
         <v>590</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.2">
@@ -24478,7 +24489,7 @@
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>417</v>
@@ -24498,7 +24509,7 @@
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>418</v>
@@ -24518,7 +24529,7 @@
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>419</v>
@@ -24538,7 +24549,7 @@
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>420</v>
@@ -24558,7 +24569,7 @@
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>421</v>
@@ -24578,7 +24589,7 @@
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>422</v>
@@ -24598,7 +24609,7 @@
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>423</v>
@@ -24618,7 +24629,7 @@
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>424</v>
@@ -24638,7 +24649,7 @@
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>425</v>
@@ -24658,7 +24669,7 @@
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>426</v>
@@ -24678,7 +24689,7 @@
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>427</v>
@@ -24698,7 +24709,7 @@
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>416</v>
@@ -24710,7 +24721,7 @@
         <v>590</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.2">
@@ -24720,7 +24731,7 @@
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>417</v>
@@ -24740,7 +24751,7 @@
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
       <c r="D175" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>418</v>
@@ -24760,7 +24771,7 @@
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
       <c r="D176" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>419</v>
@@ -24780,7 +24791,7 @@
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>420</v>
@@ -24800,7 +24811,7 @@
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>421</v>
@@ -24820,7 +24831,7 @@
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>422</v>
@@ -24840,7 +24851,7 @@
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>423</v>
@@ -24860,7 +24871,7 @@
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>424</v>
@@ -24880,7 +24891,7 @@
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>425</v>
@@ -24900,7 +24911,7 @@
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>426</v>
@@ -24920,7 +24931,7 @@
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>427</v>
@@ -24940,7 +24951,7 @@
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>143</v>

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,22 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383E7D9C-CCD0-674C-BADD-35B80F3DFA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6A2996-92A5-AE4A-9D50-E75DBBB41723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2020" yWindow="500" windowWidth="38940" windowHeight="20920" activeTab="1" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="2020" yWindow="500" windowWidth="38940" windowHeight="20920" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
     <sheet name="wide" sheetId="2" r:id="rId2"/>
-    <sheet name="enums" sheetId="3" r:id="rId3"/>
-    <sheet name="id_gen" sheetId="4" r:id="rId4"/>
+    <sheet name="wide_qualityReports" sheetId="7" r:id="rId3"/>
+    <sheet name="enums" sheetId="3" r:id="rId4"/>
+    <sheet name="id_gen" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId6"/>
+    <sheet name="maps original" sheetId="6" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">enums!$A$1:$J$185</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maps!$A$1:$L$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">enums!$A$1:$J$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maps!$A$1:$L$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'maps original'!$A$1:$L$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">wide!$A$1:$N$136</definedName>
     <definedName name="partID">[1]parts!$A:$A</definedName>
     <definedName name="partLabel">[1]parts!$B:$B</definedName>
@@ -48,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="838">
   <si>
     <t>Reporter</t>
   </si>
@@ -2431,12 +2435,171 @@
   <si>
     <t>{"reflink_target": "{{other_norm_ref}}"}</t>
   </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>sampleID + part ID of measure + row number</t>
+  </si>
+  <si>
+    <t>siteID + collDT/collDTEnd (not including time) + index (if applicable)</t>
+  </si>
+  <si>
+    <t>country code (ISO) + province code (ISO) + first 2-3 letters of municipality + 3 first letters of site name</t>
+  </si>
+  <si>
+    <t>first 5 letters of name + protocolVersion</t>
+  </si>
+  <si>
+    <t>pmmov1</t>
+  </si>
+  <si>
+    <t>caOnOttOtt20200802Covn1002</t>
+  </si>
+  <si>
+    <t>caOnOttOtt20200801</t>
+  </si>
+  <si>
+    <t>caOnOttOtt</t>
+  </si>
+  <si>
+    <t>orgID + siteID</t>
+  </si>
+  <si>
+    <t>caOnOtt002UniCaOnOttOtt</t>
+  </si>
+  <si>
+    <t>datasetID = orgID</t>
+  </si>
+  <si>
+    <t>caOnOtt002Uni</t>
+  </si>
+  <si>
+    <t>Report ID of first measure in the set + # measures in the set</t>
+  </si>
+  <si>
+    <t>caOnOttOtt20200801Covn1002003</t>
+  </si>
+  <si>
+    <t>addID + first 3 letters of name</t>
+  </si>
+  <si>
+    <t>caOnOtt002UniRes</t>
+  </si>
+  <si>
+    <t>orgID + first 3 letters of role</t>
+  </si>
+  <si>
+    <t>ID Example</t>
+  </si>
+  <si>
+    <t>ID Formula</t>
+  </si>
+  <si>
+    <t>id:measureRepID</t>
+  </si>
+  <si>
+    <t>id:polygonID</t>
+  </si>
+  <si>
+    <t>id:datasetID</t>
+  </si>
+  <si>
+    <t>id:measureSetRepID</t>
+  </si>
+  <si>
+    <t>id:stepID</t>
+  </si>
+  <si>
+    <t>id:instrumentID</t>
+  </si>
+  <si>
+    <t>id:qualityReportID</t>
+  </si>
+  <si>
+    <t>id:addressID</t>
+  </si>
+  <si>
+    <t>country code + province code + 2-3 letters of municipality + row</t>
+  </si>
+  <si>
+    <t>caOnOtt002</t>
+  </si>
+  <si>
+    <t>first 3 letters of manufacturer + first 3 letters of name + first 3 letters of model + index</t>
+  </si>
+  <si>
+    <t>fisHanHan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orgID + last 3 letters of part ID of method/measure	</t>
+  </si>
+  <si>
+    <t>caOnOtt002UniIon</t>
+  </si>
+  <si>
+    <t>quality flag part ID + either the measure report ID, the sample ID, or measure set report ID that the quality report is for</t>
+  </si>
+  <si>
+    <t>flagJcaOnOttOttawasite1202008021000covN1002</t>
+  </si>
+  <si>
+    <t>qualityFlag_target</t>
+  </si>
+  <si>
+    <t>{{qc_ignore}}</t>
+  </si>
+  <si>
+    <t>{{id:qualityReportID1}}</t>
+  </si>
+  <si>
+    <t>{{id:qualityReportID2}}</t>
+  </si>
+  <si>
+    <t>{{pcr_target_below_lod}}</t>
+  </si>
+  <si>
+    <t>{{id:qualityReportID3}}</t>
+  </si>
+  <si>
+    <t>{{ntc_amplify}}</t>
+  </si>
+  <si>
+    <t>{{inhibition_detect}}</t>
+  </si>
+  <si>
+    <t>{{id:qualityReportID4}}</t>
+  </si>
+  <si>
+    <t>flagAI OR flagFI</t>
+  </si>
+  <si>
+    <t>{{inhibition_adjust}}</t>
+  </si>
+  <si>
+    <t>{{id:qualityReportID5}}</t>
+  </si>
+  <si>
+    <t>qualityReportID_target</t>
+  </si>
+  <si>
+    <t>{{id:qualityReportID6}}</t>
+  </si>
+  <si>
+    <t>{{quality_flag}}</t>
+  </si>
+  <si>
+    <t>&lt;empty&gt;</t>
+  </si>
+  <si>
+    <t>Added by Martin</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2515,8 +2678,15 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2544,6 +2714,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2634,7 +2810,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2685,11 +2861,23 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -13943,7 +14131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}">
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="27.1640625" customWidth="1"/>
@@ -14028,25 +14216,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -14057,99 +14245,93 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="21" t="s">
-        <v>740</v>
-      </c>
+      <c r="F4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="L4" s="19" t="s">
-        <v>735</v>
-      </c>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="b">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>76</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
+      <c r="L5" t="s">
+        <v>837</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" t="b">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>712</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="A7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>710</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -14165,23 +14347,26 @@
         <v>635</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" s="2"/>
+      <c r="G8" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="21" t="s">
+        <v>740</v>
+      </c>
       <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="K8" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="b">
@@ -14194,19 +14379,19 @@
         <v>635</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>83</v>
+        <v>10</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>83</v>
+        <v>711</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -14214,7 +14399,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>1</v>
@@ -14223,24 +14408,23 @@
         <v>635</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="F10" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>732</v>
-      </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
+        <v>81</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="22" t="s">
-        <v>733</v>
-      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B11" s="2"/>
@@ -14249,43 +14433,39 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="23"/>
-    </row>
-    <row r="12" spans="1:12" s="23" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>635</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" s="28" t="s">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G12" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="19" t="s">
-        <v>738</v>
-      </c>
+      <c r="G12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="b">
@@ -14298,19 +14478,19 @@
         <v>635</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>86</v>
+        <v>13</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -14318,7 +14498,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>1</v>
@@ -14327,139 +14507,110 @@
         <v>635</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>87</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
       <c r="K14" s="2"/>
+      <c r="L14" s="22" t="s">
+        <v>733</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" t="b">
-        <v>1</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
       <c r="K15" s="2"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="b">
         <v>1</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="22" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="23"/>
+    </row>
+    <row r="18" spans="1:12" s="23" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>635</v>
+      </c>
+      <c r="D18" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="E18" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G18" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" t="b">
-        <v>1</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" t="b">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
+      <c r="H18" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="19" t="s">
+        <v>738</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="b">
@@ -14475,7 +14626,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>77</v>
@@ -14484,7 +14635,7 @@
         <v>101</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -14503,8 +14654,8 @@
       <c r="D20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>93</v>
+      <c r="E20" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>77</v>
@@ -14513,7 +14664,7 @@
         <v>101</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -14532,8 +14683,8 @@
       <c r="D21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>94</v>
+      <c r="E21" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>77</v>
@@ -14542,7 +14693,7 @@
         <v>101</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -14561,8 +14712,8 @@
       <c r="D22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>95</v>
+      <c r="E22" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>77</v>
@@ -14571,7 +14722,7 @@
         <v>101</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
@@ -14591,7 +14742,7 @@
         <v>15</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>77</v>
@@ -14600,7 +14751,7 @@
         <v>101</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -14620,7 +14771,7 @@
         <v>15</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>77</v>
@@ -14629,7 +14780,7 @@
         <v>101</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -14648,8 +14799,8 @@
       <c r="D25" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>98</v>
+      <c r="E25" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>77</v>
@@ -14658,7 +14809,7 @@
         <v>101</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -14677,8 +14828,8 @@
       <c r="D26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>99</v>
+      <c r="E26" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>77</v>
@@ -14687,136 +14838,152 @@
         <v>101</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="28" t="s">
-        <v>635</v>
-      </c>
-      <c r="D27" s="28" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" t="b">
+        <v>1</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" s="28" t="s">
+      <c r="E27" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G27" s="28" t="s">
+      <c r="G27" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H27" s="31" t="s">
-        <v>533</v>
-      </c>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="19" t="s">
-        <v>739</v>
-      </c>
+      <c r="H27" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
+      <c r="A28" t="b">
+        <v>1</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="F29" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>728</v>
+        <v>106</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="7" t="s">
-        <v>117</v>
-      </c>
+      <c r="K29" s="2"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="F30" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>729</v>
+        <v>111</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="7" t="s">
-        <v>117</v>
-      </c>
+      <c r="K30" s="2"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="b">
         <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="F31" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>713</v>
+        <v>98</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -14827,178 +14994,187 @@
         <v>1</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="F32" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>730</v>
+        <v>101</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>714</v>
+        <v>112</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" t="b">
-        <v>1</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="H33" s="6"/>
-      <c r="I33" s="20" t="s">
-        <v>707</v>
-      </c>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" t="b">
-        <v>1</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D34" s="21"/>
+    <row r="33" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>635</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="H33" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="19" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
       <c r="E34" s="3"/>
-      <c r="F34" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H34" s="2"/>
-      <c r="I34" s="20" t="s">
-        <v>708</v>
-      </c>
-      <c r="J34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>76</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>715</v>
+        <v>728</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
+      <c r="K35" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36" t="b">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>729</v>
+      </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K36" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="b">
         <v>1</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>122</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>137</v>
+        <v>713</v>
       </c>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="b">
         <v>1</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>123</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>130</v>
+        <v>730</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>135</v>
+        <v>714</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="b">
         <v>1</v>
       </c>
@@ -15008,26 +15184,22 @@
       <c r="C39" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>124</v>
-      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
         <v>118</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I39" s="2"/>
+        <v>683</v>
+      </c>
+      <c r="H39" s="6"/>
+      <c r="I39" s="20" t="s">
+        <v>707</v>
+      </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="b">
         <v>1</v>
       </c>
@@ -15037,26 +15209,22 @@
       <c r="C40" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>125</v>
-      </c>
+      <c r="D40" s="21"/>
+      <c r="E40" s="3"/>
       <c r="F40" s="2" t="s">
         <v>118</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I40" s="2"/>
+        <v>119</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="20" t="s">
+        <v>708</v>
+      </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="b">
         <v>1</v>
       </c>
@@ -15067,54 +15235,37 @@
         <v>635</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>118</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>133</v>
+        <v>715</v>
       </c>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" t="b">
-        <v>1</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>134</v>
-      </c>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="b">
         <v>1</v>
       </c>
@@ -15127,8 +15278,8 @@
       <c r="D43" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>128</v>
+      <c r="E43" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>118</v>
@@ -15137,13 +15288,13 @@
         <v>130</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="b">
         <v>1</v>
       </c>
@@ -15157,7 +15308,7 @@
         <v>24</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>118</v>
@@ -15166,194 +15317,228 @@
         <v>130</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A45" t="b">
+        <v>1</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D46" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>76</v>
+      <c r="D46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>118</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H46" s="2"/>
-      <c r="I46" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I46" s="2"/>
       <c r="J46" s="2"/>
-      <c r="K46" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K46" s="2"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>118</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H47" s="2"/>
-      <c r="I47" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I47" s="2"/>
       <c r="J47" s="2"/>
-      <c r="K47" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>118</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H48" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
-      <c r="K48" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" t="b">
+        <v>1</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
-      <c r="K49" s="1"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="b">
         <v>1</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>118</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>716</v>
+        <v>136</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A51" t="b">
-        <v>1</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>717</v>
-      </c>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
+    <row r="52" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" t="b">
+        <v>0</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
+      <c r="I52" s="17"/>
       <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K52" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="b">
         <v>0</v>
       </c>
@@ -15364,30 +15549,25 @@
         <v>635</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="I53" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="H53" s="2"/>
+      <c r="I53" s="17"/>
       <c r="J53" s="2"/>
-      <c r="K53" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="L53" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K53" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="b">
         <v>0</v>
       </c>
@@ -15398,70 +15578,66 @@
         <v>635</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>150</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A55" t="b">
-        <v>0</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>150</v>
-      </c>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-      <c r="K55" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
+      <c r="K55" s="1"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A56" t="b">
+        <v>1</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>716</v>
+      </c>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
-      <c r="K56" s="1"/>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K56" s="2"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="b">
         <v>1</v>
       </c>
@@ -15471,57 +15647,40 @@
       <c r="C57" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
+      <c r="D57" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="F57" s="2" t="s">
         <v>118</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2" t="s">
-        <v>694</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="I57" s="2"/>
       <c r="J57" s="2"/>
-      <c r="K57" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A58" t="b">
-        <v>0</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H58" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="K57" s="2"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
-      <c r="K58" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K58" s="2"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>4</v>
@@ -15529,40 +15688,55 @@
       <c r="C59" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>143</v>
-      </c>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
         <v>118</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H59" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2" t="s">
+        <v>694</v>
+      </c>
       <c r="J59" s="2"/>
       <c r="K59" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60" t="b">
+        <v>0</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H60" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
-      <c r="K60" s="1"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K60" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="b">
         <v>0</v>
       </c>
@@ -15573,10 +15747,10 @@
         <v>635</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>118</v>
@@ -15585,7 +15759,7 @@
         <v>145</v>
       </c>
       <c r="H61" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
@@ -15593,38 +15767,19 @@
         <v>146</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A62" t="b">
-        <v>0</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H62" s="2" t="b">
-        <v>1</v>
-      </c>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
-      <c r="K62" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K62" s="1"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="b">
         <v>0</v>
       </c>
@@ -15638,7 +15793,7 @@
         <v>58</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>118</v>
@@ -15647,7 +15802,7 @@
         <v>145</v>
       </c>
       <c r="H63" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -15655,46 +15810,67 @@
         <v>146</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64" t="b">
+        <v>0</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H64" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
-      <c r="K64" s="1"/>
+      <c r="K64" s="1" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>718</v>
+        <v>145</v>
+      </c>
+      <c r="H65" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
+      <c r="K65" s="1" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B66" s="2"/>
@@ -15706,22 +15882,22 @@
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
+      <c r="K66" s="1"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="b">
         <v>0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E67" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F67" s="2" t="s">
@@ -15731,12 +15907,15 @@
         <v>148</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>596</v>
+        <v>149</v>
       </c>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
-      <c r="K67" s="1" t="s">
-        <v>597</v>
+      <c r="K67" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="L67" s="19" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
@@ -15744,15 +15923,15 @@
         <v>0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E68" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>142</v>
       </c>
       <c r="F68" s="2" t="s">
@@ -15762,26 +15941,28 @@
         <v>148</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>598</v>
+        <v>150</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
+      <c r="K68" s="1" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" t="b">
         <v>0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E69" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F69" s="2" t="s">
@@ -15790,24 +15971,26 @@
       <c r="G69" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="H69" s="6" t="s">
-        <v>598</v>
+      <c r="H69" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
+      <c r="K69" s="1" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
+      <c r="K70" s="1"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="b">
@@ -15820,7 +16003,7 @@
         <v>635</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>141</v>
@@ -15832,7 +16015,7 @@
         <v>148</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
@@ -15851,7 +16034,7 @@
         <v>635</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>142</v>
@@ -15862,7 +16045,7 @@
       <c r="G72" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="H72" s="6" t="s">
+      <c r="H72" s="2" t="s">
         <v>598</v>
       </c>
       <c r="I72" s="2"/>
@@ -15870,46 +16053,45 @@
       <c r="K72" s="2"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="2"/>
+      <c r="A73" t="b">
+        <v>0</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>598</v>
+      </c>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="1:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" t="b">
-        <v>1</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>635</v>
-      </c>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="3"/>
-      <c r="F74" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>148</v>
-      </c>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
       <c r="H74" s="2"/>
-      <c r="I74" s="17" t="s">
-        <v>736</v>
-      </c>
+      <c r="I74" s="2"/>
       <c r="J74" s="2"/>
-      <c r="K74" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="L74" s="19" t="s">
-        <v>737</v>
-      </c>
+      <c r="K74" s="2"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" t="b">
@@ -15922,10 +16104,10 @@
         <v>635</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>147</v>
@@ -15934,12 +16116,12 @@
         <v>148</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>150</v>
+        <v>602</v>
       </c>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="1" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
@@ -15953,10 +16135,10 @@
         <v>635</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>603</v>
+        <v>142</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>147</v>
@@ -15967,25 +16149,23 @@
       <c r="H76" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="1" t="s">
-        <v>606</v>
-      </c>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="3"/>
-      <c r="F77" s="2"/>
+      <c r="F77" s="6"/>
       <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="1"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+    </row>
+    <row r="78" spans="1:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="b">
         <v>0</v>
       </c>
@@ -15995,25 +16175,24 @@
       <c r="C78" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>141</v>
-      </c>
+      <c r="D78" s="2"/>
+      <c r="E78" s="3"/>
       <c r="F78" s="2" t="s">
         <v>147</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="H78" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="I78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="17" t="s">
+        <v>736</v>
+      </c>
       <c r="J78" s="2"/>
       <c r="K78" s="1" t="s">
-        <v>606</v>
+        <v>734</v>
+      </c>
+      <c r="L78" s="19" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -16027,7 +16206,7 @@
         <v>635</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>142</v>
@@ -16039,7 +16218,7 @@
         <v>148</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>605</v>
+        <v>150</v>
       </c>
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
@@ -16058,10 +16237,10 @@
         <v>635</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>143</v>
+        <v>603</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>147</v>
@@ -16069,11 +16248,11 @@
       <c r="G80" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
+      <c r="H80" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
       <c r="K80" s="1" t="s">
         <v>606</v>
       </c>
@@ -16085,9 +16264,9 @@
       <c r="E81" s="3"/>
       <c r="F81" s="2"/>
       <c r="G81" s="6"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
       <c r="K81" s="1"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
@@ -16101,9 +16280,9 @@
         <v>635</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E82" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>141</v>
       </c>
       <c r="F82" s="2" t="s">
@@ -16113,12 +16292,12 @@
         <v>148</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>149</v>
+        <v>604</v>
       </c>
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="1" t="s">
-        <v>153</v>
+        <v>606</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
@@ -16132,9 +16311,9 @@
         <v>635</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E83" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>142</v>
       </c>
       <c r="F83" s="2" t="s">
@@ -16144,12 +16323,12 @@
         <v>148</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>150</v>
+        <v>605</v>
       </c>
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="1" t="s">
-        <v>153</v>
+        <v>606</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
@@ -16163,9 +16342,9 @@
         <v>635</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E84" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>143</v>
       </c>
       <c r="F84" s="2" t="s">
@@ -16175,21 +16354,21 @@
         <v>148</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="1" t="s">
-        <v>153</v>
+        <v>606</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
+      <c r="E85" s="3"/>
       <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
+      <c r="G85" s="6"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
@@ -16197,7 +16376,7 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>5</v>
@@ -16206,25 +16385,29 @@
         <v>635</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E86" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="F86" s="2" t="s">
-        <v>474</v>
+        <v>147</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>473</v>
+        <v>148</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>719</v>
+        <v>149</v>
       </c>
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
+      <c r="K86" s="1" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>5</v>
@@ -16233,27 +16416,385 @@
         <v>635</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E87" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="F87" s="2" t="s">
-        <v>476</v>
+        <v>147</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>475</v>
+        <v>148</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>720</v>
+        <v>150</v>
       </c>
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
-      <c r="L87" s="23"/>
+      <c r="K87" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A88" t="b">
+        <v>0</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="1"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A90" t="b">
+        <v>1</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A91" t="b">
+        <v>1</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
+      <c r="L91" s="23"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A93" t="b">
+        <v>1</v>
+      </c>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="H93" s="2" t="str">
+        <f>"{{"&amp;D93&amp;"}}"</f>
+        <v>{{id:datasetID}}</v>
+      </c>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A94" t="b">
+        <v>1</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="H94" s="2" t="str">
+        <f t="shared" ref="H94:H101" si="0">"{{"&amp;D94&amp;"}}"</f>
+        <v>{{id:addressID}}</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A95" t="b">
+        <v>1</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="H95" s="2" t="str">
+        <f>"{{"&amp;D95&amp;"}}"</f>
+        <v>{{id:datasetID}}</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A96" t="b">
+        <v>1</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="H96" s="2" t="str">
+        <f>"{{"&amp;D96&amp;"}}"</f>
+        <v>{{id:measureRepID}}</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" t="b">
+        <v>1</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D97" t="s">
+        <v>808</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="H97" s="2" t="str">
+        <f>"{{"&amp;D97&amp;"}}"</f>
+        <v>{{id:measureSetRepID}}</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98" t="b">
+        <v>1</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="H98" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>{{id:measureRepID}}</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" t="b">
+        <v>1</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D99" t="s">
+        <v>808</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="H99" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>{{id:measureSetRepID}}</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100" t="b">
+        <v>1</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="H100" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>{{id:instrumentID}}</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A101" t="b">
+        <v>1</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="H101" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>{{id:stepID}}</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A102" t="b">
+        <v>1</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="H102" s="2" t="str">
+        <f>"{{"&amp;D102&amp;"}}"</f>
+        <v>{{id:datasetID}}</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A103" t="b">
+        <v>1</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="H103" s="2" t="str">
+        <f>"{{"&amp;D103&amp;"}}"</f>
+        <v>{{id:datasetID}}</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A104" t="b">
+        <v>1</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="H104" s="2" t="str">
+        <f>"{{"&amp;D104&amp;"}}"</f>
+        <v>{{id:datasetID}}</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L87" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}"/>
-  <conditionalFormatting sqref="H37:J37">
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+  <autoFilter ref="A1:L91" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}"/>
+  <conditionalFormatting sqref="H43:J43">
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -16768,7 +17309,7 @@
         <v>28</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>143</v>
+        <v>836</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>152</v>
@@ -19262,7 +19803,7 @@
         <v>37</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>143</v>
+        <v>836</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>152</v>
@@ -19887,7 +20428,7 @@
         <v>38</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>143</v>
+        <v>836</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>152</v>
@@ -21283,26 +21824,26 @@
     <sortCondition ref="D99:D105"/>
   </sortState>
   <conditionalFormatting sqref="I99:J99">
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K94">
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
     <cfRule type="duplicateValues" dxfId="6" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K121:M121">
-    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L122 I122:J122 L127:L128">
-    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L134">
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L135">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L136">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -21310,6 +21851,432 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4CA3B6-4765-0A43-8534-6DA7BF8A336D}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="24" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>680</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>833</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>821</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H2" t="s">
+        <v>823</v>
+      </c>
+      <c r="I2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>635</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>635</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>836</v>
+      </c>
+      <c r="E4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>635</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" t="s">
+        <v>596</v>
+      </c>
+      <c r="H5" t="s">
+        <v>824</v>
+      </c>
+      <c r="I5" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>635</v>
+      </c>
+      <c r="C6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>635</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" t="s">
+        <v>836</v>
+      </c>
+      <c r="E7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>635</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8" t="s">
+        <v>147</v>
+      </c>
+      <c r="F8" t="s">
+        <v>602</v>
+      </c>
+      <c r="H8" t="s">
+        <v>826</v>
+      </c>
+      <c r="I8" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>635</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" t="s">
+        <v>147</v>
+      </c>
+      <c r="F9" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>635</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F10" t="s">
+        <v>830</v>
+      </c>
+      <c r="H10" t="s">
+        <v>829</v>
+      </c>
+      <c r="I10" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>635</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>635</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>603</v>
+      </c>
+      <c r="E12" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>635</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F13" t="s">
+        <v>604</v>
+      </c>
+      <c r="H13" t="s">
+        <v>832</v>
+      </c>
+      <c r="I13" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>635</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
+        <v>836</v>
+      </c>
+      <c r="E15" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>635</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>141</v>
+      </c>
+      <c r="E16" t="s">
+        <v>147</v>
+      </c>
+      <c r="F16" t="s">
+        <v>149</v>
+      </c>
+      <c r="H16" t="s">
+        <v>834</v>
+      </c>
+      <c r="I16" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>635</v>
+      </c>
+      <c r="C17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>635</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>836</v>
+      </c>
+      <c r="E18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F18" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC10C3F-0C27-5546-8767-E60C7CACEA9D}">
   <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -25056,29 +26023,41 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{077DB476-AE11-E742-9E3D-7ABA37A90AEF}">
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" customWidth="1"/>
+    <col min="6" max="6" width="27.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="23" t="s">
         <v>765</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="23" t="s">
         <v>638</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="23" t="s">
         <v>639</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="23" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="23" t="s">
+        <v>785</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>803</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="b">
         <v>1</v>
       </c>
@@ -25088,634 +26067,833 @@
       <c r="C2" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2" t="s">
+        <v>812</v>
+      </c>
+      <c r="F2" t="s">
+        <v>814</v>
+      </c>
+      <c r="G2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>79</v>
       </c>
       <c r="C3" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" t="s">
+        <v>742</v>
+      </c>
+      <c r="E5" t="s">
+        <v>805</v>
+      </c>
+      <c r="F5" t="s">
+        <v>791</v>
+      </c>
+      <c r="G5" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" t="s">
+        <v>473</v>
+      </c>
+      <c r="D6" t="s">
+        <v>719</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>719</v>
+      </c>
+      <c r="F6" t="s">
+        <v>790</v>
+      </c>
+      <c r="G6" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" t="s">
+        <v>716</v>
+      </c>
+      <c r="F7" t="s">
+        <v>792</v>
+      </c>
+      <c r="G7" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" t="s">
+        <v>745</v>
+      </c>
+      <c r="E8" t="s">
+        <v>806</v>
+      </c>
+      <c r="F8" t="s">
+        <v>795</v>
+      </c>
+      <c r="G8" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" t="s">
+        <v>710</v>
+      </c>
+      <c r="F9" t="s">
+        <v>793</v>
+      </c>
+      <c r="G9" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" t="s">
+        <v>743</v>
+      </c>
+      <c r="E10" t="s">
+        <v>807</v>
+      </c>
+      <c r="F10" t="s">
+        <v>797</v>
+      </c>
+      <c r="G10" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" t="s">
+        <v>744</v>
+      </c>
+      <c r="E11" t="s">
+        <v>808</v>
+      </c>
+      <c r="F11" t="s">
+        <v>799</v>
+      </c>
+      <c r="G11" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E12" t="s">
+        <v>717</v>
+      </c>
+      <c r="F12" t="s">
+        <v>797</v>
+      </c>
+      <c r="G12" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" t="s">
+        <v>731</v>
+      </c>
+      <c r="D13" t="s">
+        <v>709</v>
+      </c>
+      <c r="E13" t="s">
+        <v>709</v>
+      </c>
+      <c r="F13" t="s">
+        <v>801</v>
+      </c>
+      <c r="G13" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>476</v>
+      </c>
+      <c r="C15" t="s">
+        <v>750</v>
+      </c>
+      <c r="E15" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>476</v>
+      </c>
+      <c r="C16" t="s">
+        <v>473</v>
+      </c>
+      <c r="D16" t="s">
+        <v>719</v>
+      </c>
+      <c r="E16" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>476</v>
+      </c>
+      <c r="C17" t="s">
+        <v>743</v>
+      </c>
+      <c r="E17" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>476</v>
+      </c>
+      <c r="C18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E18" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="b">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>476</v>
+      </c>
+      <c r="C19" t="s">
+        <v>731</v>
+      </c>
+      <c r="E19" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="b">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" t="s">
+        <v>752</v>
+      </c>
+      <c r="E21" t="s">
+        <v>809</v>
+      </c>
+      <c r="F21" t="s">
+        <v>818</v>
+      </c>
+      <c r="G21" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="b">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" t="s">
+        <v>144</v>
+      </c>
+      <c r="E22" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="b">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" t="s">
+        <v>731</v>
+      </c>
+      <c r="E23" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="b">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" t="s">
+        <v>753</v>
+      </c>
+      <c r="E24" t="s">
+        <v>810</v>
+      </c>
+      <c r="F24" t="s">
+        <v>816</v>
+      </c>
+      <c r="G24" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="b">
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" t="s">
+        <v>749</v>
+      </c>
+      <c r="E26" t="s">
+        <v>811</v>
+      </c>
+      <c r="F26" t="s">
+        <v>820</v>
+      </c>
+      <c r="G26" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="b">
+        <v>1</v>
+      </c>
+      <c r="B27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" t="s">
+        <v>742</v>
+      </c>
+      <c r="E27" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="b">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" t="s">
+        <v>140</v>
+      </c>
+      <c r="E28" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="b">
+        <v>1</v>
+      </c>
+      <c r="B29" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" t="s">
+        <v>744</v>
+      </c>
+      <c r="E29" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="b">
+        <v>1</v>
+      </c>
+      <c r="B31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" t="s">
+        <v>716</v>
+      </c>
+      <c r="E31" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="b">
+        <v>1</v>
+      </c>
+      <c r="B32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" t="s">
+        <v>473</v>
+      </c>
+      <c r="E32" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="b">
+        <v>1</v>
+      </c>
+      <c r="B33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" t="s">
+        <v>717</v>
+      </c>
+      <c r="E33" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" t="b">
+        <v>1</v>
+      </c>
+      <c r="B34" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" t="s">
+        <v>731</v>
+      </c>
+      <c r="E34" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="b">
+        <v>1</v>
+      </c>
+      <c r="B35" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" t="b">
+        <v>1</v>
+      </c>
+      <c r="B36" t="s">
+        <v>118</v>
+      </c>
+      <c r="C36" t="s">
+        <v>743</v>
+      </c>
+      <c r="E36" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" t="b">
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" t="b">
+        <v>1</v>
+      </c>
+      <c r="B39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" t="s">
+        <v>710</v>
+      </c>
+      <c r="E39" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" t="b">
+        <v>1</v>
+      </c>
+      <c r="B40" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" t="s">
+        <v>743</v>
+      </c>
+      <c r="E40" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" t="b">
+        <v>1</v>
+      </c>
+      <c r="B41" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" t="s">
+        <v>745</v>
+      </c>
+      <c r="E41" t="s">
+        <v>806</v>
+      </c>
+      <c r="F41" t="s">
+        <v>795</v>
+      </c>
+      <c r="G41" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" t="b">
+        <v>1</v>
+      </c>
+      <c r="B42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" t="s">
+        <v>747</v>
+      </c>
+      <c r="E42" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" t="b">
+        <v>1</v>
+      </c>
+      <c r="B43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" t="b">
+        <v>1</v>
+      </c>
+      <c r="B44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" t="s">
+        <v>731</v>
+      </c>
+      <c r="E44" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" t="b">
+        <v>1</v>
+      </c>
+      <c r="B45" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" t="b">
+        <v>1</v>
+      </c>
+      <c r="B46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B48" s="32" t="s">
         <v>757</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C48" s="32" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C6" t="s">
+    <row r="49" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C49" s="32" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C7" t="s">
+    <row r="50" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C50" s="32" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="b">
+    <row r="52" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B52" s="32" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="b">
+    <row r="54" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B54" s="32" t="s">
         <v>756</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C54" s="32" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C12" t="s">
+    <row r="55" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C55" s="32" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C13" t="s">
+    <row r="56" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C56" s="32" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C14" t="s">
+    <row r="57" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C57" s="32" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C15" t="s">
+    <row r="58" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C58" s="32" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C16" t="s">
+    <row r="59" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C59" s="32" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="b">
+    <row r="61" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B61" s="32" t="s">
         <v>758</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C61" s="32" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C19" t="s">
+    <row r="62" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C62" s="32" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C20" t="s">
+    <row r="63" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C63" s="32" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C21" t="s">
+    <row r="64" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C64" s="32" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" t="b">
+    <row r="66" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B66" s="32" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B25" t="s">
-        <v>115</v>
-      </c>
-      <c r="C25" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" t="b">
-        <v>1</v>
-      </c>
-      <c r="B26" t="s">
-        <v>115</v>
-      </c>
-      <c r="C26" t="s">
+    <row r="68" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="B68" s="32" t="s">
+        <v>755</v>
+      </c>
+      <c r="C68" s="32" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C69" s="32" t="s">
         <v>473</v>
       </c>
-      <c r="D26" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" t="b">
-        <v>1</v>
-      </c>
-      <c r="B27" t="s">
-        <v>115</v>
-      </c>
-      <c r="C27" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" t="b">
-        <v>1</v>
-      </c>
-      <c r="B28" t="s">
-        <v>115</v>
-      </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="70" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C70" s="32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C71" s="32" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="B73" s="32" t="s">
+        <v>741</v>
+      </c>
+      <c r="C73" s="32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C74" s="32" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C75" s="32" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="B77" s="32" t="s">
+        <v>759</v>
+      </c>
+      <c r="C77" s="32" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" t="b">
-        <v>1</v>
-      </c>
-      <c r="B29" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" t="b">
-        <v>1</v>
-      </c>
-      <c r="B30" t="s">
-        <v>115</v>
-      </c>
-      <c r="C30" t="s">
+    <row r="78" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C78" s="32" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" t="b">
-        <v>1</v>
-      </c>
-      <c r="B31" t="s">
-        <v>115</v>
-      </c>
-      <c r="C31" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" t="b">
-        <v>1</v>
-      </c>
-      <c r="B32" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" t="s">
+    <row r="79" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C79" s="32" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" t="b">
-        <v>1</v>
-      </c>
-      <c r="B33" t="s">
-        <v>115</v>
-      </c>
-      <c r="C33" t="s">
+    <row r="80" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C80" s="32" t="s">
         <v>731</v>
       </c>
-      <c r="D33" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" t="b">
+    </row>
+    <row r="82" spans="1:2" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="B35" t="s">
-        <v>755</v>
-      </c>
-      <c r="C35" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C36" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C37" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C38" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" t="b">
+      <c r="B82" s="32" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="B40" t="s">
-        <v>741</v>
-      </c>
-      <c r="C40" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C41" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C42" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" t="b">
+      <c r="B84" s="32" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="B44" t="s">
-        <v>759</v>
-      </c>
-      <c r="C44" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C45" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" t="b">
+      <c r="B86" s="32" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="B49" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" t="b">
-        <v>1</v>
-      </c>
-      <c r="B51" t="s">
-        <v>476</v>
-      </c>
-      <c r="C51" t="s">
-        <v>750</v>
-      </c>
-      <c r="E51" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" t="b">
-        <v>1</v>
-      </c>
-      <c r="B52" t="s">
-        <v>476</v>
-      </c>
-      <c r="C52" t="s">
-        <v>473</v>
-      </c>
-      <c r="D52" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" t="b">
-        <v>1</v>
-      </c>
-      <c r="B53" t="s">
-        <v>476</v>
-      </c>
-      <c r="C53" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" t="b">
-        <v>1</v>
-      </c>
-      <c r="B54" t="s">
-        <v>476</v>
-      </c>
-      <c r="C54" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" t="b">
-        <v>1</v>
-      </c>
-      <c r="B55" t="s">
-        <v>476</v>
-      </c>
-      <c r="C55" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" t="b">
-        <v>1</v>
-      </c>
-      <c r="B57" t="s">
-        <v>152</v>
-      </c>
-      <c r="C57" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" t="b">
-        <v>1</v>
-      </c>
-      <c r="B58" t="s">
-        <v>152</v>
-      </c>
-      <c r="C58" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" t="b">
-        <v>1</v>
-      </c>
-      <c r="B59" t="s">
-        <v>152</v>
-      </c>
-      <c r="C59" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" t="b">
-        <v>1</v>
-      </c>
-      <c r="B60" t="s">
-        <v>152</v>
-      </c>
-      <c r="C60" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" t="b">
-        <v>1</v>
-      </c>
-      <c r="B62" t="s">
-        <v>147</v>
-      </c>
-      <c r="C62" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" t="b">
-        <v>1</v>
-      </c>
-      <c r="B63" t="s">
-        <v>147</v>
-      </c>
-      <c r="C63" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" t="b">
-        <v>1</v>
-      </c>
-      <c r="B64" t="s">
-        <v>147</v>
-      </c>
-      <c r="C64" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" t="b">
-        <v>1</v>
-      </c>
-      <c r="B65" t="s">
-        <v>147</v>
-      </c>
-      <c r="C65" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" t="b">
-        <v>0</v>
-      </c>
-      <c r="B67" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" t="b">
-        <v>1</v>
-      </c>
-      <c r="B69" t="s">
-        <v>118</v>
-      </c>
-      <c r="C69" t="s">
-        <v>140</v>
-      </c>
-      <c r="D69" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" t="b">
-        <v>1</v>
-      </c>
-      <c r="B70" t="s">
-        <v>118</v>
-      </c>
-      <c r="C70" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" t="b">
-        <v>1</v>
-      </c>
-      <c r="B71" t="s">
-        <v>118</v>
-      </c>
-      <c r="C71" t="s">
-        <v>144</v>
-      </c>
-      <c r="D71" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" t="b">
-        <v>1</v>
-      </c>
-      <c r="B72" t="s">
-        <v>118</v>
-      </c>
-      <c r="C72" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" t="b">
-        <v>1</v>
-      </c>
-      <c r="B73" t="s">
-        <v>118</v>
-      </c>
-      <c r="C73" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" t="b">
-        <v>1</v>
-      </c>
-      <c r="B74" t="s">
-        <v>118</v>
-      </c>
-      <c r="C74" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" t="b">
-        <v>1</v>
-      </c>
-      <c r="B76" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" t="b">
-        <v>1</v>
-      </c>
-      <c r="B77" t="s">
-        <v>77</v>
-      </c>
-      <c r="C77" t="s">
-        <v>78</v>
-      </c>
-      <c r="D77" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" t="b">
-        <v>1</v>
-      </c>
-      <c r="B78" t="s">
-        <v>77</v>
-      </c>
-      <c r="C78" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" t="b">
-        <v>1</v>
-      </c>
-      <c r="B79" t="s">
-        <v>77</v>
-      </c>
-      <c r="C79" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" t="b">
-        <v>1</v>
-      </c>
-      <c r="B80" t="s">
-        <v>77</v>
-      </c>
-      <c r="C80" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A81" t="b">
-        <v>1</v>
-      </c>
-      <c r="B81" t="s">
-        <v>77</v>
-      </c>
-      <c r="C81" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B82" t="s">
-        <v>77</v>
-      </c>
-      <c r="C82" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A83" t="b">
-        <v>1</v>
-      </c>
-      <c r="B83" t="s">
-        <v>77</v>
-      </c>
-      <c r="C83" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A84" t="b">
-        <v>1</v>
-      </c>
-      <c r="B84" t="s">
-        <v>77</v>
-      </c>
-      <c r="C84" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A86" t="b">
-        <v>0</v>
-      </c>
-      <c r="B86" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" t="b">
-        <v>0</v>
-      </c>
-      <c r="B88" t="s">
+      <c r="B88" s="32" t="s">
         <v>764</v>
       </c>
     </row>
@@ -25723,4 +26901,2332 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79BA2CFD-36F5-ED48-BA61-D06C52A754BA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FF6C9F4-4010-9243-98AE-74EEEFFCAC53}">
+  <dimension ref="A1:L87"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="3" width="27.1640625" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" customWidth="1"/>
+    <col min="8" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="28.6640625" customWidth="1"/>
+    <col min="12" max="12" width="47.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="24" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>680</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="L2" s="23"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="21" t="s">
+        <v>740</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="b">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="22" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="23"/>
+    </row>
+    <row r="12" spans="1:12" s="23" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>635</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="19" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" t="b">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" t="b">
+        <v>1</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" t="b">
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" t="b">
+        <v>1</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" t="b">
+        <v>1</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" t="b">
+        <v>1</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" t="b">
+        <v>1</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>635</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="H27" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="19" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" t="b">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" t="b">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" t="b">
+        <v>1</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32" t="b">
+        <v>1</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" t="b">
+        <v>1</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="H33" s="6"/>
+      <c r="I33" s="20" t="s">
+        <v>707</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" t="b">
+        <v>1</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D34" s="21"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H34" s="2"/>
+      <c r="I34" s="20" t="s">
+        <v>708</v>
+      </c>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" t="b">
+        <v>1</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" t="b">
+        <v>1</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" t="b">
+        <v>1</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" t="b">
+        <v>1</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" t="b">
+        <v>1</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" t="b">
+        <v>1</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" t="b">
+        <v>1</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" t="b">
+        <v>1</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" t="b">
+        <v>1</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+    </row>
+    <row r="46" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" t="b">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H46" s="2"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" t="b">
+        <v>0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" t="b">
+        <v>0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="1"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50" t="b">
+        <v>1</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" t="b">
+        <v>1</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A53" t="b">
+        <v>0</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="L53" s="19" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54" t="b">
+        <v>0</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A55" t="b">
+        <v>0</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="1"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A57" t="b">
+        <v>1</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="J57" s="2"/>
+      <c r="K57" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A58" t="b">
+        <v>0</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H58" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A59" t="b">
+        <v>0</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H59" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="1"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H61" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A62" t="b">
+        <v>0</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H62" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A63" t="b">
+        <v>0</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H63" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="1"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A65" t="b">
+        <v>1</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A67" t="b">
+        <v>0</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A68" t="b">
+        <v>0</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A69" t="b">
+        <v>0</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A71" t="b">
+        <v>0</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A72" t="b">
+        <v>0</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+    </row>
+    <row r="74" spans="1:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" t="b">
+        <v>1</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D74" s="2"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H74" s="2"/>
+      <c r="I74" s="17" t="s">
+        <v>736</v>
+      </c>
+      <c r="J74" s="2"/>
+      <c r="K74" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="L74" s="19" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A75" t="b">
+        <v>0</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A76" t="b">
+        <v>0</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="I76" s="6"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="1"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A78" t="b">
+        <v>0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A79" t="b">
+        <v>0</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A80" t="b">
+        <v>0</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="1"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A82" t="b">
+        <v>0</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A83" t="b">
+        <v>0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A84" t="b">
+        <v>0</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="1"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A86" t="b">
+        <v>1</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A87" t="b">
+        <v>1</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
+      <c r="L87" s="23"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L87" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}"/>
+  <conditionalFormatting sqref="H37:J37">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>
--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6A2996-92A5-AE4A-9D50-E75DBBB41723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6C5052-DB9B-1142-8E50-8770330E035B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2020" yWindow="500" windowWidth="38940" windowHeight="20920" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
@@ -14582,7 +14582,7 @@
     </row>
     <row r="18" spans="1:12" s="23" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>1</v>

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6C5052-DB9B-1142-8E50-8770330E035B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5DC79A-7FEE-6549-9EC3-331B947A808C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2020" yWindow="500" windowWidth="38940" windowHeight="20920" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="2020" yWindow="500" windowWidth="38940" windowHeight="20920" activeTab="2" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
@@ -18,16 +18,15 @@
     <sheet name="wide_qualityReports" sheetId="7" r:id="rId3"/>
     <sheet name="enums" sheetId="3" r:id="rId4"/>
     <sheet name="id_gen" sheetId="4" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId6"/>
-    <sheet name="maps original" sheetId="6" r:id="rId7"/>
+    <sheet name="maps original" sheetId="6" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">enums!$A$1:$J$185</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maps!$A$1:$L$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'maps original'!$A$1:$L$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'maps original'!$A$1:$L$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">wide!$A$1:$N$136</definedName>
     <definedName name="partID">[1]parts!$A:$A</definedName>
     <definedName name="partLabel">[1]parts!$B:$B</definedName>
@@ -52,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3216" uniqueCount="836">
   <si>
     <t>Reporter</t>
   </si>
@@ -2565,27 +2564,15 @@
     <t>{{ntc_amplify}}</t>
   </si>
   <si>
-    <t>{{inhibition_detect}}</t>
-  </si>
-  <si>
     <t>{{id:qualityReportID4}}</t>
   </si>
   <si>
-    <t>flagAI OR flagFI</t>
-  </si>
-  <si>
-    <t>{{inhibition_adjust}}</t>
-  </si>
-  <si>
     <t>{{id:qualityReportID5}}</t>
   </si>
   <si>
     <t>qualityReportID_target</t>
   </si>
   <si>
-    <t>{{id:qualityReportID6}}</t>
-  </si>
-  <si>
     <t>{{quality_flag}}</t>
   </si>
   <si>
@@ -2593,6 +2580,18 @@
   </si>
   <si>
     <t>Added by Martin</t>
+  </si>
+  <si>
+    <t>qualityFlag_expr</t>
+  </si>
+  <si>
+    <t>def get_qualityFlag(inhibition_detect: str, inhibition_adjust: str) -&gt; str:
+    if inhibition_detect == "yes" and inhibition_adjust == "yes":
+        return "flagAI"
+    elif inhibition_detect == "yes" and inhibition_adjust == "no":
+        return "flagFI"
+    return "ignore"
+target = get_qualityFlag(src.inhibition_detect, src.inhibition_adjust)</t>
   </si>
 </sst>
 </file>
@@ -2810,7 +2809,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2863,6 +2862,9 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14292,7 +14294,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -14564,7 +14566,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="2"/>
       <c r="L16" s="22" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -16564,12 +16566,14 @@
       <c r="A94" t="b">
         <v>1</v>
       </c>
+      <c r="B94" s="2"/>
       <c r="C94" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>812</v>
       </c>
+      <c r="E94" s="2"/>
       <c r="F94" s="2" t="s">
         <v>79</v>
       </c>
@@ -16580,17 +16584,22 @@
         <f t="shared" ref="H94:H101" si="0">"{{"&amp;D94&amp;"}}"</f>
         <v>{{id:addressID}}</v>
       </c>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" t="b">
         <v>1</v>
       </c>
+      <c r="B95" s="2"/>
       <c r="C95" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>807</v>
       </c>
+      <c r="E95" s="2"/>
       <c r="F95" s="2" t="s">
         <v>115</v>
       </c>
@@ -16601,17 +16610,22 @@
         <f>"{{"&amp;D95&amp;"}}"</f>
         <v>{{id:datasetID}}</v>
       </c>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" t="b">
         <v>1</v>
       </c>
+      <c r="B96" s="2"/>
       <c r="C96" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>805</v>
       </c>
+      <c r="E96" s="2"/>
       <c r="F96" s="2" t="s">
         <v>115</v>
       </c>
@@ -16622,17 +16636,22 @@
         <f>"{{"&amp;D96&amp;"}}"</f>
         <v>{{id:measureRepID}}</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" t="b">
         <v>1</v>
       </c>
+      <c r="B97" s="2"/>
       <c r="C97" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="2" t="s">
         <v>808</v>
       </c>
+      <c r="E97" s="2"/>
       <c r="F97" s="2" t="s">
         <v>115</v>
       </c>
@@ -16643,17 +16662,22 @@
         <f>"{{"&amp;D97&amp;"}}"</f>
         <v>{{id:measureSetRepID}}</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" t="b">
         <v>1</v>
       </c>
+      <c r="B98" s="2"/>
       <c r="C98" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>805</v>
       </c>
+      <c r="E98" s="2"/>
       <c r="F98" s="2" t="s">
         <v>147</v>
       </c>
@@ -16664,17 +16688,22 @@
         <f t="shared" si="0"/>
         <v>{{id:measureRepID}}</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" t="b">
         <v>1</v>
       </c>
+      <c r="B99" s="2"/>
       <c r="C99" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="2" t="s">
         <v>808</v>
       </c>
+      <c r="E99" s="2"/>
       <c r="F99" s="2" t="s">
         <v>147</v>
       </c>
@@ -16685,17 +16714,22 @@
         <f t="shared" si="0"/>
         <v>{{id:measureSetRepID}}</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" t="b">
         <v>1</v>
       </c>
+      <c r="B100" s="2"/>
       <c r="C100" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>810</v>
       </c>
+      <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
         <v>152</v>
       </c>
@@ -16706,17 +16740,22 @@
         <f t="shared" si="0"/>
         <v>{{id:instrumentID}}</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" t="b">
         <v>1</v>
       </c>
+      <c r="B101" s="2"/>
       <c r="C101" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>809</v>
       </c>
+      <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
         <v>152</v>
       </c>
@@ -16727,17 +16766,22 @@
         <f t="shared" si="0"/>
         <v>{{id:stepID}}</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" t="b">
         <v>1</v>
       </c>
+      <c r="B102" s="2"/>
       <c r="C102" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>807</v>
       </c>
+      <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
         <v>476</v>
       </c>
@@ -16748,17 +16792,22 @@
         <f>"{{"&amp;D102&amp;"}}"</f>
         <v>{{id:datasetID}}</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" t="b">
         <v>1</v>
       </c>
+      <c r="B103" s="2"/>
       <c r="C103" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>807</v>
       </c>
+      <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
         <v>118</v>
       </c>
@@ -16769,17 +16818,22 @@
         <f>"{{"&amp;D103&amp;"}}"</f>
         <v>{{id:datasetID}}</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I103" s="2"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" t="b">
         <v>1</v>
       </c>
+      <c r="B104" s="2"/>
       <c r="C104" s="2" t="s">
         <v>635</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>807</v>
       </c>
+      <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
         <v>77</v>
       </c>
@@ -16790,6 +16844,9 @@
         <f>"{{"&amp;D104&amp;"}}"</f>
         <v>{{id:datasetID}}</v>
       </c>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L91" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}"/>
@@ -17309,7 +17366,7 @@
         <v>28</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>152</v>
@@ -19803,7 +19860,7 @@
         <v>37</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>152</v>
@@ -20428,7 +20485,7 @@
         <v>38</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>152</v>
@@ -21827,8 +21884,8 @@
     <cfRule type="duplicateValues" dxfId="8" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K94">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K121:M121">
     <cfRule type="duplicateValues" dxfId="5" priority="7"/>
@@ -21852,7 +21909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4CA3B6-4765-0A43-8534-6DA7BF8A336D}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -21860,10 +21917,10 @@
     <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" customWidth="1"/>
+    <col min="9" max="10" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="24" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="24" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>680</v>
       </c>
@@ -21886,16 +21943,19 @@
         <v>698</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="I1" s="11" t="s">
         <v>821</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
+        <v>834</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="b">
         <v>1</v>
       </c>
@@ -21921,7 +21981,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="b">
         <v>1</v>
       </c>
@@ -21941,7 +22001,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="b">
         <v>1</v>
       </c>
@@ -21952,7 +22012,7 @@
         <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="E4" t="s">
         <v>147</v>
@@ -21961,7 +22021,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="b">
         <v>1</v>
       </c>
@@ -21987,7 +22047,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="b">
         <v>1</v>
       </c>
@@ -22007,7 +22067,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="b">
         <v>1</v>
       </c>
@@ -22018,7 +22078,7 @@
         <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="E7" t="s">
         <v>147</v>
@@ -22027,7 +22087,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="b">
         <v>1</v>
       </c>
@@ -22053,7 +22113,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="b">
         <v>1</v>
       </c>
@@ -22073,7 +22133,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="b">
         <v>1</v>
       </c>
@@ -22083,23 +22143,17 @@
       <c r="C10" t="s">
         <v>68</v>
       </c>
-      <c r="D10" t="s">
-        <v>141</v>
-      </c>
       <c r="E10" t="s">
         <v>147</v>
       </c>
-      <c r="F10" t="s">
-        <v>830</v>
-      </c>
       <c r="H10" t="s">
-        <v>829</v>
-      </c>
-      <c r="I10" t="s">
         <v>828</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J10" s="34" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="b">
         <v>1</v>
       </c>
@@ -22107,19 +22161,25 @@
         <v>635</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E11" t="s">
         <v>147</v>
       </c>
       <c r="F11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="H11" t="s">
+        <v>829</v>
+      </c>
+      <c r="I11" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="b">
         <v>1</v>
       </c>
@@ -22127,19 +22187,19 @@
         <v>635</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>603</v>
+        <v>142</v>
       </c>
       <c r="E12" t="s">
         <v>147</v>
       </c>
       <c r="F12" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="b">
         <v>1</v>
       </c>
@@ -22147,127 +22207,15 @@
         <v>635</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>832</v>
       </c>
       <c r="E13" t="s">
         <v>147</v>
       </c>
       <c r="F13" t="s">
-        <v>604</v>
-      </c>
-      <c r="H13" t="s">
-        <v>832</v>
-      </c>
-      <c r="I13" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" t="b">
-        <v>1</v>
-      </c>
-      <c r="B14" t="s">
-        <v>635</v>
-      </c>
-      <c r="C14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" t="s">
-        <v>142</v>
-      </c>
-      <c r="E14" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" t="b">
-        <v>1</v>
-      </c>
-      <c r="B15" t="s">
-        <v>635</v>
-      </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>836</v>
-      </c>
-      <c r="E15" t="s">
-        <v>147</v>
-      </c>
-      <c r="F15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" t="b">
-        <v>1</v>
-      </c>
-      <c r="B16" t="s">
-        <v>635</v>
-      </c>
-      <c r="C16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16" t="s">
-        <v>147</v>
-      </c>
-      <c r="F16" t="s">
-        <v>149</v>
-      </c>
-      <c r="H16" t="s">
-        <v>834</v>
-      </c>
-      <c r="I16" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="b">
-        <v>1</v>
-      </c>
-      <c r="B17" t="s">
-        <v>635</v>
-      </c>
-      <c r="C17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" t="s">
-        <v>142</v>
-      </c>
-      <c r="E17" t="s">
-        <v>147</v>
-      </c>
-      <c r="F17" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="b">
-        <v>1</v>
-      </c>
-      <c r="B18" t="s">
-        <v>635</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" t="s">
-        <v>836</v>
-      </c>
-      <c r="E18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F18" t="s">
         <v>150</v>
       </c>
     </row>
@@ -26904,15 +26852,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79BA2CFD-36F5-ED48-BA61-D06C52A754BA}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FF6C9F4-4010-9243-98AE-74EEEFFCAC53}">
   <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5DC79A-7FEE-6549-9EC3-331B947A808C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C406B1-0321-6E49-B1E5-D658FAC8A4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2020" yWindow="500" windowWidth="38940" windowHeight="20920" activeTab="2" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="2020" yWindow="500" windowWidth="38940" windowHeight="20920" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3216" uniqueCount="836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3216" uniqueCount="837">
   <si>
     <t>Reporter</t>
   </si>
@@ -2393,48 +2393,6 @@
     <t>custodyCont</t>
   </si>
   <si>
-    <t>specimen_target</t>
-  </si>
-  <si>
-    <t>measure_target</t>
-  </si>
-  <si>
-    <t>method_target</t>
-  </si>
-  <si>
-    <t>value_target</t>
-  </si>
-  <si>
-    <t>unit_target</t>
-  </si>
-  <si>
-    <t>aggregation_target</t>
-  </si>
-  <si>
-    <t>{ "notes_target" : "{{pretreatment_specify}}" }</t>
-  </si>
-  <si>
-    <t>{"reflink_target": "{{stan_ref}}"}</t>
-  </si>
-  <si>
-    <t>{"reflink_target": "{{pcr_gene_target_ref}}", "group_target": "{{pcr_target}}"}</t>
-  </si>
-  <si>
-    <t>{"reflink_target": "{{pcr_gene_target_ref}}"}</t>
-  </si>
-  <si>
-    <t>{"reflink_target": "{{lod_ref}}"}</t>
-  </si>
-  <si>
-    <t>{"reflink_target": "{{hum_frac_target_mic_ref}}"}</t>
-  </si>
-  <si>
-    <t>{"reflink_target": "{{hum_frac_target_chem_ref}}"}</t>
-  </si>
-  <si>
-    <t>{"reflink_target": "{{other_norm_ref}}"}</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -2543,9 +2501,6 @@
     <t>flagJcaOnOttOttawasite1202008021000covN1002</t>
   </si>
   <si>
-    <t>qualityFlag_target</t>
-  </si>
-  <si>
     <t>{{qc_ignore}}</t>
   </si>
   <si>
@@ -2568,9 +2523,6 @@
   </si>
   <si>
     <t>{{id:qualityReportID5}}</t>
-  </si>
-  <si>
-    <t>qualityReportID_target</t>
   </si>
   <si>
     <t>{{quality_flag}}</t>
@@ -2592,6 +2544,57 @@
         return "flagFI"
     return "ignore"
 target = get_qualityFlag(src.inhibition_detect, src.inhibition_adjust)</t>
+  </si>
+  <si>
+    <t>qualityReportID_value</t>
+  </si>
+  <si>
+    <t>qualityFlag_value</t>
+  </si>
+  <si>
+    <t>{ "notes_value" : "{{pretreatment_specify}}" }</t>
+  </si>
+  <si>
+    <t>{"reflink_value": "{{stan_ref}}"}</t>
+  </si>
+  <si>
+    <t>{"reflink_value": "{{pcr_gene_target_ref}}", "group_value": "{{pcr_target}}"}</t>
+  </si>
+  <si>
+    <t>{"reflink_value": "{{pcr_gene_target_ref}}"}</t>
+  </si>
+  <si>
+    <t>{"reflink_value": "{{lod_ref}}"}</t>
+  </si>
+  <si>
+    <t>{"reflink_value": "{{hum_frac_target_mic_ref}}"}</t>
+  </si>
+  <si>
+    <t>{"reflink_value": "{{hum_frac_target_chem_ref}}"}</t>
+  </si>
+  <si>
+    <t>{"reflink_value": "{{other_norm_ref}}"}</t>
+  </si>
+  <si>
+    <t>specimen_value</t>
+  </si>
+  <si>
+    <t>measure_value</t>
+  </si>
+  <si>
+    <t>method_value</t>
+  </si>
+  <si>
+    <t>value_value</t>
+  </si>
+  <si>
+    <t>unit_value</t>
+  </si>
+  <si>
+    <t>aggregation_value</t>
+  </si>
+  <si>
+    <t>targetExpr</t>
   </si>
 </sst>
 </file>
@@ -14172,7 +14175,7 @@
         <v>640</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>681</v>
+        <v>836</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>682</v>
@@ -14294,7 +14297,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" t="s">
-        <v>833</v>
+        <v>817</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -14566,7 +14569,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="2"/>
       <c r="L16" s="22" t="s">
-        <v>833</v>
+        <v>817</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -16545,7 +16548,7 @@
         <v>635</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2" t="s">
@@ -16571,7 +16574,7 @@
         <v>635</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>812</v>
+        <v>798</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2" t="s">
@@ -16597,7 +16600,7 @@
         <v>635</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2" t="s">
@@ -16623,7 +16626,7 @@
         <v>635</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2" t="s">
@@ -16649,7 +16652,7 @@
         <v>635</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>808</v>
+        <v>794</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2" t="s">
@@ -16675,7 +16678,7 @@
         <v>635</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2" t="s">
@@ -16701,7 +16704,7 @@
         <v>635</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>808</v>
+        <v>794</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="s">
@@ -16727,7 +16730,7 @@
         <v>635</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>810</v>
+        <v>796</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
@@ -16753,7 +16756,7 @@
         <v>635</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>809</v>
+        <v>795</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
@@ -16779,7 +16782,7 @@
         <v>635</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
@@ -16805,7 +16808,7 @@
         <v>635</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
@@ -16831,7 +16834,7 @@
         <v>635</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
@@ -16897,22 +16900,22 @@
         <v>698</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>771</v>
+        <v>830</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>772</v>
+        <v>831</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>773</v>
+        <v>832</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>774</v>
+        <v>833</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>775</v>
+        <v>834</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>776</v>
+        <v>835</v>
       </c>
       <c r="N1" s="12" t="s">
         <v>121</v>
@@ -17164,7 +17167,7 @@
         <v>650</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>777</v>
+        <v>822</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>165</v>
@@ -17366,7 +17369,7 @@
         <v>28</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>832</v>
+        <v>816</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>152</v>
@@ -19860,7 +19863,7 @@
         <v>37</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>832</v>
+        <v>816</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>152</v>
@@ -20485,7 +20488,7 @@
         <v>38</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>832</v>
+        <v>816</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>152</v>
@@ -21147,7 +21150,7 @@
         <v>408</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>778</v>
+        <v>823</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>76</v>
@@ -21523,7 +21526,7 @@
         <v>650</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>779</v>
+        <v>824</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>165</v>
@@ -21565,7 +21568,7 @@
         <v>650</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>780</v>
+        <v>825</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>165</v>
@@ -21607,7 +21610,7 @@
         <v>650</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>780</v>
+        <v>825</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>165</v>
@@ -21649,7 +21652,7 @@
         <v>650</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>780</v>
+        <v>825</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>165</v>
@@ -21691,7 +21694,7 @@
         <v>650</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>781</v>
+        <v>826</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>165</v>
@@ -21773,7 +21776,7 @@
         <v>650</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>782</v>
+        <v>827</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>165</v>
@@ -21813,7 +21816,7 @@
         <v>650</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>783</v>
+        <v>828</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>165</v>
@@ -21853,7 +21856,7 @@
         <v>650</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>784</v>
+        <v>829</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>165</v>
@@ -21909,7 +21912,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4CA3B6-4765-0A43-8534-6DA7BF8A336D}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -21943,13 +21946,13 @@
         <v>698</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="I1" s="11" t="s">
         <v>821</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>834</v>
+        <v>818</v>
       </c>
       <c r="K1" s="12" t="s">
         <v>121</v>
@@ -21975,10 +21978,10 @@
         <v>149</v>
       </c>
       <c r="H2" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="I2" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -22012,7 +22015,7 @@
         <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>832</v>
+        <v>816</v>
       </c>
       <c r="E4" t="s">
         <v>147</v>
@@ -22021,32 +22024,6 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" t="b">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>635</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" t="s">
-        <v>141</v>
-      </c>
-      <c r="E5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" t="s">
-        <v>596</v>
-      </c>
-      <c r="H5" t="s">
-        <v>824</v>
-      </c>
-      <c r="I5" t="s">
-        <v>825</v>
-      </c>
-    </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="b">
         <v>1</v>
@@ -22058,13 +22035,19 @@
         <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
         <v>147</v>
       </c>
       <c r="F6" t="s">
-        <v>598</v>
+        <v>596</v>
+      </c>
+      <c r="H6" t="s">
+        <v>809</v>
+      </c>
+      <c r="I6" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -22078,7 +22061,7 @@
         <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>832</v>
+        <v>142</v>
       </c>
       <c r="E7" t="s">
         <v>147</v>
@@ -22095,62 +22078,42 @@
         <v>635</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>816</v>
       </c>
       <c r="E8" t="s">
         <v>147</v>
       </c>
       <c r="F8" t="s">
-        <v>602</v>
-      </c>
-      <c r="H8" t="s">
-        <v>826</v>
-      </c>
-      <c r="I8" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" t="b">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>635</v>
-      </c>
-      <c r="C9" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>635</v>
+      </c>
+      <c r="C10" t="s">
         <v>66</v>
       </c>
-      <c r="D9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F9" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>635</v>
-      </c>
-      <c r="C10" t="s">
-        <v>68</v>
+      <c r="D10" t="s">
+        <v>141</v>
       </c>
       <c r="E10" t="s">
         <v>147</v>
       </c>
+      <c r="F10" t="s">
+        <v>602</v>
+      </c>
       <c r="H10" t="s">
-        <v>828</v>
-      </c>
-      <c r="J10" s="34" t="s">
-        <v>835</v>
+        <v>811</v>
+      </c>
+      <c r="I10" t="s">
+        <v>812</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -22161,45 +22124,19 @@
         <v>635</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E11" t="s">
         <v>147</v>
       </c>
       <c r="F11" t="s">
-        <v>149</v>
-      </c>
-      <c r="H11" t="s">
-        <v>829</v>
-      </c>
-      <c r="I11" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B12" t="s">
-        <v>635</v>
-      </c>
-      <c r="C12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" t="s">
-        <v>142</v>
-      </c>
-      <c r="E12" t="s">
-        <v>147</v>
-      </c>
-      <c r="F12" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="b">
         <v>1</v>
       </c>
@@ -22207,15 +22144,84 @@
         <v>635</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" t="s">
-        <v>832</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>147</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
+        <v>813</v>
+      </c>
+      <c r="J13" s="34" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J14" s="34"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>635</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" t="s">
+        <v>149</v>
+      </c>
+      <c r="H15" t="s">
+        <v>814</v>
+      </c>
+      <c r="I15" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>635</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" t="s">
+        <v>147</v>
+      </c>
+      <c r="F16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>635</v>
+      </c>
+      <c r="C17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
+        <v>816</v>
+      </c>
+      <c r="E17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17" t="s">
         <v>150</v>
       </c>
     </row>
@@ -25996,13 +26002,13 @@
         <v>636</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>804</v>
+        <v>790</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -26016,13 +26022,13 @@
         <v>747</v>
       </c>
       <c r="E2" t="s">
-        <v>812</v>
+        <v>798</v>
       </c>
       <c r="F2" t="s">
-        <v>814</v>
+        <v>800</v>
       </c>
       <c r="G2" t="s">
-        <v>813</v>
+        <v>799</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -26033,7 +26039,7 @@
         <v>743</v>
       </c>
       <c r="E3" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -26047,13 +26053,13 @@
         <v>742</v>
       </c>
       <c r="E5" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="F5" t="s">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="G5" t="s">
-        <v>786</v>
+        <v>772</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -26073,10 +26079,10 @@
         <v>719</v>
       </c>
       <c r="F6" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="G6" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -26093,10 +26099,10 @@
         <v>716</v>
       </c>
       <c r="F7" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="G7" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -26110,13 +26116,13 @@
         <v>745</v>
       </c>
       <c r="E8" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="F8" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="G8" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -26133,10 +26139,10 @@
         <v>710</v>
       </c>
       <c r="F9" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="G9" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -26150,13 +26156,13 @@
         <v>743</v>
       </c>
       <c r="E10" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="F10" t="s">
-        <v>797</v>
+        <v>783</v>
       </c>
       <c r="G10" t="s">
-        <v>796</v>
+        <v>782</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -26170,13 +26176,13 @@
         <v>744</v>
       </c>
       <c r="E11" t="s">
-        <v>808</v>
+        <v>794</v>
       </c>
       <c r="F11" t="s">
-        <v>799</v>
+        <v>785</v>
       </c>
       <c r="G11" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -26193,10 +26199,10 @@
         <v>717</v>
       </c>
       <c r="F12" t="s">
-        <v>797</v>
+        <v>783</v>
       </c>
       <c r="G12" t="s">
-        <v>800</v>
+        <v>786</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -26216,10 +26222,10 @@
         <v>709</v>
       </c>
       <c r="F13" t="s">
-        <v>801</v>
+        <v>787</v>
       </c>
       <c r="G13" t="s">
-        <v>802</v>
+        <v>788</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -26264,7 +26270,7 @@
         <v>743</v>
       </c>
       <c r="E17" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -26306,13 +26312,13 @@
         <v>752</v>
       </c>
       <c r="E21" t="s">
-        <v>809</v>
+        <v>795</v>
       </c>
       <c r="F21" t="s">
-        <v>818</v>
+        <v>804</v>
       </c>
       <c r="G21" t="s">
-        <v>817</v>
+        <v>803</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -26354,13 +26360,13 @@
         <v>753</v>
       </c>
       <c r="E24" t="s">
-        <v>810</v>
+        <v>796</v>
       </c>
       <c r="F24" t="s">
-        <v>816</v>
+        <v>802</v>
       </c>
       <c r="G24" t="s">
-        <v>815</v>
+        <v>801</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -26374,13 +26380,13 @@
         <v>749</v>
       </c>
       <c r="E26" t="s">
-        <v>811</v>
+        <v>797</v>
       </c>
       <c r="F26" t="s">
-        <v>820</v>
+        <v>806</v>
       </c>
       <c r="G26" t="s">
-        <v>819</v>
+        <v>805</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -26394,7 +26400,7 @@
         <v>742</v>
       </c>
       <c r="E27" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -26422,7 +26428,7 @@
         <v>744</v>
       </c>
       <c r="E29" t="s">
-        <v>808</v>
+        <v>794</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -26512,7 +26518,7 @@
         <v>743</v>
       </c>
       <c r="E36" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -26554,7 +26560,7 @@
         <v>743</v>
       </c>
       <c r="E40" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
@@ -26568,13 +26574,13 @@
         <v>745</v>
       </c>
       <c r="E41" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="F41" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="G41" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -26588,7 +26594,7 @@
         <v>747</v>
       </c>
       <c r="E42" t="s">
-        <v>812</v>
+        <v>798</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C406B1-0321-6E49-B1E5-D658FAC8A4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F954EFD8-4B08-3F45-A3DC-4037CFB16FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2020" yWindow="500" windowWidth="38940" windowHeight="20920" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="2020" yWindow="500" windowWidth="38940" windowHeight="20920" activeTab="3" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3216" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2995" uniqueCount="837">
   <si>
     <t>Reporter</t>
   </si>
@@ -2601,7 +2601,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2685,6 +2685,17 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2812,7 +2823,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2868,6 +2879,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14197,9 +14214,7 @@
       <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="E2" s="2"/>
       <c r="F2" s="1" t="s">
         <v>115</v>
       </c>
@@ -14229,9 +14244,7 @@
       <c r="D3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
         <v>115</v>
       </c>
@@ -14325,9 +14338,7 @@
       <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
         <v>77</v>
       </c>
@@ -14386,9 +14397,7 @@
       <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
         <v>79</v>
       </c>
@@ -14415,9 +14424,7 @@
       <c r="D10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
         <v>77</v>
       </c>
@@ -14586,36 +14593,34 @@
       <c r="L17" s="23"/>
     </row>
     <row r="18" spans="1:12" s="23" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>635</v>
-      </c>
-      <c r="D18" s="28" t="s">
+      <c r="A18" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>635</v>
+      </c>
+      <c r="D18" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="G18" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="H18" s="28" t="s">
+      <c r="H18" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="19" t="s">
-        <v>738</v>
-      </c>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="38"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="b">
@@ -15242,9 +15247,7 @@
       <c r="D41" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>76</v>
-      </c>
+      <c r="E41" s="3"/>
       <c r="F41" s="2" t="s">
         <v>118</v>
       </c>
@@ -15527,9 +15530,7 @@
       <c r="D52" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
         <v>118</v>
       </c>
@@ -15556,9 +15557,7 @@
       <c r="D53" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
         <v>118</v>
       </c>
@@ -15585,9 +15584,7 @@
       <c r="D54" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
         <v>118</v>
       </c>
@@ -15626,9 +15623,7 @@
       <c r="D56" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
         <v>118</v>
       </c>
@@ -15655,9 +15650,7 @@
       <c r="D57" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
         <v>118</v>
       </c>
@@ -15755,7 +15748,7 @@
         <v>57</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>143</v>
+        <v>816</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>118</v>
@@ -15860,7 +15853,7 @@
         <v>58</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>143</v>
+        <v>816</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>118</v>
@@ -15968,7 +15961,7 @@
         <v>56</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>143</v>
+        <v>816</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>147</v>
@@ -16071,7 +16064,7 @@
         <v>64</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>143</v>
+        <v>816</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>147</v>
@@ -16350,7 +16343,7 @@
         <v>69</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>143</v>
+        <v>816</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>147</v>
@@ -16358,9 +16351,7 @@
       <c r="G84" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="H84" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="H84" s="2"/>
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="1" t="s">
@@ -16455,7 +16446,7 @@
         <v>73</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>143</v>
+        <v>816</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>147</v>
@@ -16869,7 +16860,7 @@
     <col min="2" max="2" width="28.6640625" customWidth="1"/>
     <col min="3" max="4" width="25.5" customWidth="1"/>
     <col min="5" max="7" width="22.5" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
     <col min="9" max="10" width="29.33203125" customWidth="1"/>
     <col min="11" max="11" width="23.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.5" customWidth="1"/>
@@ -17065,12 +17056,8 @@
       <c r="K5" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -17181,12 +17168,8 @@
       <c r="K8" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
       <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -17224,9 +17207,7 @@
         <v>423</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
         <v>650</v>
       </c>
@@ -17236,12 +17217,8 @@
       <c r="K10" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
       <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -17274,12 +17251,8 @@
       <c r="K11" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
       <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -17312,12 +17285,8 @@
       <c r="K12" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
       <c r="N12" s="2"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -17350,12 +17319,8 @@
       <c r="K13" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
       <c r="N13" s="2"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -17374,9 +17339,7 @@
       <c r="E14" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
@@ -17388,12 +17351,8 @@
       <c r="K14" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
       <c r="N14" s="2"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -17431,9 +17390,7 @@
         <v>429</v>
       </c>
       <c r="G16" s="2"/>
-      <c r="H16" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
         <v>650</v>
       </c>
@@ -17443,12 +17400,8 @@
       <c r="K16" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
       <c r="N16" s="2"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
@@ -17481,12 +17434,8 @@
       <c r="K17" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
       <c r="N17" s="2"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -17519,12 +17468,8 @@
       <c r="K18" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
       <c r="N18" s="2"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -17557,12 +17502,8 @@
       <c r="K19" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
       <c r="N19" s="2"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -17593,12 +17534,8 @@
         <v>650</v>
       </c>
       <c r="K20" s="2"/>
-      <c r="L20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
       <c r="N20" s="2"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
@@ -17631,12 +17568,8 @@
       <c r="K21" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
       <c r="N21" s="2"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
@@ -17669,12 +17602,8 @@
       <c r="K22" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
       <c r="N22" s="2"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
@@ -17707,12 +17636,8 @@
       <c r="K23" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
       <c r="N23" s="2"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
@@ -17745,12 +17670,8 @@
       <c r="K24" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
       <c r="N24" s="2"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
@@ -17783,12 +17704,8 @@
       <c r="K25" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
       <c r="N25" s="2"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -17821,12 +17738,8 @@
       <c r="K26" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
       <c r="N26" s="2"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -17859,12 +17772,8 @@
       <c r="K27" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
       <c r="N27" s="2"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
@@ -17897,12 +17806,8 @@
       <c r="K28" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
       <c r="N28" s="2"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
@@ -17935,12 +17840,8 @@
       <c r="K29" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
       <c r="N29" s="2"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -17973,12 +17874,8 @@
       <c r="K30" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
       <c r="N30" s="2"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
@@ -18011,12 +17908,8 @@
       <c r="K31" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
       <c r="N31" s="2"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
@@ -18049,12 +17942,8 @@
       <c r="K32" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L32" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
       <c r="N32" s="2"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
@@ -18087,12 +17976,8 @@
       <c r="K33" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
       <c r="N33" s="2"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
@@ -18125,12 +18010,8 @@
       <c r="K34" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L34" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
       <c r="N34" s="2"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -18163,12 +18044,8 @@
       <c r="K35" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L35" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
       <c r="N35" s="2"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
@@ -18201,12 +18078,8 @@
       <c r="K36" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L36" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
       <c r="N36" s="2"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
@@ -18239,12 +18112,8 @@
       <c r="K37" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L37" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
       <c r="N37" s="2"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
@@ -18277,12 +18146,8 @@
       <c r="K38" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
       <c r="N38" s="2"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
@@ -18315,12 +18180,8 @@
       <c r="K39" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L39" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
       <c r="N39" s="2"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
@@ -18358,9 +18219,7 @@
         <v>447</v>
       </c>
       <c r="G41" s="2"/>
-      <c r="H41" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="H41" s="2"/>
       <c r="I41" s="2" t="s">
         <v>650</v>
       </c>
@@ -18370,12 +18229,8 @@
       <c r="K41" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="L41" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
@@ -18408,12 +18263,8 @@
       <c r="K42" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L42" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
       <c r="N42" s="2"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
@@ -18446,12 +18297,8 @@
       <c r="K43" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L43" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
       <c r="N43" s="2"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
@@ -18484,12 +18331,8 @@
       <c r="K44" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L44" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
       <c r="N44" s="2"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
@@ -18522,12 +18365,8 @@
       <c r="K45" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L45" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
       <c r="N45" s="2"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
@@ -18560,12 +18399,8 @@
       <c r="K46" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L46" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
       <c r="N46" s="2"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
@@ -18598,12 +18433,8 @@
       <c r="K47" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L47" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
@@ -18636,12 +18467,8 @@
       <c r="K48" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L48" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
       <c r="N48" s="2"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
@@ -18674,12 +18501,8 @@
       <c r="K49" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L49" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
       <c r="N49" s="2"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
@@ -18712,12 +18535,8 @@
       <c r="K50" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L50" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
       <c r="N50" s="2"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
@@ -18750,12 +18569,8 @@
       <c r="K51" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L51" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
       <c r="N51" s="2"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
@@ -18788,12 +18603,8 @@
       <c r="K52" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L52" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
       <c r="N52" s="2"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
@@ -18826,12 +18637,8 @@
       <c r="K53" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L53" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
       <c r="N53" s="2"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
@@ -18864,12 +18671,8 @@
       <c r="K54" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L54" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
       <c r="N54" s="2"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
@@ -18902,12 +18705,8 @@
       <c r="K55" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L55" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
       <c r="N55" s="2"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
@@ -18940,12 +18739,8 @@
       <c r="K56" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L56" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
       <c r="N56" s="2"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
@@ -18978,12 +18773,8 @@
       <c r="K57" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L57" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
       <c r="N57" s="2"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
@@ -19016,12 +18807,8 @@
       <c r="K58" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L58" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
       <c r="N58" s="2"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
@@ -19054,12 +18841,8 @@
       <c r="K59" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L59" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M59" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
       <c r="N59" s="2"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
@@ -19092,12 +18875,8 @@
       <c r="K60" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L60" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
       <c r="N60" s="2"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
@@ -19130,12 +18909,8 @@
       <c r="K61" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L61" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
       <c r="N61" s="2"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
@@ -19168,12 +18943,8 @@
       <c r="K62" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L62" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
       <c r="N62" s="2"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
@@ -19206,12 +18977,8 @@
       <c r="K63" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L63" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M63" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
       <c r="N63" s="2"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
@@ -19244,12 +19011,8 @@
       <c r="K64" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L64" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
       <c r="N64" s="2"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
@@ -19282,12 +19045,8 @@
       <c r="K65" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L65" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
       <c r="N65" s="2"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
@@ -19320,12 +19079,8 @@
       <c r="K66" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L66" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
       <c r="N66" s="2"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
@@ -19358,12 +19113,8 @@
       <c r="K67" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L67" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
       <c r="N67" s="2"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
@@ -19396,12 +19147,8 @@
       <c r="K68" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L68" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
       <c r="N68" s="2"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
@@ -19434,12 +19181,8 @@
       <c r="K69" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L69" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M69" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
       <c r="N69" s="2"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
@@ -19472,12 +19215,8 @@
       <c r="K70" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L70" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M70" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
       <c r="N70" s="2"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
@@ -19510,12 +19249,8 @@
       <c r="K71" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L71" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M71" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
       <c r="N71" s="2"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
@@ -19548,12 +19283,8 @@
       <c r="K72" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L72" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
       <c r="N72" s="2"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
@@ -19586,12 +19317,8 @@
       <c r="K73" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L73" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
       <c r="N73" s="2"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
@@ -19779,9 +19506,7 @@
         <v>650</v>
       </c>
       <c r="G79" s="2"/>
-      <c r="H79" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="H79" s="2"/>
       <c r="I79" s="2" t="s">
         <v>650</v>
       </c>
@@ -19817,9 +19542,7 @@
         <v>650</v>
       </c>
       <c r="G80" s="2"/>
-      <c r="H80" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="H80" s="2"/>
       <c r="I80" s="2" t="s">
         <v>650</v>
       </c>
@@ -19829,12 +19552,8 @@
       <c r="K80" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2"/>
       <c r="N80" s="2"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
@@ -19868,13 +19587,9 @@
       <c r="E82" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F82" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="F82" s="2"/>
       <c r="G82" s="2"/>
-      <c r="H82" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="H82" s="2"/>
       <c r="I82" s="2" t="s">
         <v>650</v>
       </c>
@@ -19884,12 +19599,8 @@
       <c r="K82" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="L82" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M82" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
       <c r="N82" s="2"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
@@ -19922,12 +19633,8 @@
       <c r="K83" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L83" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L83" s="2"/>
+      <c r="M83" s="2"/>
       <c r="N83" s="2"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
@@ -19960,12 +19667,8 @@
       <c r="K84" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L84" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L84" s="2"/>
+      <c r="M84" s="2"/>
       <c r="N84" s="2"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
@@ -19998,12 +19701,8 @@
       <c r="K85" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L85" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M85" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2"/>
       <c r="N85" s="2"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
@@ -20036,12 +19735,8 @@
       <c r="K86" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L86" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M86" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2"/>
       <c r="N86" s="2"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
@@ -20074,12 +19769,8 @@
       <c r="K87" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L87" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M87" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2"/>
       <c r="N87" s="2"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
@@ -20112,12 +19803,8 @@
       <c r="K88" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L88" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M88" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2"/>
       <c r="N88" s="2"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
@@ -20150,12 +19837,8 @@
       <c r="K89" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L89" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M89" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
       <c r="N89" s="2"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
@@ -20188,12 +19871,8 @@
       <c r="K90" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L90" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M90" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2"/>
       <c r="N90" s="2"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
@@ -20226,12 +19905,8 @@
       <c r="K91" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L91" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M91" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L91" s="2"/>
+      <c r="M91" s="2"/>
       <c r="N91" s="2"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
@@ -20264,12 +19939,8 @@
       <c r="K92" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L92" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M92" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L92" s="2"/>
+      <c r="M92" s="2"/>
       <c r="N92" s="2"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
@@ -20302,12 +19973,8 @@
       <c r="K93" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L93" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M93" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2"/>
       <c r="N93" s="2"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
@@ -20340,12 +20007,8 @@
       <c r="K94" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L94" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M94" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
       <c r="N94" s="2"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
@@ -20378,12 +20041,8 @@
       <c r="K95" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L95" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M95" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
       <c r="N95" s="2"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
@@ -20416,12 +20075,8 @@
       <c r="K96" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L96" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M96" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L96" s="2"/>
+      <c r="M96" s="2"/>
       <c r="N96" s="2"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
@@ -20454,12 +20109,8 @@
       <c r="K97" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L97" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M97" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L97" s="2"/>
+      <c r="M97" s="2"/>
       <c r="N97" s="2"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
@@ -20493,13 +20144,9 @@
       <c r="E99" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F99" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="F99" s="2"/>
       <c r="G99" s="2"/>
-      <c r="H99" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="H99" s="2"/>
       <c r="I99" s="2" t="s">
         <v>650</v>
       </c>
@@ -20509,12 +20156,8 @@
       <c r="K99" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="L99" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M99" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L99" s="2"/>
+      <c r="M99" s="2"/>
       <c r="N99" s="2"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
@@ -20547,12 +20190,8 @@
       <c r="K100" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L100" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M100" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L100" s="2"/>
+      <c r="M100" s="2"/>
       <c r="N100" s="2"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
@@ -20585,12 +20224,8 @@
       <c r="K101" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L101" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M101" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L101" s="2"/>
+      <c r="M101" s="2"/>
       <c r="N101" s="2"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
@@ -20623,12 +20258,8 @@
       <c r="K102" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L102" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M102" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L102" s="2"/>
+      <c r="M102" s="2"/>
       <c r="N102" s="2"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
@@ -20661,12 +20292,8 @@
       <c r="K103" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L103" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M103" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L103" s="2"/>
+      <c r="M103" s="2"/>
       <c r="N103" s="2"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.2">
@@ -20699,12 +20326,8 @@
       <c r="K104" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L104" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M104" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L104" s="2"/>
+      <c r="M104" s="2"/>
       <c r="N104" s="2"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
@@ -20737,12 +20360,8 @@
       <c r="K105" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L105" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M105" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L105" s="2"/>
+      <c r="M105" s="2"/>
       <c r="N105" s="2"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
@@ -20816,9 +20435,7 @@
         <v>650</v>
       </c>
       <c r="G108" s="2"/>
-      <c r="H108" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="H108" s="2"/>
       <c r="I108" s="2" t="s">
         <v>650</v>
       </c>
@@ -20828,12 +20445,8 @@
       <c r="K108" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="L108" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M108" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L108" s="2"/>
+      <c r="M108" s="2"/>
       <c r="N108" s="2"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
@@ -20871,9 +20484,7 @@
         <v>389</v>
       </c>
       <c r="G110" s="2"/>
-      <c r="H110" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="H110" s="2"/>
       <c r="I110" s="2" t="s">
         <v>650</v>
       </c>
@@ -20883,12 +20494,8 @@
       <c r="K110" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="L110" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M110" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L110" s="2"/>
+      <c r="M110" s="2"/>
       <c r="N110" s="2"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
@@ -20921,12 +20528,8 @@
       <c r="K111" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L111" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M111" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L111" s="2"/>
+      <c r="M111" s="2"/>
       <c r="N111" s="2"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
@@ -20959,12 +20562,8 @@
       <c r="K112" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L112" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M112" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L112" s="2"/>
+      <c r="M112" s="2"/>
       <c r="N112" s="2"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.2">
@@ -20997,12 +20596,8 @@
       <c r="K113" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L113" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M113" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L113" s="2"/>
+      <c r="M113" s="2"/>
       <c r="N113" s="2"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
@@ -21035,12 +20630,8 @@
       <c r="K114" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L114" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M114" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L114" s="2"/>
+      <c r="M114" s="2"/>
       <c r="N114" s="2"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.2">
@@ -21073,12 +20664,8 @@
       <c r="K115" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L115" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M115" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L115" s="2"/>
+      <c r="M115" s="2"/>
       <c r="N115" s="2"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
@@ -21152,9 +20739,7 @@
       <c r="G118" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="H118" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="H118" s="2"/>
       <c r="I118" s="2" t="s">
         <v>650</v>
       </c>
@@ -21164,12 +20749,8 @@
       <c r="K118" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="L118" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M118" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L118" s="2"/>
+      <c r="M118" s="2"/>
       <c r="N118" s="2"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
@@ -21202,12 +20783,8 @@
       <c r="K119" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="L119" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M119" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="L119" s="2"/>
+      <c r="M119" s="2"/>
       <c r="N119" s="2"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
@@ -21258,9 +20835,7 @@
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
-      <c r="H121" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="H121" s="2"/>
       <c r="I121" s="2" t="s">
         <v>650</v>
       </c>
@@ -25132,7 +24707,7 @@
         <v>701</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>143</v>
+        <v>816</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
@@ -25234,7 +24809,7 @@
         <v>702</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>143</v>
+        <v>816</v>
       </c>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
@@ -25456,7 +25031,7 @@
         <v>703</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>143</v>
+        <v>816</v>
       </c>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
@@ -25960,7 +25535,7 @@
         <v>705</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>143</v>
+        <v>816</v>
       </c>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F954EFD8-4B08-3F45-A3DC-4037CFB16FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047DCD60-FE69-034B-BFC5-840057F0F7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2020" yWindow="500" windowWidth="38940" windowHeight="20920" activeTab="3" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="7400" yWindow="500" windowWidth="38940" windowHeight="20920" activeTab="1" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
-    <sheet name="wide" sheetId="2" r:id="rId2"/>
-    <sheet name="wide_qualityReports" sheetId="7" r:id="rId3"/>
-    <sheet name="enums" sheetId="3" r:id="rId4"/>
-    <sheet name="id_gen" sheetId="4" r:id="rId5"/>
-    <sheet name="maps original" sheetId="6" r:id="rId6"/>
+    <sheet name="wide_measures" sheetId="2" r:id="rId2"/>
+    <sheet name="wide_protocolSteps" sheetId="8" r:id="rId3"/>
+    <sheet name="wide_qualityReports" sheetId="7" r:id="rId4"/>
+    <sheet name="enums" sheetId="3" r:id="rId5"/>
+    <sheet name="id_gen" sheetId="4" r:id="rId6"/>
+    <sheet name="maps original" sheetId="6" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">enums!$A$1:$J$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">enums!$A$1:$J$185</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maps!$A$1:$L$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'maps original'!$A$1:$L$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">wide!$A$1:$N$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'maps original'!$A$1:$L$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">wide_measures!$A$1:$N$24</definedName>
     <definedName name="partID">[1]parts!$A:$A</definedName>
     <definedName name="partLabel">[1]parts!$B:$B</definedName>
   </definedNames>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2995" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="837">
   <si>
     <t>Reporter</t>
   </si>
@@ -16854,7 +16855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B39AC7DD-3F73-2C47-925D-21E5B4EBE6FC}">
-  <dimension ref="A1:N136"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.6640625" customWidth="1"/>
@@ -17173,16 +17174,972 @@
       <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="A9" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="N13" s="2"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="N15" s="2"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" t="b">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" t="b">
+        <v>1</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" t="b">
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" t="b">
+        <v>1</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="N22" s="2"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" t="b">
+        <v>1</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="N23" s="2"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" t="b">
+        <v>1</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="N24" s="2"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N24" xr:uid="{B39AC7DD-3F73-2C47-925D-21E5B4EBE6FC}"/>
+  <conditionalFormatting sqref="L10 I10:J10 L15:L16">
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L22">
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L23">
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L24">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDC6A21B-0669-0743-9D12-F41DCA15CA4A}">
+  <dimension ref="A1:N112"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="96.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="24" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>680</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>830</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>831</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>832</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>833</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>834</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>835</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>428</v>
+      </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="I9" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -17195,16 +18152,16 @@
         <v>635</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -17212,10 +18169,10 @@
         <v>650</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>422</v>
+        <v>650</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>684</v>
+        <v>650</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -17229,16 +18186,16 @@
         <v>635</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -17263,16 +18220,16 @@
         <v>635</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>181</v>
+        <v>29</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>187</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -17282,9 +18239,7 @@
       <c r="J12" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -17297,16 +18252,16 @@
         <v>635</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -17331,15 +18286,17 @@
         <v>635</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>816</v>
+        <v>189</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>432</v>
+      </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
@@ -17356,16 +18313,35 @@
       <c r="N14" s="2"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="A15" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>434</v>
+      </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="I15" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -17380,14 +18356,14 @@
       <c r="C16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>183</v>
+      <c r="D16" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -17395,10 +18371,10 @@
         <v>650</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>427</v>
+        <v>650</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>685</v>
+        <v>650</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -17415,13 +18391,13 @@
         <v>29</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -17449,13 +18425,13 @@
         <v>29</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -17483,13 +18459,13 @@
         <v>29</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -17516,14 +18492,14 @@
       <c r="C20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>187</v>
+      <c r="D20" s="3" t="s">
+        <v>195</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -17533,7 +18509,9 @@
       <c r="J20" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="K20" s="2"/>
+      <c r="K20" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -17549,13 +18527,13 @@
         <v>29</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>433</v>
+        <v>615</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -17572,7 +18550,7 @@
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="b">
         <v>1</v>
       </c>
@@ -17583,13 +18561,13 @@
         <v>29</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -17617,13 +18595,13 @@
         <v>29</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -17651,13 +18629,13 @@
         <v>29</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -17684,14 +18662,14 @@
       <c r="C25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>192</v>
+      <c r="D25" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -17719,13 +18697,13 @@
         <v>29</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -17753,13 +18731,13 @@
         <v>29</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -17787,13 +18765,13 @@
         <v>29</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>439</v>
+        <v>616</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -17821,13 +18799,13 @@
         <v>29</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -17844,7 +18822,7 @@
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
     </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" t="b">
         <v>1</v>
       </c>
@@ -17855,13 +18833,13 @@
         <v>29</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>440</v>
+        <v>618</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -17889,13 +18867,13 @@
         <v>29</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -17913,35 +18891,16 @@
       <c r="N31" s="2"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" t="b">
-        <v>1</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>442</v>
-      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -17954,16 +18913,16 @@
         <v>635</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>200</v>
+        <v>30</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>221</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -17971,10 +18930,10 @@
         <v>650</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>650</v>
+        <v>446</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>650</v>
+        <v>686</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -17988,16 +18947,16 @@
         <v>635</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -18022,16 +18981,16 @@
         <v>635</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>444</v>
+        <v>619</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -18056,16 +19015,16 @@
         <v>635</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -18090,16 +19049,16 @@
         <v>635</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>204</v>
+        <v>30</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -18124,16 +19083,16 @@
         <v>635</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>205</v>
+        <v>30</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>236</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -18158,16 +19117,16 @@
         <v>635</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>182</v>
+        <v>216</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -18185,16 +19144,35 @@
       <c r="N39" s="2"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+      <c r="A40" t="b">
+        <v>1</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>450</v>
+      </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
+      <c r="I40" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -18209,14 +19187,14 @@
       <c r="C41" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="14" t="s">
-        <v>221</v>
+      <c r="D41" s="3" t="s">
+        <v>218</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -18224,10 +19202,10 @@
         <v>650</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>446</v>
+        <v>650</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>686</v>
+        <v>650</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -18244,13 +19222,13 @@
         <v>30</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -18278,13 +19256,13 @@
         <v>30</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>619</v>
+        <v>453</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -18312,13 +19290,13 @@
         <v>30</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>620</v>
+        <v>454</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -18345,14 +19323,14 @@
       <c r="C45" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>232</v>
+      <c r="D45" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>621</v>
+        <v>455</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -18379,14 +19357,14 @@
       <c r="C46" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D46" s="15" t="s">
-        <v>236</v>
+      <c r="D46" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>622</v>
+        <v>456</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -18414,13 +19392,13 @@
         <v>30</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>449</v>
+        <v>623</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -18448,13 +19426,13 @@
         <v>30</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -18481,14 +19459,14 @@
       <c r="C49" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>218</v>
+      <c r="D49" s="4" t="s">
+        <v>206</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -18516,13 +19494,13 @@
         <v>30</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -18550,13 +19528,13 @@
         <v>30</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -18584,13 +19562,13 @@
         <v>30</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -18618,13 +19596,13 @@
         <v>30</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>455</v>
+        <v>624</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -18652,13 +19630,13 @@
         <v>30</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -18686,13 +19664,13 @@
         <v>30</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>623</v>
+        <v>463</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -18720,13 +19698,13 @@
         <v>30</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>458</v>
+        <v>625</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -18753,14 +19731,14 @@
       <c r="C57" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>206</v>
+      <c r="D57" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -18788,13 +19766,13 @@
         <v>30</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>457</v>
+        <v>626</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -18821,14 +19799,14 @@
       <c r="C59" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>210</v>
+      <c r="D59" s="15" t="s">
+        <v>227</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>460</v>
+        <v>627</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -18855,14 +19833,14 @@
       <c r="C60" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>222</v>
+      <c r="D60" s="15" t="s">
+        <v>228</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>461</v>
+        <v>628</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -18890,13 +19868,13 @@
         <v>30</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>624</v>
+        <v>465</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -18924,13 +19902,13 @@
         <v>30</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
@@ -18958,13 +19936,13 @@
         <v>30</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
@@ -18991,14 +19969,14 @@
       <c r="C64" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>234</v>
+      <c r="D64" s="16" t="s">
+        <v>229</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
@@ -19025,14 +20003,14 @@
       <c r="C65" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>224</v>
+      <c r="D65" s="16" t="s">
+        <v>230</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>464</v>
+        <v>630</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
@@ -19050,35 +20028,16 @@
       <c r="N65" s="2"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A66" t="b">
-        <v>1</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>626</v>
-      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
-      <c r="I66" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -19091,30 +20050,34 @@
         <v>635</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>227</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="D67" s="2"/>
       <c r="E67" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
+      <c r="H67" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="I67" s="2" t="s">
-        <v>650</v>
+        <v>479</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>650</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
+        <v>657</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="N67" s="2"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
@@ -19125,30 +20088,34 @@
         <v>635</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>228</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D68" s="2"/>
       <c r="E68" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>628</v>
+        <v>650</v>
       </c>
       <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
+      <c r="H68" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="I68" s="2" t="s">
-        <v>650</v>
+        <v>480</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>650</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
+        <v>658</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="N68" s="2"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
@@ -19159,30 +20126,34 @@
         <v>635</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>220</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D69" s="2"/>
       <c r="E69" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>465</v>
+        <v>650</v>
       </c>
       <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
+      <c r="H69" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="I69" s="2" t="s">
-        <v>650</v>
+        <v>481</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>650</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
+        <v>659</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="N69" s="2"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
@@ -19193,30 +20164,34 @@
         <v>635</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>203</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D70" s="2"/>
       <c r="E70" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>466</v>
+        <v>650</v>
       </c>
       <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
+      <c r="H70" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="I70" s="2" t="s">
-        <v>650</v>
+        <v>482</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>650</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
+        <v>660</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="N70" s="2"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
@@ -19227,16 +20202,14 @@
         <v>635</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>223</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D71" s="2"/>
       <c r="E71" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>467</v>
+        <v>650</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -19244,13 +20217,17 @@
         <v>650</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>650</v>
+        <v>483</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
+        <v>661</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="N71" s="2"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
@@ -19261,16 +20238,14 @@
         <v>635</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>229</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D72" s="2"/>
       <c r="E72" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>629</v>
+        <v>650</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -19278,60 +20253,58 @@
         <v>650</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>650</v>
+        <v>484</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A73" t="b">
-        <v>1</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D73" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>630</v>
-      </c>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
-      <c r="I73" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J73" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K73" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="2"/>
+      <c r="A74" t="b">
+        <v>1</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
+      <c r="I74" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>687</v>
+      </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -19344,34 +20317,30 @@
         <v>635</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D75" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="E75" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>650</v>
+        <v>631</v>
       </c>
       <c r="G75" s="2"/>
-      <c r="H75" s="2" t="s">
-        <v>165</v>
-      </c>
+      <c r="H75" s="2"/>
       <c r="I75" s="2" t="s">
-        <v>479</v>
+        <v>650</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>650</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>155</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2"/>
       <c r="N75" s="2"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
@@ -19382,34 +20351,30 @@
         <v>635</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D76" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="E76" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>650</v>
+        <v>487</v>
       </c>
       <c r="G76" s="2"/>
-      <c r="H76" s="2" t="s">
-        <v>165</v>
-      </c>
+      <c r="H76" s="2"/>
       <c r="I76" s="2" t="s">
-        <v>480</v>
+        <v>650</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>650</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>155</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
       <c r="N76" s="2"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
@@ -19420,34 +20385,30 @@
         <v>635</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D77" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>237</v>
+      </c>
       <c r="E77" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>650</v>
+        <v>488</v>
       </c>
       <c r="G77" s="2"/>
-      <c r="H77" s="2" t="s">
-        <v>165</v>
-      </c>
+      <c r="H77" s="2"/>
       <c r="I77" s="2" t="s">
-        <v>481</v>
+        <v>650</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>650</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>155</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2"/>
       <c r="N77" s="2"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
@@ -19458,34 +20419,30 @@
         <v>635</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D78" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="E78" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>650</v>
+        <v>489</v>
       </c>
       <c r="G78" s="2"/>
-      <c r="H78" s="2" t="s">
-        <v>165</v>
-      </c>
+      <c r="H78" s="2"/>
       <c r="I78" s="2" t="s">
-        <v>482</v>
+        <v>650</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>650</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="L78" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="M78" s="2" t="s">
-        <v>155</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="L78" s="2"/>
+      <c r="M78" s="2"/>
       <c r="N78" s="2"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
@@ -19496,14 +20453,16 @@
         <v>635</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D79" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="E79" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>650</v>
+        <v>490</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -19511,17 +20470,13 @@
         <v>650</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>483</v>
+        <v>650</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="L79" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="M79" s="2" t="s">
-        <v>155</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2"/>
       <c r="N79" s="2"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
@@ -19532,14 +20487,16 @@
         <v>635</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D80" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>247</v>
+      </c>
       <c r="E80" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>650</v>
+        <v>491</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -19547,26 +20504,45 @@
         <v>650</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>484</v>
+        <v>650</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
+      <c r="A81" t="b">
+        <v>1</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>492</v>
+      </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
+      <c r="I81" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -19582,22 +20558,24 @@
         <v>37</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>816</v>
+        <v>249</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F82" s="2"/>
+      <c r="F82" s="2" t="s">
+        <v>493</v>
+      </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2" t="s">
         <v>650</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>485</v>
+        <v>650</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>687</v>
+        <v>650</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -19614,13 +20592,13 @@
         <v>37</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>631</v>
+        <v>494</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -19648,13 +20626,13 @@
         <v>37</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -19682,13 +20660,13 @@
         <v>37</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>488</v>
+        <v>632</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -19716,13 +20694,13 @@
         <v>37</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -19750,13 +20728,13 @@
         <v>37</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>490</v>
+        <v>633</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -19784,13 +20762,13 @@
         <v>37</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -19818,13 +20796,13 @@
         <v>37</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -19842,35 +20820,16 @@
       <c r="N89" s="2"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A90" t="b">
-        <v>1</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>493</v>
-      </c>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
-      <c r="I90" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J90" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -19883,27 +20842,25 @@
         <v>635</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>245</v>
+        <v>816</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>494</v>
-      </c>
+      <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="2" t="s">
         <v>650</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>650</v>
+        <v>486</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>650</v>
+        <v>688</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -19917,16 +20874,16 @@
         <v>635</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -19951,16 +20908,16 @@
         <v>635</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>632</v>
+        <v>500</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -19985,16 +20942,16 @@
         <v>635</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -20019,16 +20976,16 @@
         <v>635</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>633</v>
+        <v>502</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -20053,16 +21010,16 @@
         <v>635</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -20087,16 +21044,16 @@
         <v>635</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -20136,60 +21093,41 @@
         <v>635</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>816</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D99" s="2"/>
       <c r="E99" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F99" s="2"/>
+      <c r="F99" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="2" t="s">
         <v>650</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A100" t="b">
-        <v>1</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>498</v>
-      </c>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
-      <c r="I100" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J100" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K100" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
@@ -20202,16 +21140,16 @@
         <v>635</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>257</v>
+        <v>389</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>500</v>
+        <v>389</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -20219,10 +21157,10 @@
         <v>650</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>650</v>
+        <v>468</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>650</v>
+        <v>689</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -20236,16 +21174,16 @@
         <v>635</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>256</v>
+        <v>390</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>501</v>
+        <v>390</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -20270,16 +21208,16 @@
         <v>635</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>252</v>
+        <v>391</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -20304,16 +21242,16 @@
         <v>635</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>253</v>
+        <v>392</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>503</v>
+        <v>469</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -20338,16 +21276,16 @@
         <v>635</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>255</v>
+        <v>393</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>499</v>
+        <v>470</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -20365,16 +21303,35 @@
       <c r="N105" s="2"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
+      <c r="A106" t="b">
+        <v>1</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>471</v>
+      </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
-      <c r="J106" s="2"/>
-      <c r="K106" s="2"/>
+      <c r="I106" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>650</v>
+      </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
@@ -20387,79 +21344,79 @@
         <v>635</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D107" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>395</v>
+      </c>
       <c r="E107" s="2" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>650</v>
+        <v>390</v>
       </c>
       <c r="G107" s="2"/>
-      <c r="H107" s="2" t="s">
-        <v>165</v>
-      </c>
+      <c r="H107" s="2"/>
       <c r="I107" s="2" t="s">
-        <v>581</v>
+        <v>650</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>650</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="L107" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="M107" s="2" t="s">
-        <v>155</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="L107" s="2"/>
+      <c r="M107" s="2"/>
       <c r="N107" s="2"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A108" t="b">
-        <v>1</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
-      <c r="I108" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J108" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="K108" s="2" t="s">
-        <v>664</v>
-      </c>
+      <c r="I108" s="2"/>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2"/>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
+      <c r="A109" t="b">
+        <v>1</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>823</v>
+      </c>
       <c r="H109" s="2"/>
-      <c r="I109" s="2"/>
-      <c r="J109" s="2"/>
-      <c r="K109" s="2"/>
+      <c r="I109" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>690</v>
+      </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
@@ -20472,16 +21429,16 @@
         <v>635</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -20489,10 +21446,10 @@
         <v>650</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>468</v>
+        <v>650</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>689</v>
+        <v>650</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -20505,32 +21462,30 @@
       <c r="B111" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>390</v>
-      </c>
+      <c r="C111" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D111" s="1"/>
       <c r="E111" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F111" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="G111" s="2"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K111" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="L111" s="2"/>
-      <c r="M111" s="2"/>
-      <c r="N111" s="2"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="L111" s="1"/>
+      <c r="M111" s="1"/>
+      <c r="N111" s="18" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" t="b">
@@ -20540,958 +21495,56 @@
         <v>635</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>391</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D112" s="2"/>
       <c r="E112" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F112" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2" t="s">
         <v>650</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>650</v>
+        <v>583</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="L112" s="2"/>
-      <c r="M112" s="2"/>
-      <c r="N112" s="2"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A113" t="b">
-        <v>1</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="G113" s="2"/>
-      <c r="H113" s="2"/>
-      <c r="I113" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J113" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K113" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="L113" s="2"/>
-      <c r="M113" s="2"/>
-      <c r="N113" s="2"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A114" t="b">
-        <v>1</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="G114" s="2"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J114" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K114" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="L114" s="2"/>
-      <c r="M114" s="2"/>
-      <c r="N114" s="2"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A115" t="b">
-        <v>1</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="G115" s="2"/>
-      <c r="H115" s="2"/>
-      <c r="I115" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J115" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="L115" s="2"/>
-      <c r="M115" s="2"/>
-      <c r="N115" s="2"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A116" t="b">
-        <v>1</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="G116" s="2"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J116" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K116" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="L116" s="2"/>
-      <c r="M116" s="2"/>
-      <c r="N116" s="2"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="2"/>
-      <c r="J117" s="2"/>
-      <c r="K117" s="2"/>
-      <c r="L117" s="2"/>
-      <c r="M117" s="2"/>
-      <c r="N117" s="2"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A118" t="b">
-        <v>1</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="H118" s="2"/>
-      <c r="I118" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J118" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="K118" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="L118" s="2"/>
-      <c r="M118" s="2"/>
-      <c r="N118" s="2"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A119" t="b">
-        <v>1</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="G119" s="2"/>
-      <c r="H119" s="2"/>
-      <c r="I119" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J119" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K119" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="L119" s="2"/>
-      <c r="M119" s="2"/>
-      <c r="N119" s="2"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A120" t="b">
-        <v>1</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D120" s="1"/>
-      <c r="E120" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F120" s="1"/>
-      <c r="G120" s="1"/>
-      <c r="H120" s="1"/>
-      <c r="I120" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="J120" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K120" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="L120" s="1"/>
-      <c r="M120" s="1"/>
-      <c r="N120" s="18" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A121" t="b">
-        <v>1</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-      <c r="H121" s="2"/>
-      <c r="I121" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J121" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="K121" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="L121" s="2" t="s">
+      <c r="L112" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="M121" s="2" t="s">
+      <c r="M112" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N121" s="2" t="s">
+      <c r="N112" s="2" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A122" t="b">
-        <v>1</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D122" s="2"/>
-      <c r="E122" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G122" s="2"/>
-      <c r="H122" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="J122" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K122" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="L122" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="M122" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="N122" s="2"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A123" t="b">
-        <v>1</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D123" s="2"/>
-      <c r="E123" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G123" s="2"/>
-      <c r="H123" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J123" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K123" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="L123" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="M123" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="N123" s="2"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A124" t="b">
-        <v>1</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G124" s="2"/>
-      <c r="H124" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="J124" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K124" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="L124" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="M124" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="N124" s="2"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A125" t="b">
-        <v>1</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D125" s="2"/>
-      <c r="E125" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G125" s="2"/>
-      <c r="H125" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J125" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K125" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="L125" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="M125" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="N125" s="2"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A126" t="b">
-        <v>1</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D126" s="2"/>
-      <c r="E126" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G126" s="2"/>
-      <c r="H126" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J126" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K126" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="L126" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="M126" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="N126" s="2"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A127" t="b">
-        <v>1</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D127" s="2"/>
-      <c r="E127" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G127" s="2"/>
-      <c r="H127" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I127" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="J127" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K127" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="L127" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="M127" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="N127" s="2"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A128" t="b">
-        <v>1</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D128" s="2"/>
-      <c r="E128" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K128" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="L128" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="M128" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="N128" s="2" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A129" t="b">
-        <v>1</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D129" s="2"/>
-      <c r="E129" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="J129" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K129" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="L129" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="M129" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="N129" s="1" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A130" t="b">
-        <v>1</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D130" s="2"/>
-      <c r="E130" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G130" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I130" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="J130" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K130" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="L130" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="M130" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="N130" s="1" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A131" t="b">
-        <v>1</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K131" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="L131" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="M131" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="N131" s="1" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A132" t="b">
-        <v>1</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="J132" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K132" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="L132" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="M132" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="N132" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A133" t="b">
-        <v>1</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D133" s="2"/>
-      <c r="E133" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G133" s="2"/>
-      <c r="H133" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I133" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="J133" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="L133" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="M133" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="N133" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A134" t="b">
-        <v>1</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D134" s="2"/>
-      <c r="E134" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="J134" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K134" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="L134" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="M134" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="N134" s="2"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A135" t="b">
-        <v>1</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D135" s="2"/>
-      <c r="E135" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G135" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="J135" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K135" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="L135" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="M135" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="N135" s="2"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A136" t="b">
-        <v>1</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D136" s="2"/>
-      <c r="E136" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G136" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="J136" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K136" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="L136" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="M136" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="N136" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N136" xr:uid="{B39AC7DD-3F73-2C47-925D-21E5B4EBE6FC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D99:D105">
-    <sortCondition ref="D99:D105"/>
-  </sortState>
-  <conditionalFormatting sqref="I99:J99">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+  <conditionalFormatting sqref="I91:J91">
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K94">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+  <conditionalFormatting sqref="K86">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K121:M121">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L122 I122:J122 L127:L128">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L134">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L135">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L136">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  <conditionalFormatting sqref="K112:M112">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4CA3B6-4765-0A43-8534-6DA7BF8A336D}">
   <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
@@ -21711,7 +21764,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="b">
         <v>1</v>
       </c>
@@ -21805,7 +21858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC10C3F-0C27-5546-8767-E60C7CACEA9D}">
   <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -25552,7 +25605,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{077DB476-AE11-E742-9E3D-7ABA37A90AEF}">
   <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -26432,7 +26485,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FF6C9F4-4010-9243-98AE-74EEEFFCAC53}">
   <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047DCD60-FE69-034B-BFC5-840057F0F7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20896D0A-180B-FA43-866E-616E12B509CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7400" yWindow="500" windowWidth="38940" windowHeight="20920" activeTab="1" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="1980" yWindow="500" windowWidth="38940" windowHeight="20920" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
     <sheet name="wide_measures" sheetId="2" r:id="rId2"/>
-    <sheet name="wide_protocolSteps" sheetId="8" r:id="rId3"/>
-    <sheet name="wide_qualityReports" sheetId="7" r:id="rId4"/>
+    <sheet name="wide_qualityReports" sheetId="7" r:id="rId3"/>
+    <sheet name="wide_protocolSteps" sheetId="8" r:id="rId4"/>
     <sheet name="enums" sheetId="3" r:id="rId5"/>
     <sheet name="id_gen" sheetId="4" r:id="rId6"/>
     <sheet name="maps original" sheetId="6" r:id="rId7"/>
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">enums!$A$1:$J$185</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maps!$A$1:$L$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'maps original'!$A$1:$L$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">wide_measures!$A$1:$N$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">wide_measures!$A$1:$O$24</definedName>
     <definedName name="partID">[1]parts!$A:$A</definedName>
     <definedName name="partLabel">[1]parts!$B:$B</definedName>
   </definedNames>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3025" uniqueCount="861">
   <si>
     <t>Reporter</t>
   </si>
@@ -2247,9 +2247,6 @@
     <t>For source slot pcr_gene_target</t>
   </si>
   <si>
-    <t>For source slot .hum_frac_target_mic</t>
-  </si>
-  <si>
     <t>For source slot hum_frac_target_chem</t>
   </si>
   <si>
@@ -2596,6 +2593,81 @@
   </si>
   <si>
     <t>targetExpr</t>
+  </si>
+  <si>
+    <t>For source slot hum_frac_target_mic</t>
+  </si>
+  <si>
+    <t>measureRepID_value</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID0}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID1}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID2}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID3}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID4}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID5}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID6}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID7}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID8}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID9}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID10}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID11}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID12}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID13}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID14}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID15}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID16}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID17}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID18}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID19}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID20}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID21}}</t>
+  </si>
+  <si>
+    <t>{{id:measureRepID22}}</t>
   </si>
 </sst>
 </file>
@@ -14154,7 +14226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}">
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="27.1640625" customWidth="1"/>
@@ -14193,7 +14265,7 @@
         <v>640</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>682</v>
@@ -14220,7 +14292,7 @@
         <v>115</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>709</v>
@@ -14311,7 +14383,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -14375,14 +14447,14 @@
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="21" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="1" t="s">
         <v>614</v>
       </c>
       <c r="L8" s="19" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -14530,13 +14602,13 @@
         <v>121</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
       <c r="K14" s="2"/>
       <c r="L14" s="22" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -14577,7 +14649,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="2"/>
       <c r="L16" s="22" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -15058,7 +15130,7 @@
       <c r="J33" s="31"/>
       <c r="K33" s="28"/>
       <c r="L33" s="19" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
@@ -15094,7 +15166,7 @@
         <v>121</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
@@ -15123,7 +15195,7 @@
         <v>121</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
@@ -15176,7 +15248,7 @@
         <v>77</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>714</v>
@@ -15749,7 +15821,7 @@
         <v>57</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>118</v>
@@ -15854,7 +15926,7 @@
         <v>58</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>118</v>
@@ -15962,7 +16034,7 @@
         <v>56</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>147</v>
@@ -16065,7 +16137,7 @@
         <v>64</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>147</v>
@@ -16184,14 +16256,14 @@
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="17" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="L78" s="19" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -16344,7 +16416,7 @@
         <v>69</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>147</v>
@@ -16447,7 +16519,7 @@
         <v>73</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>147</v>
@@ -16540,14 +16612,14 @@
         <v>635</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H93" s="2" t="str">
         <f>"{{"&amp;D93&amp;"}}"</f>
@@ -16566,17 +16638,17 @@
         <v>635</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H94" s="2" t="str">
-        <f t="shared" ref="H94:H101" si="0">"{{"&amp;D94&amp;"}}"</f>
+        <f t="shared" ref="H94:H99" si="0">"{{"&amp;D94&amp;"}}"</f>
         <v>{{id:addressID}}</v>
       </c>
       <c r="I94" s="2"/>
@@ -16592,14 +16664,14 @@
         <v>635</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2" t="s">
         <v>115</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H95" s="2" t="str">
         <f>"{{"&amp;D95&amp;"}}"</f>
@@ -16618,18 +16690,18 @@
         <v>635</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2" t="s">
         <v>115</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H96" s="2" t="str">
         <f>"{{"&amp;D96&amp;"}}"</f>
-        <v>{{id:measureRepID}}</v>
+        <v>{{id:measureSetRepID}}</v>
       </c>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
@@ -16644,17 +16716,17 @@
         <v>635</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H97" s="2" t="str">
-        <f>"{{"&amp;D97&amp;"}}"</f>
+        <f t="shared" si="0"/>
         <v>{{id:measureSetRepID}}</v>
       </c>
       <c r="I97" s="2"/>
@@ -16670,18 +16742,18 @@
         <v>635</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>742</v>
+        <v>752</v>
       </c>
       <c r="H98" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>{{id:measureRepID}}</v>
+        <v>{{id:instrumentID}}</v>
       </c>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
@@ -16700,14 +16772,14 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="H99" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>{{id:measureSetRepID}}</v>
+        <v>{{id:stepID}}</v>
       </c>
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
@@ -16722,18 +16794,18 @@
         <v>635</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>152</v>
+        <v>476</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="H100" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>{{id:instrumentID}}</v>
+        <f>"{{"&amp;D100&amp;"}}"</f>
+        <v>{{id:datasetID}}</v>
       </c>
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
@@ -16748,18 +16820,18 @@
         <v>635</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="H101" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>{{id:stepID}}</v>
+        <f>"{{"&amp;D101&amp;"}}"</f>
+        <v>{{id:datasetID}}</v>
       </c>
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
@@ -16774,14 +16846,14 @@
         <v>635</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
-        <v>476</v>
+        <v>77</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H102" s="2" t="str">
         <f>"{{"&amp;D102&amp;"}}"</f>
@@ -16790,58 +16862,6 @@
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A103" t="b">
-        <v>1</v>
-      </c>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="H103" s="2" t="str">
-        <f>"{{"&amp;D103&amp;"}}"</f>
-        <v>{{id:datasetID}}</v>
-      </c>
-      <c r="I103" s="2"/>
-      <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A104" t="b">
-        <v>1</v>
-      </c>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="H104" s="2" t="str">
-        <f>"{{"&amp;D104&amp;"}}"</f>
-        <v>{{id:datasetID}}</v>
-      </c>
-      <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L91" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}"/>
@@ -16855,21 +16875,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B39AC7DD-3F73-2C47-925D-21E5B4EBE6FC}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.6640625" customWidth="1"/>
     <col min="3" max="4" width="25.5" customWidth="1"/>
-    <col min="5" max="7" width="22.5" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="10" width="29.33203125" customWidth="1"/>
-    <col min="11" max="11" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5" customWidth="1"/>
-    <col min="13" max="13" width="19" customWidth="1"/>
-    <col min="14" max="14" width="27.6640625" customWidth="1"/>
+    <col min="5" max="8" width="22.5" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="11" width="29.33203125" customWidth="1"/>
+    <col min="12" max="12" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5" customWidth="1"/>
+    <col min="14" max="14" width="19" customWidth="1"/>
+    <col min="15" max="15" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="24" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="24" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>680</v>
       </c>
@@ -16891,29 +16911,32 @@
       <c r="G1" s="9" t="s">
         <v>698</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>829</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>830</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>831</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>832</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>833</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="N1" s="11" t="s">
         <v>834</v>
       </c>
-      <c r="M1" s="11" t="s">
-        <v>835</v>
-      </c>
-      <c r="N1" s="12" t="s">
+      <c r="O1" s="12" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="b">
         <v>1</v>
       </c>
@@ -16931,27 +16954,30 @@
         <v>650</v>
       </c>
       <c r="G2" s="2"/>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="I2" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="J2" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="J2" s="13" t="s">
-        <v>650</v>
-      </c>
       <c r="K2" s="13" t="s">
+        <v>650</v>
+      </c>
+      <c r="L2" s="13" t="s">
         <v>651</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="M2" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="N2" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="b">
         <v>1</v>
       </c>
@@ -16970,26 +16996,29 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K3" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="N3" s="2"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="b">
         <v>1</v>
       </c>
@@ -17008,26 +17037,29 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K4" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="b">
         <v>1</v>
       </c>
@@ -17046,22 +17078,25 @@
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K5" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="b">
         <v>1</v>
       </c>
@@ -17080,26 +17115,29 @@
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K6" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="b">
         <v>1</v>
       </c>
@@ -17118,26 +17156,29 @@
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K7" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="b">
         <v>1</v>
       </c>
@@ -17155,25 +17196,28 @@
         <v>650</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K8" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="b">
         <v>1</v>
       </c>
@@ -17192,26 +17236,29 @@
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K9" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="N9" s="2"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="b">
         <v>1</v>
       </c>
@@ -17230,26 +17277,29 @@
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K10" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N10" s="2"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="b">
         <v>1</v>
       </c>
@@ -17268,26 +17318,29 @@
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K11" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="N11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="b">
         <v>1</v>
       </c>
@@ -17306,26 +17359,29 @@
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K12" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" t="b">
         <v>1</v>
       </c>
@@ -17344,26 +17400,29 @@
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K13" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="N13" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" t="b">
         <v>1</v>
       </c>
@@ -17382,26 +17441,29 @@
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K14" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="N14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" t="b">
         <v>1</v>
       </c>
@@ -17420,26 +17482,29 @@
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K15" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="N15" s="2"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="b">
         <v>1</v>
       </c>
@@ -17457,31 +17522,34 @@
         <v>650</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="b">
         <v>1</v>
       </c>
@@ -17499,31 +17567,34 @@
         <v>650</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K17" s="2" t="s">
+      <c r="K17" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="O17" s="1" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="b">
         <v>1</v>
       </c>
@@ -17541,31 +17612,34 @@
         <v>650</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="M18" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="O18" s="1" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="b">
         <v>1</v>
       </c>
@@ -17583,31 +17657,34 @@
         <v>650</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K19" s="2" t="s">
+      <c r="K19" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="L19" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="M19" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="O19" s="1" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="b">
         <v>1</v>
       </c>
@@ -17625,31 +17702,34 @@
         <v>650</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H20" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="J20" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K20" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="O20" s="1" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="b">
         <v>1</v>
       </c>
@@ -17668,28 +17748,31 @@
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="J21" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="K21" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="M21" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="O21" s="1" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="b">
         <v>1</v>
       </c>
@@ -17707,29 +17790,32 @@
         <v>650</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K22" s="2" t="s">
+      <c r="K22" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="L22" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N22" s="2"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="2"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="b">
         <v>1</v>
       </c>
@@ -17747,29 +17833,32 @@
         <v>650</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K23" s="2" t="s">
+      <c r="K23" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="L23" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N23" s="2"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="2"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="b">
         <v>1</v>
       </c>
@@ -17787,40 +17876,43 @@
         <v>650</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="K24" s="2" t="s">
+      <c r="K24" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="M24" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N24" xr:uid="{B39AC7DD-3F73-2C47-925D-21E5B4EBE6FC}"/>
-  <conditionalFormatting sqref="L10 I10:J10 L15:L16">
+  <autoFilter ref="A1:O24" xr:uid="{B39AC7DD-3F73-2C47-925D-21E5B4EBE6FC}"/>
+  <conditionalFormatting sqref="M10 J10:K10 M15:M16">
     <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L22">
+  <conditionalFormatting sqref="M22">
     <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L23">
+  <conditionalFormatting sqref="M23">
     <cfRule type="duplicateValues" dxfId="6" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L24">
+  <conditionalFormatting sqref="M24">
     <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17829,6 +17921,326 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4CA3B6-4765-0A43-8534-6DA7BF8A336D}">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="10" width="22.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="24" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>680</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>819</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>820</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>817</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H2" t="s">
+        <v>807</v>
+      </c>
+      <c r="I2" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>635</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>635</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>815</v>
+      </c>
+      <c r="E4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>635</v>
+      </c>
+      <c r="C6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6" t="s">
+        <v>596</v>
+      </c>
+      <c r="H6" t="s">
+        <v>808</v>
+      </c>
+      <c r="I6" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>635</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>635</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>815</v>
+      </c>
+      <c r="E8" t="s">
+        <v>147</v>
+      </c>
+      <c r="F8" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>635</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F10" t="s">
+        <v>602</v>
+      </c>
+      <c r="H10" t="s">
+        <v>810</v>
+      </c>
+      <c r="I10" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>635</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>635</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" t="s">
+        <v>147</v>
+      </c>
+      <c r="H13" t="s">
+        <v>812</v>
+      </c>
+      <c r="J13" s="34" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J14" s="34"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>635</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" t="s">
+        <v>149</v>
+      </c>
+      <c r="H15" t="s">
+        <v>813</v>
+      </c>
+      <c r="I15" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>635</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" t="s">
+        <v>147</v>
+      </c>
+      <c r="F16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>635</v>
+      </c>
+      <c r="C17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
+        <v>815</v>
+      </c>
+      <c r="E17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDC6A21B-0669-0743-9D12-F41DCA15CA4A}">
   <dimension ref="A1:N112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -17872,22 +18284,22 @@
         <v>698</v>
       </c>
       <c r="H1" s="11" t="s">
+        <v>829</v>
+      </c>
+      <c r="I1" s="11" t="s">
         <v>830</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>831</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>832</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>833</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>834</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>835</v>
       </c>
       <c r="N1" s="12" t="s">
         <v>121</v>
@@ -18040,7 +18452,7 @@
         <v>28</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>152</v>
@@ -20288,7 +20700,7 @@
         <v>37</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>152</v>
@@ -20845,7 +21257,7 @@
         <v>38</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>152</v>
@@ -21405,7 +21817,7 @@
         <v>408</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H109" s="2"/>
       <c r="I109" s="2" t="s">
@@ -21534,326 +21946,6 @@
   <conditionalFormatting sqref="K112:M112">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4CA3B6-4765-0A43-8534-6DA7BF8A336D}">
-  <dimension ref="A1:K17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="10" width="22.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="24" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>680</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>636</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>698</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>820</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>821</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>818</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="b">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H2" t="s">
-        <v>808</v>
-      </c>
-      <c r="I2" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" t="b">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>635</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="b">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>635</v>
-      </c>
-      <c r="C4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" t="s">
-        <v>816</v>
-      </c>
-      <c r="E4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" t="b">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>635</v>
-      </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" t="s">
-        <v>596</v>
-      </c>
-      <c r="H6" t="s">
-        <v>809</v>
-      </c>
-      <c r="I6" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>635</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" t="s">
-        <v>142</v>
-      </c>
-      <c r="E7" t="s">
-        <v>147</v>
-      </c>
-      <c r="F7" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" t="b">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
-        <v>635</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>816</v>
-      </c>
-      <c r="E8" t="s">
-        <v>147</v>
-      </c>
-      <c r="F8" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>635</v>
-      </c>
-      <c r="C10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" t="s">
-        <v>602</v>
-      </c>
-      <c r="H10" t="s">
-        <v>811</v>
-      </c>
-      <c r="I10" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" t="b">
-        <v>1</v>
-      </c>
-      <c r="B11" t="s">
-        <v>635</v>
-      </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E11" t="s">
-        <v>147</v>
-      </c>
-      <c r="F11" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" t="b">
-        <v>1</v>
-      </c>
-      <c r="B13" t="s">
-        <v>635</v>
-      </c>
-      <c r="C13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" t="s">
-        <v>147</v>
-      </c>
-      <c r="H13" t="s">
-        <v>813</v>
-      </c>
-      <c r="J13" s="34" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J14" s="34"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" t="b">
-        <v>1</v>
-      </c>
-      <c r="B15" t="s">
-        <v>635</v>
-      </c>
-      <c r="C15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" t="s">
-        <v>141</v>
-      </c>
-      <c r="E15" t="s">
-        <v>147</v>
-      </c>
-      <c r="F15" t="s">
-        <v>149</v>
-      </c>
-      <c r="H15" t="s">
-        <v>814</v>
-      </c>
-      <c r="I15" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" t="b">
-        <v>1</v>
-      </c>
-      <c r="B16" t="s">
-        <v>635</v>
-      </c>
-      <c r="C16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" t="s">
-        <v>142</v>
-      </c>
-      <c r="E16" t="s">
-        <v>147</v>
-      </c>
-      <c r="F16" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="b">
-        <v>1</v>
-      </c>
-      <c r="B17" t="s">
-        <v>635</v>
-      </c>
-      <c r="C17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" t="s">
-        <v>816</v>
-      </c>
-      <c r="E17" t="s">
-        <v>147</v>
-      </c>
-      <c r="F17" t="s">
-        <v>150</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -24647,7 +24739,7 @@
         <v>505</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>724</v>
+        <v>836</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
@@ -24760,7 +24852,7 @@
         <v>701</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
@@ -24789,7 +24881,7 @@
         <v>609</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
@@ -24862,7 +24954,7 @@
         <v>702</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
@@ -24891,7 +24983,7 @@
         <v>505</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
@@ -25084,7 +25176,7 @@
         <v>703</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
@@ -25113,7 +25205,7 @@
         <v>584</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.2">
@@ -25588,7 +25680,7 @@
         <v>705</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
@@ -25618,7 +25710,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B1" s="23" t="s">
         <v>638</v>
@@ -25630,13 +25722,13 @@
         <v>636</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F1" s="23" t="s">
+        <v>788</v>
+      </c>
+      <c r="G1" s="23" t="s">
         <v>789</v>
-      </c>
-      <c r="G1" s="23" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -25647,16 +25739,16 @@
         <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E2" t="s">
+        <v>797</v>
+      </c>
+      <c r="F2" t="s">
+        <v>799</v>
+      </c>
+      <c r="G2" t="s">
         <v>798</v>
-      </c>
-      <c r="F2" t="s">
-        <v>800</v>
-      </c>
-      <c r="G2" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -25664,10 +25756,10 @@
         <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -25678,16 +25770,16 @@
         <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="F5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G5" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -25707,10 +25799,10 @@
         <v>719</v>
       </c>
       <c r="F6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G6" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -25727,10 +25819,10 @@
         <v>716</v>
       </c>
       <c r="F7" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G7" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -25741,16 +25833,16 @@
         <v>115</v>
       </c>
       <c r="C8" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E8" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -25767,10 +25859,10 @@
         <v>710</v>
       </c>
       <c r="F9" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G9" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -25781,16 +25873,16 @@
         <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E10" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F10" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G10" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -25801,16 +25893,16 @@
         <v>115</v>
       </c>
       <c r="C11" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E11" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="F11" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G11" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -25827,10 +25919,10 @@
         <v>717</v>
       </c>
       <c r="F12" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G12" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -25841,7 +25933,7 @@
         <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D13" t="s">
         <v>709</v>
@@ -25850,10 +25942,10 @@
         <v>709</v>
       </c>
       <c r="F13" t="s">
+        <v>786</v>
+      </c>
+      <c r="G13" t="s">
         <v>787</v>
-      </c>
-      <c r="G13" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -25864,10 +25956,10 @@
         <v>476</v>
       </c>
       <c r="C15" t="s">
+        <v>749</v>
+      </c>
+      <c r="E15" t="s">
         <v>750</v>
-      </c>
-      <c r="E15" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -25895,10 +25987,10 @@
         <v>476</v>
       </c>
       <c r="C17" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E17" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -25923,7 +26015,7 @@
         <v>476</v>
       </c>
       <c r="C19" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E19" t="s">
         <v>709</v>
@@ -25937,16 +26029,16 @@
         <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E21" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F21" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G21" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -25971,7 +26063,7 @@
         <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E23" t="s">
         <v>709</v>
@@ -25985,16 +26077,16 @@
         <v>152</v>
       </c>
       <c r="C24" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E24" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F24" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G24" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -26005,16 +26097,16 @@
         <v>147</v>
       </c>
       <c r="C26" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E26" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="F26" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G26" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -26025,10 +26117,10 @@
         <v>147</v>
       </c>
       <c r="C27" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E27" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -26053,10 +26145,10 @@
         <v>147</v>
       </c>
       <c r="C29" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E29" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -26115,7 +26207,7 @@
         <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E34" t="s">
         <v>709</v>
@@ -26143,10 +26235,10 @@
         <v>118</v>
       </c>
       <c r="C36" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E36" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -26157,7 +26249,7 @@
         <v>77</v>
       </c>
       <c r="C38" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
@@ -26185,10 +26277,10 @@
         <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E40" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
@@ -26199,16 +26291,16 @@
         <v>77</v>
       </c>
       <c r="C41" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E41" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F41" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G41" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -26219,10 +26311,10 @@
         <v>77</v>
       </c>
       <c r="C42" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E42" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -26247,7 +26339,7 @@
         <v>77</v>
       </c>
       <c r="C44" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E44" t="s">
         <v>709</v>
@@ -26261,7 +26353,7 @@
         <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -26272,7 +26364,7 @@
         <v>77</v>
       </c>
       <c r="C46" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26280,15 +26372,15 @@
         <v>0</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C48" s="32" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="49" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C49" s="32" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="50" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26301,7 +26393,7 @@
         <v>0</v>
       </c>
       <c r="B52" s="32" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="54" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26309,35 +26401,35 @@
         <v>0</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C54" s="32" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="55" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C55" s="32" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="56" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C56" s="32" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="57" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C57" s="32" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="58" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C58" s="32" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="59" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C59" s="32" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="61" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26345,20 +26437,20 @@
         <v>0</v>
       </c>
       <c r="B61" s="32" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="62" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C62" s="32" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="63" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C63" s="32" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="64" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26371,7 +26463,7 @@
         <v>0</v>
       </c>
       <c r="B66" s="32" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="68" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26379,10 +26471,10 @@
         <v>0</v>
       </c>
       <c r="B68" s="32" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C68" s="32" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="69" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26397,7 +26489,7 @@
     </row>
     <row r="71" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C71" s="32" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="73" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26405,7 +26497,7 @@
         <v>0</v>
       </c>
       <c r="B73" s="32" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C73" s="32" t="s">
         <v>144</v>
@@ -26413,12 +26505,12 @@
     </row>
     <row r="74" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C74" s="32" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="75" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C75" s="32" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="77" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26426,15 +26518,15 @@
         <v>0</v>
       </c>
       <c r="B77" s="32" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C77" s="32" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="78" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C78" s="32" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="79" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26444,7 +26536,7 @@
     </row>
     <row r="80" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C80" s="32" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="82" spans="1:2" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26452,7 +26544,7 @@
         <v>0</v>
       </c>
       <c r="B82" s="32" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="84" spans="1:2" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26460,7 +26552,7 @@
         <v>0</v>
       </c>
       <c r="B84" s="32" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="86" spans="1:2" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26468,7 +26560,7 @@
         <v>0</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="88" spans="1:2" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -26476,7 +26568,7 @@
         <v>0</v>
       </c>
       <c r="B88" s="32" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
   </sheetData>
@@ -26555,7 +26647,7 @@
         <v>115</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>709</v>
@@ -26618,14 +26710,14 @@
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="21" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="1" t="s">
         <v>614</v>
       </c>
       <c r="L4" s="19" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -26777,13 +26869,13 @@
         <v>121</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="2"/>
       <c r="L10" s="22" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -26828,7 +26920,7 @@
       <c r="J12" s="28"/>
       <c r="K12" s="28"/>
       <c r="L12" s="19" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -27266,7 +27358,7 @@
       <c r="J27" s="31"/>
       <c r="K27" s="28"/>
       <c r="L27" s="19" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -27302,7 +27394,7 @@
         <v>121</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -27331,7 +27423,7 @@
         <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -27384,7 +27476,7 @@
         <v>77</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>714</v>
@@ -28445,14 +28537,14 @@
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="17" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="L74" s="19" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F92C19-512E-3C41-ACA8-AE862A9ABD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F379BF-1E55-BE48-A1A6-2C0B94893D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1980" yWindow="500" windowWidth="38940" windowHeight="20880" activeTab="2" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
@@ -2725,13 +2725,6 @@
   </si>
   <si>
     <t>case(
-    ((str(inhibition_detect) == "yes") * (str(inhibition_adjust) == "yes"), "flagFI"),
-    ((str(inhibition_detect) == "yes") * (str(inhibition_adjust) == "no"), "flagAI"),
-    (True, "&lt;ignore&gt;")
-)</t>
-  </si>
-  <si>
-    <t>case(
     (sample_location == "wwtp",
         case((stormwater_input == "yes", "wwtpMuC"),
             (stormwater_input == "no", "wwtpMuS"),
@@ -2747,6 +2740,13 @@
         )
     ),
     (True, "")
+)</t>
+  </si>
+  <si>
+    <t>case(
+    ((inhibition_detect == "yes") * (inhibition_adjust == "yes"), "flagFI"),
+    ((inhibition_detect == "yes") * (inhibition_adjust == "no"), "flagAI"),
+    (True, "&lt;ignore&gt;")
 )</t>
   </si>
 </sst>
@@ -15526,7 +15526,7 @@
       </c>
       <c r="G57" s="27"/>
       <c r="H57" s="50" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="I57" s="27"/>
       <c r="J57" s="27"/>
@@ -17036,7 +17036,7 @@
         <v>799</v>
       </c>
       <c r="K2" s="42" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="L2" s="42" t="s">
         <v>866</v>

--- a/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
+++ b/data/mapping_config_files/NWSS-to-ODM-dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75B0A60-DEA7-1E4F-94E8-FDE80A882ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE17CF6-4E3F-5241-AEC0-B0C17D9F9EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="500" windowWidth="38940" windowHeight="20880" activeTab="3" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" activeTab="1" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2796" uniqueCount="882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2797" uniqueCount="883">
   <si>
     <t>Reporter</t>
   </si>
@@ -2745,6 +2745,9 @@
   </si>
   <si>
     <t>(dashboard_ignore == 'yes') + (analysis_ignore == 'yes') == 0</t>
+  </si>
+  <si>
+    <t>Is ml OR grams for unit_value correct?</t>
   </si>
 </sst>
 </file>
@@ -2945,7 +2948,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -3022,7 +3025,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15807,6 +15809,9 @@
       <c r="P7" s="25" t="s">
         <v>154</v>
       </c>
+      <c r="T7" s="26" t="s">
+        <v>882</v>
+      </c>
     </row>
     <row r="8" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="b">
@@ -16044,7 +16049,6 @@
       <c r="Q13" s="25" t="s">
         <v>872</v>
       </c>
-      <c r="T13" s="44"/>
     </row>
     <row r="14" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="b">
@@ -16384,7 +16388,6 @@
       <c r="P21" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="T21" s="44"/>
     </row>
     <row r="22" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="25" t="b">
